--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,6 +1560,2783 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123008031</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>712167</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6649816</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123008249</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>712159</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6649832</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122996823</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>712187</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6650002</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123007916</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>712142</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6649796</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123000056</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>712308</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6649706</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122998729</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>712176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6649818</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122997739</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>712167</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6649980</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122999323</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>712171</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6649822</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123002767</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>712151</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6649915</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122997583</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>712166</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6649973</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123000064</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>712318</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6649737</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122998042</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>712150</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6649898</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123009298</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>712186</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6649996</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122997028</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>712198</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6650001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122997556</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>712163</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6649978</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123000100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4776</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>712304</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6649724</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122999077</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>712127</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6649778</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122999168</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>712092</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6649793</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123008181</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>712179</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6649820</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122998889</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>712161</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6649804</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122998873</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>712170</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6649811</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123009388</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>712196</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6650006</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123001398</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>712451</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6649760</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122998128</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kvarnån, Kvarnån, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>712162</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6649897</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,7 +1562,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008031</v>
+        <v>123002767</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,16 +1605,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712167</v>
+        <v>712151</v>
       </c>
       <c r="R9" t="n">
-        <v>6649816</v>
+        <v>6649915</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,19 +1649,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,22 +1666,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123008249</v>
+        <v>123000056</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>97311</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,52 +1690,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712159</v>
+        <v>712308</v>
       </c>
       <c r="R10" t="n">
-        <v>6649832</v>
+        <v>6649706</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1780,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122996823</v>
+        <v>123008249</v>
       </c>
       <c r="B11" t="n">
         <v>98357</v>
@@ -1834,7 +1815,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1847,18 +1828,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712187</v>
+        <v>712159</v>
       </c>
       <c r="R11" t="n">
-        <v>6650002</v>
+        <v>6649832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,7 +1878,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1918,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123007916</v>
+        <v>122997556</v>
       </c>
       <c r="B12" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1930,40 +1908,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1972,10 +1941,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712142</v>
+        <v>712163</v>
       </c>
       <c r="R12" t="n">
-        <v>6649796</v>
+        <v>6649978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2034,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123000056</v>
+        <v>122999077</v>
       </c>
       <c r="B13" t="n">
-        <v>97311</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,38 +2015,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712308</v>
+        <v>712127</v>
       </c>
       <c r="R13" t="n">
-        <v>6649706</v>
+        <v>6649778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2118,6 +2103,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2136,7 +2122,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122998729</v>
+        <v>122998889</v>
       </c>
       <c r="B14" t="n">
         <v>98357</v>
@@ -2171,7 +2157,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2184,18 +2170,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712176</v>
+        <v>712161</v>
       </c>
       <c r="R14" t="n">
-        <v>6649818</v>
+        <v>6649804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,7 +2220,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2238,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122997739</v>
+        <v>122998128</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2290,7 +2273,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2298,16 +2281,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712167</v>
+        <v>712162</v>
       </c>
       <c r="R15" t="n">
-        <v>6649980</v>
+        <v>6649897</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,19 +2325,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,19 +2342,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122999323</v>
+        <v>122997739</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2425,10 +2403,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712171</v>
+        <v>712167</v>
       </c>
       <c r="R16" t="n">
-        <v>6649822</v>
+        <v>6649980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,7 +2438,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2470,7 +2448,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2475,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123002767</v>
+        <v>122998042</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2532,7 +2510,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2545,16 +2523,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712151</v>
+        <v>712150</v>
       </c>
       <c r="R17" t="n">
-        <v>6649915</v>
+        <v>6649898</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2595,6 +2575,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2613,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122997583</v>
+        <v>122997028</v>
       </c>
       <c r="B18" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,31 +2606,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2658,13 +2643,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712166</v>
+        <v>712198</v>
       </c>
       <c r="R18" t="n">
-        <v>6649973</v>
+        <v>6650001</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2691,9 +2676,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,22 +2703,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123000064</v>
+        <v>122999323</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2732,31 +2727,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2765,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712318</v>
+        <v>712171</v>
       </c>
       <c r="R19" t="n">
-        <v>6649737</v>
+        <v>6649822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2800,7 +2799,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2809,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,7 +2836,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122998042</v>
+        <v>122996823</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -2872,7 +2871,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2893,10 +2892,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712150</v>
+        <v>712187</v>
       </c>
       <c r="R20" t="n">
-        <v>6649898</v>
+        <v>6650002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2956,7 +2955,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123009298</v>
+        <v>123008181</v>
       </c>
       <c r="B21" t="n">
         <v>98357</v>
@@ -2991,7 +2990,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3005,10 +3004,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712186</v>
+        <v>712179</v>
       </c>
       <c r="R21" t="n">
-        <v>6649996</v>
+        <v>6649820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,7 +3039,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,7 +3049,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,10 +3076,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122997028</v>
+        <v>123000064</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3089,35 +3088,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712198</v>
+        <v>712318</v>
       </c>
       <c r="R22" t="n">
-        <v>6650001</v>
+        <v>6649737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3161,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3171,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,10 +3193,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122997556</v>
+        <v>123009298</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3210,31 +3205,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3243,10 +3242,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712163</v>
+        <v>712186</v>
       </c>
       <c r="R23" t="n">
-        <v>6649978</v>
+        <v>6649996</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,9 +3275,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,22 +3302,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123000100</v>
+        <v>122998729</v>
       </c>
       <c r="B24" t="n">
-        <v>4776</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3317,43 +3326,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712304</v>
+        <v>712176</v>
       </c>
       <c r="R24" t="n">
-        <v>6649724</v>
+        <v>6649818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3394,6 +3414,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3412,7 +3433,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122999077</v>
+        <v>123008031</v>
       </c>
       <c r="B25" t="n">
         <v>98357</v>
@@ -3447,7 +3468,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,23 +3476,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712127</v>
+        <v>712167</v>
       </c>
       <c r="R25" t="n">
-        <v>6649778</v>
+        <v>6649816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,40 +3515,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122999168</v>
+        <v>123000100</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3547,21 +3570,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3576,10 +3599,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712092</v>
+        <v>712304</v>
       </c>
       <c r="R26" t="n">
-        <v>6649793</v>
+        <v>6649724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3638,7 +3661,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123008181</v>
+        <v>122998873</v>
       </c>
       <c r="B27" t="n">
         <v>98357</v>
@@ -3673,7 +3696,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3681,16 +3704,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712179</v>
+        <v>712170</v>
       </c>
       <c r="R27" t="n">
-        <v>6649820</v>
+        <v>6649811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3720,19 +3748,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3747,22 +3765,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122998889</v>
+        <v>122999168</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>5173</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3771,40 +3789,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3813,10 +3822,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712161</v>
+        <v>712092</v>
       </c>
       <c r="R28" t="n">
-        <v>6649804</v>
+        <v>6649793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3875,10 +3884,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122998873</v>
+        <v>122997583</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3887,40 +3896,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3929,13 +3929,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712170</v>
+        <v>712166</v>
       </c>
       <c r="R29" t="n">
-        <v>6649811</v>
+        <v>6649973</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123001398</v>
+        <v>123007916</v>
       </c>
       <c r="B31" t="n">
         <v>105463</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4157,14 +4157,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712451</v>
+        <v>712142</v>
       </c>
       <c r="R31" t="n">
-        <v>6649760</v>
+        <v>6649796</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122998128</v>
+        <v>123001398</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4235,25 +4235,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712162</v>
+        <v>712451</v>
       </c>
       <c r="R32" t="n">
-        <v>6649897</v>
+        <v>6649760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4336,6 +4336,3733 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123054338</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>712174</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6649978</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123054346</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>712166</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6649838</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123054339</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>712159</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6649889</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122999379</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110495</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>711874</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6649764</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123005529</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>712073</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6649811</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123008739</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>712097</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123054320</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Charlottenberg, V om, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>712566</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6649705</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123054344</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110495</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>712108</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6649847</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123054352</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>712040</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6649749</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123003505</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>712047</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6649756</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123001473</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78835</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>637</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>711936</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6649774</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123054347</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>712173</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6649820</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123054358</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78835</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>637</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>711929</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6649767</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123008545</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110495</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>712097</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123054353</v>
+      </c>
+      <c r="B47" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>712005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6649760</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123054351</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>712043</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6649750</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123054332</v>
+      </c>
+      <c r="B49" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Charlottenberg, V om, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>712595</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6649701</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123054333</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Charlottenberg, V om, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>712580</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6649752</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123054337</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>712185</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6649993</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123012181</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>712565</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6649707</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123007899</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>712152</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6649789</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123011961</v>
+      </c>
+      <c r="B54" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>712591</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6649698</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123054342</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>712108</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123008808</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92258</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>712097</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123002544</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78835</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>637</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>711951</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6649783</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123054334</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Charlottenberg, V om, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>712597</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6649817</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123054345</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>712165</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6649838</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123011797</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>712581</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6649757</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123054336</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>712184</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6649994</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123002458</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78835</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>637</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>711934</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6649764</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123003233</v>
+      </c>
+      <c r="B63" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>712047</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6649756</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123054371</v>
+      </c>
+      <c r="B64" t="n">
+        <v>100623</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>711866</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6649752</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123002982</v>
+      </c>
+      <c r="B65" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>712017</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6649759</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -3991,10 +3991,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123009388</v>
+        <v>123007916</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712196</v>
+        <v>712142</v>
       </c>
       <c r="R30" t="n">
-        <v>6650006</v>
+        <v>6649796</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123007916</v>
+        <v>123009388</v>
       </c>
       <c r="B31" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4119,35 +4119,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712142</v>
+        <v>712196</v>
       </c>
       <c r="R31" t="n">
-        <v>6649796</v>
+        <v>6650006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123011961</v>
+        <v>123054342</v>
       </c>
       <c r="B54" t="n">
-        <v>105463</v>
+        <v>100623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6728,43 +6728,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712591</v>
+        <v>712108</v>
       </c>
       <c r="R54" t="n">
-        <v>6649698</v>
+        <v>6649846</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6808,25 +6804,30 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054342</v>
+        <v>123011961</v>
       </c>
       <c r="B55" t="n">
-        <v>100623</v>
+        <v>105463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6839,39 +6840,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712108</v>
+        <v>712591</v>
       </c>
       <c r="R55" t="n">
-        <v>6649846</v>
+        <v>6649698</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6915,20 +6920,15 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123002767</v>
+        <v>122997583</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,40 +1574,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1616,13 +1607,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712151</v>
+        <v>712166</v>
       </c>
       <c r="R9" t="n">
-        <v>6649915</v>
+        <v>6649973</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1678,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123000056</v>
+        <v>122997739</v>
       </c>
       <c r="B10" t="n">
-        <v>97311</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,38 +1681,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712308</v>
+        <v>712167</v>
       </c>
       <c r="R10" t="n">
-        <v>6649706</v>
+        <v>6649980</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,9 +1751,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,22 +1778,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008249</v>
+        <v>122999323</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,21 +1833,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712159</v>
+        <v>712171</v>
       </c>
       <c r="R11" t="n">
-        <v>6649832</v>
+        <v>6649822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,9 +1872,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,22 +1899,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122997556</v>
+        <v>123008181</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,31 +1923,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1941,10 +1960,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712163</v>
+        <v>712179</v>
       </c>
       <c r="R12" t="n">
-        <v>6649978</v>
+        <v>6649820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,9 +1993,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,22 +2020,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122999077</v>
+        <v>123009388</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,7 +2067,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,18 +2080,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712127</v>
+        <v>712196</v>
       </c>
       <c r="R13" t="n">
-        <v>6649778</v>
+        <v>6650006</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2103,7 +2130,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2122,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122998889</v>
+        <v>122998042</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,7 +2183,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2170,16 +2196,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712161</v>
+        <v>712150</v>
       </c>
       <c r="R14" t="n">
-        <v>6649804</v>
+        <v>6649898</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2220,6 +2248,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2238,10 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122998128</v>
+        <v>122997028</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2273,7 +2302,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2281,21 +2310,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712162</v>
+        <v>712198</v>
       </c>
       <c r="R15" t="n">
-        <v>6649897</v>
+        <v>6650001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2325,9 +2349,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,22 +2376,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122997739</v>
+        <v>123000056</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>97319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,47 +2400,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712167</v>
+        <v>712308</v>
       </c>
       <c r="R16" t="n">
-        <v>6649980</v>
+        <v>6649706</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2436,19 +2461,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,22 +2478,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122998042</v>
+        <v>123001398</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2487,35 +2502,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2523,18 +2538,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712150</v>
+        <v>712451</v>
       </c>
       <c r="R17" t="n">
-        <v>6649898</v>
+        <v>6649760</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2575,7 +2588,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2594,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122997028</v>
+        <v>122998729</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2629,7 +2641,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2637,16 +2649,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712198</v>
+        <v>712176</v>
       </c>
       <c r="R18" t="n">
-        <v>6650001</v>
+        <v>6649818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2676,49 +2695,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122999323</v>
+        <v>122998128</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2750,7 +2760,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2758,16 +2768,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712171</v>
+        <v>712162</v>
       </c>
       <c r="R19" t="n">
-        <v>6649822</v>
+        <v>6649897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2797,19 +2812,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,22 +2829,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122996823</v>
+        <v>122998873</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,7 +2876,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2884,18 +2889,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712187</v>
+        <v>712170</v>
       </c>
       <c r="R20" t="n">
-        <v>6650002</v>
+        <v>6649811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2936,7 +2939,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2955,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123008181</v>
+        <v>123009298</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2990,7 +2992,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3004,10 +3006,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712179</v>
+        <v>712186</v>
       </c>
       <c r="R21" t="n">
-        <v>6649820</v>
+        <v>6649996</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,7 +3041,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3049,7 +3051,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3076,10 +3078,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123000064</v>
+        <v>122997556</v>
       </c>
       <c r="B22" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3088,20 +3090,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3112,7 +3114,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3121,10 +3123,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712318</v>
+        <v>712163</v>
       </c>
       <c r="R22" t="n">
-        <v>6649737</v>
+        <v>6649978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,19 +3156,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,22 +3173,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123009298</v>
+        <v>123008249</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3228,7 +3220,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3236,16 +3228,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712186</v>
+        <v>712159</v>
       </c>
       <c r="R23" t="n">
-        <v>6649996</v>
+        <v>6649832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3275,19 +3272,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3302,22 +3289,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122998729</v>
+        <v>122999168</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3326,54 +3313,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712176</v>
+        <v>712092</v>
       </c>
       <c r="R24" t="n">
-        <v>6649818</v>
+        <v>6649793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3414,7 +3390,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3433,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123008031</v>
+        <v>122998889</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3468,7 +3443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3476,16 +3451,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712167</v>
+        <v>712161</v>
       </c>
       <c r="R25" t="n">
-        <v>6649816</v>
+        <v>6649804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,19 +3495,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3542,22 +3512,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123000100</v>
+        <v>123000064</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>57848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3570,27 +3540,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3599,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712304</v>
+        <v>712318</v>
       </c>
       <c r="R26" t="n">
-        <v>6649724</v>
+        <v>6649737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3632,9 +3602,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3649,22 +3629,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122998873</v>
+        <v>123002767</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3696,7 +3676,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3715,10 +3695,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712170</v>
+        <v>712151</v>
       </c>
       <c r="R27" t="n">
-        <v>6649811</v>
+        <v>6649915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3777,10 +3757,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122999168</v>
+        <v>123000100</v>
       </c>
       <c r="B28" t="n">
-        <v>5173</v>
+        <v>4776</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3793,21 +3773,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3822,10 +3802,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712092</v>
+        <v>712304</v>
       </c>
       <c r="R28" t="n">
-        <v>6649793</v>
+        <v>6649724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3884,10 +3864,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122997583</v>
+        <v>122999077</v>
       </c>
       <c r="B29" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3896,46 +3876,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712166</v>
+        <v>712127</v>
       </c>
       <c r="R29" t="n">
-        <v>6649973</v>
+        <v>6649778</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3973,6 +3964,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3991,10 +3983,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123007916</v>
+        <v>123008031</v>
       </c>
       <c r="B30" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,40 +3995,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4045,10 +4032,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712142</v>
+        <v>712167</v>
       </c>
       <c r="R30" t="n">
-        <v>6649796</v>
+        <v>6649816</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4078,9 +4065,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4095,22 +4092,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123009388</v>
+        <v>122996823</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4142,7 +4139,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4155,16 +4152,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712196</v>
+        <v>712187</v>
       </c>
       <c r="R31" t="n">
-        <v>6650006</v>
+        <v>6650002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4205,6 +4204,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123001398</v>
+        <v>123007916</v>
       </c>
       <c r="B32" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712451</v>
+        <v>712142</v>
       </c>
       <c r="R32" t="n">
-        <v>6649760</v>
+        <v>6649796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123054338</v>
+        <v>123002544</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>78835</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4355,42 +4355,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712174</v>
+        <v>711951</v>
       </c>
       <c r="R33" t="n">
-        <v>6649978</v>
+        <v>6649783</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4430,31 +4434,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054346</v>
+        <v>123011797</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4484,25 +4483,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712166</v>
+        <v>712581</v>
       </c>
       <c r="R34" t="n">
-        <v>6649838</v>
+        <v>6649757</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4542,31 +4545,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054339</v>
+        <v>123054353</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4575,25 +4573,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4608,10 +4606,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712159</v>
+        <v>712005</v>
       </c>
       <c r="R35" t="n">
-        <v>6649889</v>
+        <v>6649760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4644,11 +4642,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4673,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122999379</v>
+        <v>123002982</v>
       </c>
       <c r="B36" t="n">
-        <v>110495</v>
+        <v>105471</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4696,37 +4689,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711874</v>
+        <v>712017</v>
       </c>
       <c r="R36" t="n">
-        <v>6649764</v>
+        <v>6649759</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4782,10 +4784,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123005529</v>
+        <v>123054336</v>
       </c>
       <c r="B37" t="n">
-        <v>97311</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,41 +4796,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712073</v>
+        <v>712184</v>
       </c>
       <c r="R37" t="n">
-        <v>6649811</v>
+        <v>6649994</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4868,26 +4884,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123008739</v>
+        <v>123054338</v>
       </c>
       <c r="B38" t="n">
-        <v>100623</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,41 +4917,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712097</v>
+        <v>712174</v>
       </c>
       <c r="R38" t="n">
-        <v>6649846</v>
+        <v>6649978</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4970,26 +4996,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054320</v>
+        <v>123054344</v>
       </c>
       <c r="B39" t="n">
-        <v>97311</v>
+        <v>110503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5002,16 +5033,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5020,16 +5051,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712566</v>
+        <v>712108</v>
       </c>
       <c r="R39" t="n">
-        <v>6649705</v>
+        <v>6649847</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5086,17 +5122,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054344</v>
+        <v>123054320</v>
       </c>
       <c r="B40" t="n">
-        <v>110495</v>
+        <v>97319</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5109,16 +5145,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5127,21 +5163,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712108</v>
+        <v>712566</v>
       </c>
       <c r="R40" t="n">
-        <v>6649847</v>
+        <v>6649705</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5198,17 +5229,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123054352</v>
+        <v>123003467</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5238,34 +5269,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712040</v>
+        <v>712047</v>
       </c>
       <c r="R41" t="n">
-        <v>6649749</v>
+        <v>6649756</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5305,31 +5322,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123003505</v>
+        <v>123054332</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,50 +5350,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712047</v>
+        <v>712595</v>
       </c>
       <c r="R42" t="n">
-        <v>6649756</v>
+        <v>6649701</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5421,26 +5429,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123001473</v>
+        <v>123054337</v>
       </c>
       <c r="B43" t="n">
-        <v>78835</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5453,45 +5466,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711936</v>
+        <v>712185</v>
       </c>
       <c r="R43" t="n">
-        <v>6649774</v>
+        <v>6649993</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5526,70 +5533,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054347</v>
+        <v>123054346</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5619,16 +5595,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5640,10 +5607,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712173</v>
+        <v>712166</v>
       </c>
       <c r="R44" t="n">
-        <v>6649820</v>
+        <v>6649838</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5707,10 +5674,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123054358</v>
+        <v>123054333</v>
       </c>
       <c r="B45" t="n">
-        <v>78835</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5723,43 +5690,48 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>711929</v>
+        <v>712580</v>
       </c>
       <c r="R45" t="n">
-        <v>6649767</v>
+        <v>6649752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5794,11 +5766,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5821,17 +5788,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123008545</v>
+        <v>123054342</v>
       </c>
       <c r="B46" t="n">
-        <v>110495</v>
+        <v>100631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5844,37 +5811,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712097</v>
+        <v>712108</v>
       </c>
       <c r="R46" t="n">
         <v>6649846</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5914,26 +5886,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123054353</v>
+        <v>123008739</v>
       </c>
       <c r="B47" t="n">
-        <v>105463</v>
+        <v>100631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5946,42 +5923,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712005</v>
+        <v>712097</v>
       </c>
       <c r="R47" t="n">
-        <v>6649760</v>
+        <v>6649846</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6021,31 +5993,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054351</v>
+        <v>123054334</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6054,52 +6021,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712043</v>
+        <v>712597</v>
       </c>
       <c r="R48" t="n">
-        <v>6649750</v>
+        <v>6649817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6134,6 +6087,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6156,17 +6114,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054332</v>
+        <v>123011961</v>
       </c>
       <c r="B49" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6196,22 +6154,26 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712595</v>
+        <v>712591</v>
       </c>
       <c r="R49" t="n">
-        <v>6649701</v>
+        <v>6649698</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6255,30 +6217,25 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123054333</v>
+        <v>123054345</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6310,7 +6267,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6325,14 +6282,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712580</v>
+        <v>712165</v>
       </c>
       <c r="R50" t="n">
-        <v>6649752</v>
+        <v>6649838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6389,17 +6346,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054337</v>
+        <v>123054352</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6429,7 +6386,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6441,10 +6407,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712185</v>
+        <v>712040</v>
       </c>
       <c r="R51" t="n">
-        <v>6649993</v>
+        <v>6649749</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6508,10 +6474,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123012181</v>
+        <v>123008808</v>
       </c>
       <c r="B52" t="n">
-        <v>97311</v>
+        <v>92266</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6524,37 +6490,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712565</v>
+        <v>712097</v>
       </c>
       <c r="R52" t="n">
-        <v>6649707</v>
+        <v>6649846</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6610,10 +6576,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123007899</v>
+        <v>122999379</v>
       </c>
       <c r="B53" t="n">
-        <v>97311</v>
+        <v>110503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6626,16 +6592,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6650,13 +6616,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712152</v>
+        <v>711874</v>
       </c>
       <c r="R53" t="n">
-        <v>6649789</v>
+        <v>6649764</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6712,10 +6678,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123054342</v>
+        <v>123008545</v>
       </c>
       <c r="B54" t="n">
-        <v>100623</v>
+        <v>110503</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6728,42 +6694,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712108</v>
+        <v>712097</v>
       </c>
       <c r="R54" t="n">
         <v>6649846</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6803,31 +6764,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123011961</v>
+        <v>123012181</v>
       </c>
       <c r="B55" t="n">
-        <v>105463</v>
+        <v>97319</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6840,43 +6796,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712591</v>
+        <v>712565</v>
       </c>
       <c r="R55" t="n">
-        <v>6649698</v>
+        <v>6649707</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6935,10 +6882,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123008808</v>
+        <v>123002458</v>
       </c>
       <c r="B56" t="n">
-        <v>92258</v>
+        <v>78835</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6947,41 +6894,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>637</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712097</v>
+        <v>711934</v>
       </c>
       <c r="R56" t="n">
-        <v>6649846</v>
+        <v>6649764</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7013,12 +6971,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7030,14 +6994,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123002544</v>
+        <v>123001473</v>
       </c>
       <c r="B57" t="n">
         <v>78835</v>
@@ -7072,7 +7036,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7080,19 +7044,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>711951</v>
+        <v>711936</v>
       </c>
       <c r="R57" t="n">
-        <v>6649783</v>
+        <v>6649774</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7124,14 +7090,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7148,10 +7150,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054334</v>
+        <v>123007899</v>
       </c>
       <c r="B58" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7164,37 +7166,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712597</v>
+        <v>712152</v>
       </c>
       <c r="R58" t="n">
-        <v>6649817</v>
+        <v>6649789</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7226,11 +7228,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7239,31 +7236,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054345</v>
+        <v>123054351</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7295,7 +7287,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7314,10 +7306,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712165</v>
+        <v>712043</v>
       </c>
       <c r="R59" t="n">
-        <v>6649838</v>
+        <v>6649750</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7381,10 +7373,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123011797</v>
+        <v>123003233</v>
       </c>
       <c r="B60" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7393,30 +7385,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7426,14 +7418,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712581</v>
+        <v>712047</v>
       </c>
       <c r="R60" t="n">
-        <v>6649757</v>
+        <v>6649756</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7492,10 +7484,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054336</v>
+        <v>123054339</v>
       </c>
       <c r="B61" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7525,16 +7517,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7546,10 +7529,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712184</v>
+        <v>712159</v>
       </c>
       <c r="R61" t="n">
-        <v>6649994</v>
+        <v>6649889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7582,6 +7565,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7613,10 +7601,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123002458</v>
+        <v>123054347</v>
       </c>
       <c r="B62" t="n">
-        <v>78835</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7629,48 +7617,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>711934</v>
+        <v>712173</v>
       </c>
       <c r="R62" t="n">
-        <v>6649764</v>
+        <v>6649820</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7702,40 +7693,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123003233</v>
+        <v>123054358</v>
       </c>
       <c r="B63" t="n">
-        <v>105463</v>
+        <v>78835</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7744,50 +7734,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>637</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712047</v>
+        <v>711929</v>
       </c>
       <c r="R63" t="n">
-        <v>6649756</v>
+        <v>6649767</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7819,6 +7809,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7827,16 +7822,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
         <v>123054371</v>
       </c>
       <c r="B64" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123002982</v>
+        <v>123005529</v>
       </c>
       <c r="B65" t="n">
-        <v>105463</v>
+        <v>97319</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7971,43 +7971,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712017</v>
+        <v>712073</v>
       </c>
       <c r="R65" t="n">
-        <v>6649759</v>
+        <v>6649811</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122998042</v>
+        <v>123000056</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,54 +2160,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712150</v>
+        <v>712308</v>
       </c>
       <c r="R14" t="n">
-        <v>6649898</v>
+        <v>6649706</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2248,7 +2232,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122997028</v>
+        <v>123001398</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2279,47 +2262,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712198</v>
+        <v>712451</v>
       </c>
       <c r="R15" t="n">
-        <v>6650001</v>
+        <v>6649760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2349,19 +2337,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,22 +2354,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123000056</v>
+        <v>122998042</v>
       </c>
       <c r="B16" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,38 +2378,54 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712308</v>
+        <v>712150</v>
       </c>
       <c r="R16" t="n">
-        <v>6649706</v>
+        <v>6649898</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,6 +2466,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2490,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123001398</v>
+        <v>122997028</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2502,52 +2497,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712451</v>
+        <v>712198</v>
       </c>
       <c r="R17" t="n">
-        <v>6649760</v>
+        <v>6650001</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,9 +2567,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,12 +2594,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122998873</v>
+        <v>122997556</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,40 +2853,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2895,10 +2886,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712170</v>
+        <v>712163</v>
       </c>
       <c r="R20" t="n">
-        <v>6649811</v>
+        <v>6649978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2957,7 +2948,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123009298</v>
+        <v>122998873</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2992,7 +2983,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3000,16 +2991,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712186</v>
+        <v>712170</v>
       </c>
       <c r="R21" t="n">
-        <v>6649996</v>
+        <v>6649811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,19 +3035,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,22 +3052,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122997556</v>
+        <v>123009298</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3090,31 +3076,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3123,10 +3113,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712163</v>
+        <v>712186</v>
       </c>
       <c r="R22" t="n">
-        <v>6649978</v>
+        <v>6649996</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,9 +3146,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123001473</v>
+        <v>123007899</v>
       </c>
       <c r="B57" t="n">
-        <v>78835</v>
+        <v>97319</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7013,52 +7013,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>637</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>711936</v>
+        <v>712152</v>
       </c>
       <c r="R57" t="n">
-        <v>6649774</v>
+        <v>6649789</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7090,50 +7079,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7143,17 +7096,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123007899</v>
+        <v>123054351</v>
       </c>
       <c r="B58" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7162,41 +7115,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712152</v>
+        <v>712043</v>
       </c>
       <c r="R58" t="n">
-        <v>6649789</v>
+        <v>6649750</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7236,26 +7203,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054351</v>
+        <v>123001473</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>78835</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7268,48 +7240,45 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712043</v>
+        <v>711936</v>
       </c>
       <c r="R59" t="n">
-        <v>6649750</v>
+        <v>6649774</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7344,29 +7313,60 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122997583</v>
+        <v>122999077</v>
       </c>
       <c r="B9" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,46 +1574,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712166</v>
+        <v>712127</v>
       </c>
       <c r="R9" t="n">
-        <v>6649973</v>
+        <v>6649778</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1651,6 +1662,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122997739</v>
+        <v>123000100</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>4776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,35 +1693,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1718,10 +1726,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712167</v>
+        <v>712304</v>
       </c>
       <c r="R10" t="n">
-        <v>6649980</v>
+        <v>6649724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,19 +1759,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,19 +1776,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122999323</v>
+        <v>122997028</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1825,7 +1823,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1839,10 +1837,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712171</v>
+        <v>712198</v>
       </c>
       <c r="R11" t="n">
-        <v>6649822</v>
+        <v>6650001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1872,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1884,7 +1882,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,7 +1909,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008181</v>
+        <v>123009298</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1946,7 +1944,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1960,10 +1958,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712179</v>
+        <v>712186</v>
       </c>
       <c r="R12" t="n">
-        <v>6649820</v>
+        <v>6649996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1995,7 +1993,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2005,7 +2003,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123009388</v>
+        <v>123000056</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,52 +2042,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712196</v>
+        <v>712308</v>
       </c>
       <c r="R13" t="n">
-        <v>6650006</v>
+        <v>6649706</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2148,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123000056</v>
+        <v>122999323</v>
       </c>
       <c r="B14" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,38 +2144,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712308</v>
+        <v>712171</v>
       </c>
       <c r="R14" t="n">
-        <v>6649706</v>
+        <v>6649822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2221,9 +2214,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,22 +2241,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123001398</v>
+        <v>122997739</v>
       </c>
       <c r="B15" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,52 +2265,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712451</v>
+        <v>712167</v>
       </c>
       <c r="R15" t="n">
-        <v>6649760</v>
+        <v>6649980</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,9 +2335,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,22 +2362,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122998042</v>
+        <v>122997556</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,54 +2386,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712150</v>
+        <v>712163</v>
       </c>
       <c r="R16" t="n">
-        <v>6649898</v>
+        <v>6649978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2466,7 +2463,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2481,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122997028</v>
+        <v>123008181</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2520,7 +2516,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2534,10 +2530,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712198</v>
+        <v>712179</v>
       </c>
       <c r="R17" t="n">
-        <v>6650001</v>
+        <v>6649820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2575,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,7 +2595,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2725,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998128</v>
+        <v>122999168</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,40 +2733,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2779,10 +2766,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712162</v>
+        <v>712092</v>
       </c>
       <c r="R19" t="n">
-        <v>6649897</v>
+        <v>6649793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,10 +2828,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122997556</v>
+        <v>122996823</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,43 +2840,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712163</v>
+        <v>712187</v>
       </c>
       <c r="R20" t="n">
-        <v>6649978</v>
+        <v>6650002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,6 +2928,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2948,7 +2947,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122998873</v>
+        <v>122998128</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2983,7 +2982,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3002,10 +3001,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712170</v>
+        <v>712162</v>
       </c>
       <c r="R21" t="n">
-        <v>6649811</v>
+        <v>6649897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3064,10 +3063,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123009298</v>
+        <v>123007916</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3076,35 +3075,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3113,10 +3117,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712186</v>
+        <v>712142</v>
       </c>
       <c r="R22" t="n">
-        <v>6649996</v>
+        <v>6649796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,19 +3150,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,12 +3167,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3301,10 +3295,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122999168</v>
+        <v>122998889</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3313,31 +3307,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3346,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712092</v>
+        <v>712161</v>
       </c>
       <c r="R24" t="n">
-        <v>6649793</v>
+        <v>6649804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3408,7 +3411,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122998889</v>
+        <v>123008031</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3443,7 +3446,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3451,21 +3454,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712161</v>
+        <v>712167</v>
       </c>
       <c r="R25" t="n">
-        <v>6649804</v>
+        <v>6649816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3495,9 +3493,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,22 +3520,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123000064</v>
+        <v>122998873</v>
       </c>
       <c r="B26" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,31 +3544,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3569,10 +3586,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712318</v>
+        <v>712170</v>
       </c>
       <c r="R26" t="n">
-        <v>6649737</v>
+        <v>6649811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3602,19 +3619,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,22 +3636,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123002767</v>
+        <v>122997583</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3653,40 +3660,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3695,13 +3693,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712151</v>
+        <v>712166</v>
       </c>
       <c r="R27" t="n">
-        <v>6649915</v>
+        <v>6649973</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3757,10 +3755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123000100</v>
+        <v>123009388</v>
       </c>
       <c r="B28" t="n">
-        <v>4776</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3769,31 +3767,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3802,10 +3809,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712304</v>
+        <v>712196</v>
       </c>
       <c r="R28" t="n">
-        <v>6649724</v>
+        <v>6650006</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3864,7 +3871,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122999077</v>
+        <v>122998042</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3899,7 +3906,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3916,14 +3923,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712127</v>
+        <v>712150</v>
       </c>
       <c r="R29" t="n">
-        <v>6649778</v>
+        <v>6649898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3983,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123008031</v>
+        <v>123000064</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,35 +4002,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712167</v>
+        <v>712318</v>
       </c>
       <c r="R30" t="n">
-        <v>6649816</v>
+        <v>6649737</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4067,7 +4070,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,7 +4080,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,14 +4100,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122996823</v>
+        <v>123002767</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4139,7 +4142,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4152,18 +4155,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712187</v>
+        <v>712151</v>
       </c>
       <c r="R31" t="n">
-        <v>6650002</v>
+        <v>6649915</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4204,7 +4205,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123007916</v>
+        <v>123001398</v>
       </c>
       <c r="B32" t="n">
         <v>105471</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712142</v>
+        <v>712451</v>
       </c>
       <c r="R32" t="n">
-        <v>6649796</v>
+        <v>6649760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123002544</v>
+        <v>123002982</v>
       </c>
       <c r="B33" t="n">
-        <v>78835</v>
+        <v>105471</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>637</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711951</v>
+        <v>712017</v>
       </c>
       <c r="R33" t="n">
-        <v>6649783</v>
+        <v>6649759</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4443,14 +4443,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123011797</v>
+        <v>123054345</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4485,27 +4485,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712581</v>
+        <v>712165</v>
       </c>
       <c r="R34" t="n">
-        <v>6649757</v>
+        <v>6649838</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4545,26 +4550,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054353</v>
+        <v>123054333</v>
       </c>
       <c r="B35" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4573,28 +4583,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4602,14 +4621,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712005</v>
+        <v>712580</v>
       </c>
       <c r="R35" t="n">
-        <v>6649760</v>
+        <v>6649752</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4666,17 +4685,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123002982</v>
+        <v>123008545</v>
       </c>
       <c r="B36" t="n">
-        <v>105471</v>
+        <v>110503</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4689,43 +4708,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712017</v>
+        <v>712097</v>
       </c>
       <c r="R36" t="n">
-        <v>6649759</v>
+        <v>6649846</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4784,10 +4794,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054336</v>
+        <v>123054358</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4800,36 +4810,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4838,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712184</v>
+        <v>711929</v>
       </c>
       <c r="R37" t="n">
-        <v>6649994</v>
+        <v>6649767</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4874,6 +4879,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5017,10 +5027,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054344</v>
+        <v>123054351</v>
       </c>
       <c r="B39" t="n">
-        <v>110503</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5029,28 +5039,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5062,10 +5081,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712108</v>
+        <v>712043</v>
       </c>
       <c r="R39" t="n">
-        <v>6649847</v>
+        <v>6649750</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5129,10 +5148,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054320</v>
+        <v>123054339</v>
       </c>
       <c r="B40" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5141,38 +5160,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712566</v>
+        <v>712159</v>
       </c>
       <c r="R40" t="n">
-        <v>6649705</v>
+        <v>6649889</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5207,6 +5231,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5229,17 +5258,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123003467</v>
+        <v>123003233</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5248,28 +5277,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
@@ -5338,10 +5376,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054332</v>
+        <v>123012181</v>
       </c>
       <c r="B42" t="n">
-        <v>105471</v>
+        <v>97319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5354,39 +5392,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712595</v>
+        <v>712565</v>
       </c>
       <c r="R42" t="n">
-        <v>6649701</v>
+        <v>6649707</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5430,30 +5463,25 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054337</v>
+        <v>123054320</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5462,43 +5490,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712185</v>
+        <v>712566</v>
       </c>
       <c r="R43" t="n">
-        <v>6649993</v>
+        <v>6649705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5555,14 +5578,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054346</v>
+        <v>123054352</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5595,7 +5618,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5607,10 +5639,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712166</v>
+        <v>712040</v>
       </c>
       <c r="R44" t="n">
-        <v>6649838</v>
+        <v>6649749</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5674,7 +5706,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123054333</v>
+        <v>123003505</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5709,7 +5741,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5717,24 +5749,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712580</v>
+        <v>712047</v>
       </c>
       <c r="R45" t="n">
-        <v>6649752</v>
+        <v>6649756</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5774,31 +5801,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123054342</v>
+        <v>123011797</v>
       </c>
       <c r="B46" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5807,46 +5829,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712108</v>
+        <v>712581</v>
       </c>
       <c r="R46" t="n">
-        <v>6649846</v>
+        <v>6649757</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5886,31 +5912,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123008739</v>
+        <v>123011961</v>
       </c>
       <c r="B47" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5923,37 +5944,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712097</v>
+        <v>712591</v>
       </c>
       <c r="R47" t="n">
-        <v>6649846</v>
+        <v>6649698</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6009,10 +6039,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054334</v>
+        <v>123054337</v>
       </c>
       <c r="B48" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6021,38 +6051,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712597</v>
+        <v>712185</v>
       </c>
       <c r="R48" t="n">
-        <v>6649817</v>
+        <v>6649993</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6087,11 +6122,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6114,17 +6144,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123011961</v>
+        <v>123054336</v>
       </c>
       <c r="B49" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6133,47 +6163,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712591</v>
+        <v>712184</v>
       </c>
       <c r="R49" t="n">
-        <v>6649698</v>
+        <v>6649994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6217,25 +6252,30 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123054345</v>
+        <v>123008739</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6244,55 +6284,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712165</v>
+        <v>712097</v>
       </c>
       <c r="R50" t="n">
-        <v>6649838</v>
+        <v>6649846</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6332,31 +6358,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054352</v>
+        <v>123002458</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6369,51 +6390,48 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712040</v>
+        <v>711934</v>
       </c>
       <c r="R51" t="n">
-        <v>6649749</v>
+        <v>6649764</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6445,39 +6463,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123008808</v>
+        <v>123054353</v>
       </c>
       <c r="B52" t="n">
-        <v>92266</v>
+        <v>105471</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6490,37 +6509,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712097</v>
+        <v>712005</v>
       </c>
       <c r="R52" t="n">
-        <v>6649846</v>
+        <v>6649760</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6560,26 +6584,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122999379</v>
+        <v>123002544</v>
       </c>
       <c r="B53" t="n">
-        <v>110503</v>
+        <v>78833</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6588,41 +6617,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711874</v>
+        <v>711951</v>
       </c>
       <c r="R53" t="n">
-        <v>6649764</v>
+        <v>6649783</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6671,14 +6709,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123008545</v>
+        <v>122999379</v>
       </c>
       <c r="B54" t="n">
         <v>110503</v>
@@ -6718,13 +6756,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712097</v>
+        <v>711874</v>
       </c>
       <c r="R54" t="n">
-        <v>6649846</v>
+        <v>6649764</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6780,10 +6818,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123012181</v>
+        <v>123054332</v>
       </c>
       <c r="B55" t="n">
-        <v>97319</v>
+        <v>105471</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6796,34 +6834,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712565</v>
+        <v>712595</v>
       </c>
       <c r="R55" t="n">
-        <v>6649707</v>
+        <v>6649701</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6867,25 +6910,30 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123002458</v>
+        <v>123054347</v>
       </c>
       <c r="B56" t="n">
-        <v>78835</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6898,48 +6946,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>711934</v>
+        <v>712173</v>
       </c>
       <c r="R56" t="n">
-        <v>6649764</v>
+        <v>6649820</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6971,30 +7022,29 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7103,10 +7153,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054351</v>
+        <v>123054342</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7115,37 +7165,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7157,10 +7198,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712043</v>
+        <v>712108</v>
       </c>
       <c r="R58" t="n">
-        <v>6649750</v>
+        <v>6649846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7224,10 +7265,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123001473</v>
+        <v>123054344</v>
       </c>
       <c r="B59" t="n">
-        <v>78835</v>
+        <v>110503</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7236,49 +7277,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>637</v>
+        <v>219711</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>711936</v>
+        <v>712108</v>
       </c>
       <c r="R59" t="n">
-        <v>6649774</v>
+        <v>6649847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7313,70 +7348,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123003233</v>
+        <v>123008808</v>
       </c>
       <c r="B60" t="n">
-        <v>105471</v>
+        <v>92266</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7389,43 +7393,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712047</v>
+        <v>712097</v>
       </c>
       <c r="R60" t="n">
-        <v>6649756</v>
+        <v>6649846</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7484,10 +7479,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054339</v>
+        <v>123054371</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7496,25 +7491,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7529,10 +7524,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712159</v>
+        <v>711866</v>
       </c>
       <c r="R61" t="n">
-        <v>6649889</v>
+        <v>6649752</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7565,11 +7560,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7601,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054347</v>
+        <v>123005529</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7613,55 +7603,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712173</v>
+        <v>712073</v>
       </c>
       <c r="R62" t="n">
-        <v>6649820</v>
+        <v>6649811</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7701,31 +7677,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054358</v>
+        <v>123054346</v>
       </c>
       <c r="B63" t="n">
-        <v>78835</v>
+        <v>98365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7738,31 +7709,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7771,10 +7738,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>711929</v>
+        <v>712166</v>
       </c>
       <c r="R63" t="n">
-        <v>6649767</v>
+        <v>6649838</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7807,11 +7774,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7843,10 +7805,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054371</v>
+        <v>123001473</v>
       </c>
       <c r="B64" t="n">
-        <v>100631</v>
+        <v>78833</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7855,43 +7817,49 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>637</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>711866</v>
+        <v>711936</v>
       </c>
       <c r="R64" t="n">
-        <v>6649752</v>
+        <v>6649774</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7926,39 +7894,70 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123005529</v>
+        <v>123054334</v>
       </c>
       <c r="B65" t="n">
-        <v>97319</v>
+        <v>57848</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7971,37 +7970,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712073</v>
+        <v>712597</v>
       </c>
       <c r="R65" t="n">
-        <v>6649811</v>
+        <v>6649817</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8033,6 +8032,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8041,16 +8045,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2602,10 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122998729</v>
+        <v>122999168</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,54 +2614,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712176</v>
+        <v>712092</v>
       </c>
       <c r="R18" t="n">
-        <v>6649818</v>
+        <v>6649793</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2702,7 +2691,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122999168</v>
+        <v>122998729</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,43 +2721,54 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712092</v>
+        <v>712176</v>
       </c>
       <c r="R19" t="n">
-        <v>6649793</v>
+        <v>6649818</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2810,6 +2809,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054358</v>
+        <v>123054338</v>
       </c>
       <c r="B37" t="n">
-        <v>78833</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4810,31 +4810,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4843,10 +4839,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711929</v>
+        <v>712174</v>
       </c>
       <c r="R37" t="n">
-        <v>6649767</v>
+        <v>6649978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4879,11 +4875,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4915,7 +4906,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054338</v>
+        <v>123054351</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4948,7 +4939,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712174</v>
+        <v>712043</v>
       </c>
       <c r="R38" t="n">
-        <v>6649978</v>
+        <v>6649750</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054351</v>
+        <v>123054339</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5060,16 +5060,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5081,10 +5072,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712043</v>
+        <v>712159</v>
       </c>
       <c r="R39" t="n">
-        <v>6649750</v>
+        <v>6649889</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5117,6 +5108,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5148,10 +5144,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054339</v>
+        <v>123054358</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,27 +5160,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712159</v>
+        <v>711929</v>
       </c>
       <c r="R40" t="n">
-        <v>6649889</v>
+        <v>6649767</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ymnig.</t>
+          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -7377,10 +7377,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123008808</v>
+        <v>123054371</v>
       </c>
       <c r="B60" t="n">
-        <v>92266</v>
+        <v>100631</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7393,37 +7393,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712097</v>
+        <v>711866</v>
       </c>
       <c r="R60" t="n">
-        <v>6649846</v>
+        <v>6649752</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7463,26 +7468,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054371</v>
+        <v>123008808</v>
       </c>
       <c r="B61" t="n">
-        <v>100631</v>
+        <v>92266</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7495,42 +7505,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>711866</v>
+        <v>712097</v>
       </c>
       <c r="R61" t="n">
-        <v>6649752</v>
+        <v>6649846</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7570,21 +7575,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2602,10 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122999168</v>
+        <v>122998729</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2614,43 +2614,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712092</v>
+        <v>712176</v>
       </c>
       <c r="R18" t="n">
-        <v>6649793</v>
+        <v>6649818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,6 +2702,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2709,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998729</v>
+        <v>122999168</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,54 +2733,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712176</v>
+        <v>712092</v>
       </c>
       <c r="R19" t="n">
-        <v>6649818</v>
+        <v>6649793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2809,7 +2810,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123008031</v>
+        <v>122998873</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3454,16 +3454,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712167</v>
+        <v>712170</v>
       </c>
       <c r="R25" t="n">
-        <v>6649816</v>
+        <v>6649811</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3493,19 +3498,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,19 +3515,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998873</v>
+        <v>123008031</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3567,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3575,21 +3570,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712170</v>
+        <v>712167</v>
       </c>
       <c r="R26" t="n">
-        <v>6649811</v>
+        <v>6649816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3619,9 +3609,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,12 +3636,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054338</v>
+        <v>123054358</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4810,27 +4810,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4839,10 +4843,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712174</v>
+        <v>711929</v>
       </c>
       <c r="R37" t="n">
-        <v>6649978</v>
+        <v>6649767</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4875,6 +4879,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4906,7 +4915,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054351</v>
+        <v>123054338</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4939,16 +4948,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712043</v>
+        <v>712174</v>
       </c>
       <c r="R38" t="n">
-        <v>6649750</v>
+        <v>6649978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054339</v>
+        <v>123054351</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5060,7 +5060,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5072,10 +5081,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712159</v>
+        <v>712043</v>
       </c>
       <c r="R39" t="n">
-        <v>6649889</v>
+        <v>6649750</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5108,11 +5117,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5144,10 +5148,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054358</v>
+        <v>123054339</v>
       </c>
       <c r="B40" t="n">
-        <v>78833</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5160,31 +5164,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711929</v>
+        <v>712159</v>
       </c>
       <c r="R40" t="n">
-        <v>6649767</v>
+        <v>6649889</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -7265,10 +7265,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054344</v>
+        <v>123054371</v>
       </c>
       <c r="B59" t="n">
-        <v>110503</v>
+        <v>100631</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7281,21 +7281,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712108</v>
+        <v>711866</v>
       </c>
       <c r="R59" t="n">
-        <v>6649847</v>
+        <v>6649752</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054371</v>
+        <v>123054344</v>
       </c>
       <c r="B60" t="n">
-        <v>100631</v>
+        <v>110503</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7393,21 +7393,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>711866</v>
+        <v>712108</v>
       </c>
       <c r="R60" t="n">
-        <v>6649752</v>
+        <v>6649847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122999077</v>
+        <v>123009298</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,23 +1605,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712127</v>
+        <v>712186</v>
       </c>
       <c r="R9" t="n">
-        <v>6649778</v>
+        <v>6649996</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,40 +1644,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123000100</v>
+        <v>122997556</v>
       </c>
       <c r="B10" t="n">
-        <v>4776</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,31 +1695,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1726,10 +1728,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712304</v>
+        <v>712163</v>
       </c>
       <c r="R10" t="n">
-        <v>6649724</v>
+        <v>6649978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1788,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122997028</v>
+        <v>123000064</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,35 +1802,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1837,10 +1835,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712198</v>
+        <v>712318</v>
       </c>
       <c r="R11" t="n">
-        <v>6650001</v>
+        <v>6649737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,7 +1870,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1882,7 +1880,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,7 +1907,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123009298</v>
+        <v>123008181</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1944,7 +1942,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1958,10 +1956,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712186</v>
+        <v>712179</v>
       </c>
       <c r="R12" t="n">
-        <v>6649996</v>
+        <v>6649820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,7 +1991,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2003,7 +2001,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2030,10 +2028,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123000056</v>
+        <v>122998729</v>
       </c>
       <c r="B13" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,38 +2040,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712308</v>
+        <v>712176</v>
       </c>
       <c r="R13" t="n">
-        <v>6649706</v>
+        <v>6649818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2114,6 +2128,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2132,7 +2147,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122999323</v>
+        <v>122996823</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2167,7 +2182,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2175,16 +2190,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712171</v>
+        <v>712187</v>
       </c>
       <c r="R14" t="n">
-        <v>6649822</v>
+        <v>6650002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2214,46 +2236,37 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122997739</v>
+        <v>123002767</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2296,16 +2309,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712167</v>
+        <v>712151</v>
       </c>
       <c r="R15" t="n">
-        <v>6649980</v>
+        <v>6649915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,19 +2353,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,22 +2370,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122997556</v>
+        <v>123009388</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2386,31 +2394,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2419,10 +2436,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712163</v>
+        <v>712196</v>
       </c>
       <c r="R16" t="n">
-        <v>6649978</v>
+        <v>6650006</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2481,10 +2498,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008181</v>
+        <v>123001398</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,47 +2510,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712179</v>
+        <v>712451</v>
       </c>
       <c r="R17" t="n">
-        <v>6649820</v>
+        <v>6649760</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,19 +2585,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,19 +2602,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122998729</v>
+        <v>122999323</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2637,7 +2649,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2645,23 +2657,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712176</v>
+        <v>712171</v>
       </c>
       <c r="R18" t="n">
-        <v>6649818</v>
+        <v>6649822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,40 +2696,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122999168</v>
+        <v>122997028</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,31 +2747,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2766,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712092</v>
+        <v>712198</v>
       </c>
       <c r="R19" t="n">
-        <v>6649793</v>
+        <v>6650001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,9 +2817,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2816,22 +2844,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122996823</v>
+        <v>123007916</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,35 +2868,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2876,18 +2904,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712187</v>
+        <v>712142</v>
       </c>
       <c r="R20" t="n">
-        <v>6650002</v>
+        <v>6649796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,7 +2954,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2947,10 +2972,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122998128</v>
+        <v>122997583</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2959,40 +2984,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3001,13 +3017,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712162</v>
+        <v>712166</v>
       </c>
       <c r="R21" t="n">
-        <v>6649897</v>
+        <v>6649973</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3063,10 +3079,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123007916</v>
+        <v>123008249</v>
       </c>
       <c r="B22" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3075,35 +3091,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3117,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712142</v>
+        <v>712159</v>
       </c>
       <c r="R22" t="n">
-        <v>6649796</v>
+        <v>6649832</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3179,7 +3195,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123008249</v>
+        <v>123008031</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3214,7 +3230,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3222,21 +3238,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712159</v>
+        <v>712167</v>
       </c>
       <c r="R23" t="n">
-        <v>6649832</v>
+        <v>6649816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3266,9 +3277,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3283,19 +3304,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122998889</v>
+        <v>122997739</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3330,7 +3351,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3338,21 +3359,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712161</v>
+        <v>712167</v>
       </c>
       <c r="R24" t="n">
-        <v>6649804</v>
+        <v>6649980</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3382,9 +3398,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,19 +3425,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122998873</v>
+        <v>122998889</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3446,7 +3472,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3465,10 +3491,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712170</v>
+        <v>712161</v>
       </c>
       <c r="R25" t="n">
-        <v>6649811</v>
+        <v>6649804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3527,7 +3553,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123008031</v>
+        <v>122998128</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3562,7 +3588,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3570,16 +3596,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712167</v>
+        <v>712162</v>
       </c>
       <c r="R26" t="n">
-        <v>6649816</v>
+        <v>6649897</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3609,19 +3640,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,22 +3657,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122997583</v>
+        <v>122998042</v>
       </c>
       <c r="B27" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3660,46 +3681,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712166</v>
+        <v>712150</v>
       </c>
       <c r="R27" t="n">
-        <v>6649973</v>
+        <v>6649898</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3737,6 +3769,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3755,10 +3788,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123009388</v>
+        <v>123000100</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>4776</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3767,40 +3800,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3809,10 +3833,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712196</v>
+        <v>712304</v>
       </c>
       <c r="R28" t="n">
-        <v>6650006</v>
+        <v>6649724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3871,10 +3895,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122998042</v>
+        <v>122999168</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3883,54 +3907,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712150</v>
+        <v>712092</v>
       </c>
       <c r="R29" t="n">
-        <v>6649898</v>
+        <v>6649793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3971,7 +3984,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3990,10 +4002,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123000064</v>
+        <v>123000056</v>
       </c>
       <c r="B30" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4006,39 +4018,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712318</v>
+        <v>712308</v>
       </c>
       <c r="R30" t="n">
-        <v>6649737</v>
+        <v>6649706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4068,19 +4075,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4095,19 +4092,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123002767</v>
+        <v>122999077</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4142,7 +4139,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4155,16 +4152,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712151</v>
+        <v>712127</v>
       </c>
       <c r="R31" t="n">
-        <v>6649915</v>
+        <v>6649778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4205,6 +4204,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123001398</v>
+        <v>122998873</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4235,35 +4235,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712451</v>
+        <v>712170</v>
       </c>
       <c r="R32" t="n">
-        <v>6649760</v>
+        <v>6649811</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123002982</v>
+        <v>123054344</v>
       </c>
       <c r="B33" t="n">
-        <v>105471</v>
+        <v>110503</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4355,46 +4355,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712017</v>
+        <v>712108</v>
       </c>
       <c r="R33" t="n">
-        <v>6649759</v>
+        <v>6649847</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4434,26 +4430,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054345</v>
+        <v>123054353</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,37 +4463,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4504,10 +4496,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712165</v>
+        <v>712005</v>
       </c>
       <c r="R34" t="n">
-        <v>6649838</v>
+        <v>6649760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4571,7 +4563,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054333</v>
+        <v>123011797</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4611,27 +4603,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712580</v>
+        <v>712581</v>
       </c>
       <c r="R35" t="n">
-        <v>6649752</v>
+        <v>6649757</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4671,31 +4658,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123008545</v>
+        <v>123002458</v>
       </c>
       <c r="B36" t="n">
-        <v>110503</v>
+        <v>78833</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4704,41 +4686,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712097</v>
+        <v>711934</v>
       </c>
       <c r="R36" t="n">
-        <v>6649846</v>
+        <v>6649764</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4770,12 +4763,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4787,17 +4786,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054358</v>
+        <v>123005529</v>
       </c>
       <c r="B37" t="n">
-        <v>78833</v>
+        <v>97319</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4806,50 +4805,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>637</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711929</v>
+        <v>712073</v>
       </c>
       <c r="R37" t="n">
-        <v>6649767</v>
+        <v>6649811</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4881,11 +4871,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4894,31 +4879,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054338</v>
+        <v>123054342</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4927,25 +4907,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4960,10 +4940,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712174</v>
+        <v>712108</v>
       </c>
       <c r="R38" t="n">
-        <v>6649978</v>
+        <v>6649846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5027,7 +5007,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054351</v>
+        <v>123054346</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5060,16 +5040,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5081,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712043</v>
+        <v>712166</v>
       </c>
       <c r="R39" t="n">
-        <v>6649750</v>
+        <v>6649838</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5148,7 +5119,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054339</v>
+        <v>123054347</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5181,7 +5152,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5193,10 +5173,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712159</v>
+        <v>712173</v>
       </c>
       <c r="R40" t="n">
-        <v>6649889</v>
+        <v>6649820</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5229,11 +5209,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5265,10 +5240,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123003233</v>
+        <v>123054320</v>
       </c>
       <c r="B41" t="n">
-        <v>105471</v>
+        <v>97319</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5281,46 +5256,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712047</v>
+        <v>712566</v>
       </c>
       <c r="R41" t="n">
-        <v>6649756</v>
+        <v>6649705</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5360,23 +5326,28 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123012181</v>
+        <v>123007899</v>
       </c>
       <c r="B42" t="n">
         <v>97319</v>
@@ -5412,17 +5383,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712565</v>
+        <v>712152</v>
       </c>
       <c r="R42" t="n">
-        <v>6649707</v>
+        <v>6649789</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5478,10 +5449,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054320</v>
+        <v>123054338</v>
       </c>
       <c r="B43" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5490,38 +5461,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712566</v>
+        <v>712174</v>
       </c>
       <c r="R43" t="n">
-        <v>6649705</v>
+        <v>6649978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5578,17 +5554,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054352</v>
+        <v>123008808</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>92266</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5597,55 +5573,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712040</v>
+        <v>712097</v>
       </c>
       <c r="R44" t="n">
-        <v>6649749</v>
+        <v>6649846</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5685,31 +5647,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123003505</v>
+        <v>123002544</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5722,31 +5679,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5755,10 +5712,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712047</v>
+        <v>711951</v>
       </c>
       <c r="R45" t="n">
-        <v>6649756</v>
+        <v>6649783</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5810,17 +5767,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123011797</v>
+        <v>123008545</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>110503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5829,47 +5786,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712581</v>
+        <v>712097</v>
       </c>
       <c r="R46" t="n">
-        <v>6649757</v>
+        <v>6649846</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5928,10 +5876,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123011961</v>
+        <v>123012181</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>97319</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5944,43 +5892,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712591</v>
+        <v>712565</v>
       </c>
       <c r="R47" t="n">
-        <v>6649698</v>
+        <v>6649707</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6039,7 +5978,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054337</v>
+        <v>123054352</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6072,7 +6011,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6084,10 +6032,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712185</v>
+        <v>712040</v>
       </c>
       <c r="R48" t="n">
-        <v>6649993</v>
+        <v>6649749</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6151,10 +6099,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054336</v>
+        <v>123054371</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6163,37 +6111,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6205,10 +6144,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712184</v>
+        <v>711866</v>
       </c>
       <c r="R49" t="n">
-        <v>6649994</v>
+        <v>6649752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6272,10 +6211,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123008739</v>
+        <v>123002982</v>
       </c>
       <c r="B50" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6288,34 +6227,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712097</v>
+        <v>712017</v>
       </c>
       <c r="R50" t="n">
-        <v>6649846</v>
+        <v>6649759</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6374,7 +6322,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123002458</v>
+        <v>123001473</v>
       </c>
       <c r="B51" t="n">
         <v>78833</v>
@@ -6409,7 +6357,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6425,13 +6373,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>711934</v>
+        <v>711936</v>
       </c>
       <c r="R51" t="n">
-        <v>6649764</v>
+        <v>6649774</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6465,7 +6413,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6477,6 +6425,36 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6493,10 +6471,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123054353</v>
+        <v>123054334</v>
       </c>
       <c r="B52" t="n">
-        <v>105471</v>
+        <v>57848</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6509,39 +6487,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712005</v>
+        <v>712597</v>
       </c>
       <c r="R52" t="n">
-        <v>6649760</v>
+        <v>6649817</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6576,6 +6549,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6598,17 +6576,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123002544</v>
+        <v>122999379</v>
       </c>
       <c r="B53" t="n">
-        <v>78833</v>
+        <v>110503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6617,50 +6595,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>637</v>
+        <v>219711</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711951</v>
+        <v>711874</v>
       </c>
       <c r="R53" t="n">
-        <v>6649783</v>
+        <v>6649764</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6709,17 +6678,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122999379</v>
+        <v>123003233</v>
       </c>
       <c r="B54" t="n">
-        <v>110503</v>
+        <v>105471</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6732,37 +6701,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>711874</v>
+        <v>712047</v>
       </c>
       <c r="R54" t="n">
-        <v>6649764</v>
+        <v>6649756</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6818,10 +6796,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054332</v>
+        <v>123054337</v>
       </c>
       <c r="B55" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6830,25 +6808,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6859,14 +6837,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712595</v>
+        <v>712185</v>
       </c>
       <c r="R55" t="n">
-        <v>6649701</v>
+        <v>6649993</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6923,14 +6901,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123054347</v>
+        <v>123003467</v>
       </c>
       <c r="B56" t="n">
         <v>98365</v>
@@ -6963,34 +6941,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712173</v>
+        <v>712047</v>
       </c>
       <c r="R56" t="n">
-        <v>6649820</v>
+        <v>6649756</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7030,31 +6994,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123007899</v>
+        <v>123054345</v>
       </c>
       <c r="B57" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7063,41 +7022,55 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712152</v>
+        <v>712165</v>
       </c>
       <c r="R57" t="n">
-        <v>6649789</v>
+        <v>6649838</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7137,26 +7110,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054342</v>
+        <v>123054339</v>
       </c>
       <c r="B58" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7165,25 +7143,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7198,10 +7176,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712108</v>
+        <v>712159</v>
       </c>
       <c r="R58" t="n">
-        <v>6649846</v>
+        <v>6649889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7234,6 +7212,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7265,10 +7248,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054371</v>
+        <v>123054351</v>
       </c>
       <c r="B59" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7277,28 +7260,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7310,10 +7302,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>711866</v>
+        <v>712043</v>
       </c>
       <c r="R59" t="n">
-        <v>6649752</v>
+        <v>6649750</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7377,10 +7369,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054344</v>
+        <v>123008739</v>
       </c>
       <c r="B60" t="n">
-        <v>110503</v>
+        <v>100631</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7393,42 +7385,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712108</v>
+        <v>712097</v>
       </c>
       <c r="R60" t="n">
-        <v>6649847</v>
+        <v>6649846</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7468,31 +7455,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123008808</v>
+        <v>123054332</v>
       </c>
       <c r="B61" t="n">
-        <v>92266</v>
+        <v>105471</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7505,37 +7487,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712097</v>
+        <v>712595</v>
       </c>
       <c r="R61" t="n">
-        <v>6649846</v>
+        <v>6649701</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7575,26 +7562,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123005529</v>
+        <v>123054358</v>
       </c>
       <c r="B62" t="n">
-        <v>97319</v>
+        <v>78833</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7603,41 +7595,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712073</v>
+        <v>711929</v>
       </c>
       <c r="R62" t="n">
-        <v>6649811</v>
+        <v>6649767</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7669,6 +7670,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7677,23 +7683,28 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054346</v>
+        <v>123054336</v>
       </c>
       <c r="B63" t="n">
         <v>98365</v>
@@ -7726,7 +7737,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7738,10 +7758,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712166</v>
+        <v>712184</v>
       </c>
       <c r="R63" t="n">
-        <v>6649838</v>
+        <v>6649994</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7805,10 +7825,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123001473</v>
+        <v>123054333</v>
       </c>
       <c r="B64" t="n">
-        <v>78833</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7821,45 +7841,48 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>711936</v>
+        <v>712580</v>
       </c>
       <c r="R64" t="n">
-        <v>6649774</v>
+        <v>6649752</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7894,70 +7917,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123054334</v>
+        <v>123011961</v>
       </c>
       <c r="B65" t="n">
-        <v>57848</v>
+        <v>105471</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7970,34 +7962,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712597</v>
+        <v>712591</v>
       </c>
       <c r="R65" t="n">
-        <v>6649817</v>
+        <v>6649698</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8032,11 +8033,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8045,21 +8041,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,7 +1562,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123009298</v>
+        <v>122999077</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,16 +1605,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712186</v>
+        <v>712127</v>
       </c>
       <c r="R9" t="n">
-        <v>6649996</v>
+        <v>6649778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,49 +1651,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122997556</v>
+        <v>122998128</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,31 +1693,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1728,10 +1735,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712163</v>
+        <v>712162</v>
       </c>
       <c r="R10" t="n">
-        <v>6649978</v>
+        <v>6649897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1790,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123000064</v>
+        <v>123000100</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>4776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1806,27 +1813,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1835,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712318</v>
+        <v>712304</v>
       </c>
       <c r="R11" t="n">
-        <v>6649737</v>
+        <v>6649724</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,19 +1875,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,19 +1892,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008181</v>
+        <v>122997028</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1942,7 +1939,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1956,10 +1953,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712179</v>
+        <v>712198</v>
       </c>
       <c r="R12" t="n">
-        <v>6649820</v>
+        <v>6650001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,7 +1988,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2001,7 +1998,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,14 +2018,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122998729</v>
+        <v>123008249</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -2063,7 +2060,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2076,18 +2073,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R13" t="n">
-        <v>6649818</v>
+        <v>6649832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,7 +2123,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2147,7 +2141,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122996823</v>
+        <v>122998873</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2182,7 +2176,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2195,18 +2189,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712187</v>
+        <v>712170</v>
       </c>
       <c r="R14" t="n">
-        <v>6650002</v>
+        <v>6649811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2247,7 +2239,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2266,7 +2257,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123002767</v>
+        <v>122998042</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2301,7 +2292,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2314,16 +2305,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712151</v>
+        <v>712150</v>
       </c>
       <c r="R15" t="n">
-        <v>6649915</v>
+        <v>6649898</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2364,6 +2357,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2382,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123009388</v>
+        <v>123000056</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,52 +2388,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712196</v>
+        <v>712308</v>
       </c>
       <c r="R16" t="n">
-        <v>6650006</v>
+        <v>6649706</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2498,10 +2478,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123001398</v>
+        <v>122998889</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2510,35 +2490,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2548,14 +2528,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712451</v>
+        <v>712161</v>
       </c>
       <c r="R17" t="n">
-        <v>6649760</v>
+        <v>6649804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2614,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122999323</v>
+        <v>123000064</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2626,35 +2606,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2663,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712171</v>
+        <v>712318</v>
       </c>
       <c r="R18" t="n">
-        <v>6649822</v>
+        <v>6649737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2698,7 +2674,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2708,7 +2684,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2735,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122997028</v>
+        <v>123007916</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,35 +2723,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2784,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712198</v>
+        <v>712142</v>
       </c>
       <c r="R19" t="n">
-        <v>6650001</v>
+        <v>6649796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2817,19 +2798,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2844,22 +2815,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123007916</v>
+        <v>122999168</v>
       </c>
       <c r="B20" t="n">
-        <v>105471</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,36 +2843,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2910,10 +2872,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712142</v>
+        <v>712092</v>
       </c>
       <c r="R20" t="n">
-        <v>6649796</v>
+        <v>6649793</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2972,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122997583</v>
+        <v>122998729</v>
       </c>
       <c r="B21" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,46 +2946,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712166</v>
+        <v>712176</v>
       </c>
       <c r="R21" t="n">
-        <v>6649973</v>
+        <v>6649818</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3061,6 +3034,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3079,7 +3053,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123008249</v>
+        <v>123009388</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3114,7 +3088,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3133,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712159</v>
+        <v>712196</v>
       </c>
       <c r="R22" t="n">
-        <v>6649832</v>
+        <v>6650006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3195,10 +3169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123008031</v>
+        <v>123001398</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3207,47 +3181,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712167</v>
+        <v>712451</v>
       </c>
       <c r="R23" t="n">
-        <v>6649816</v>
+        <v>6649760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3277,19 +3256,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3304,19 +3273,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122997739</v>
+        <v>123008181</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3351,7 +3320,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3365,10 +3334,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712167</v>
+        <v>712179</v>
       </c>
       <c r="R24" t="n">
-        <v>6649980</v>
+        <v>6649820</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3400,7 +3369,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3410,7 +3379,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,14 +3399,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122998889</v>
+        <v>122999323</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3472,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3480,21 +3449,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712161</v>
+        <v>712171</v>
       </c>
       <c r="R25" t="n">
-        <v>6649804</v>
+        <v>6649822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,9 +3488,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3541,19 +3515,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998128</v>
+        <v>123009298</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3588,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3596,21 +3570,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712162</v>
+        <v>712186</v>
       </c>
       <c r="R26" t="n">
-        <v>6649897</v>
+        <v>6649996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3640,9 +3609,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3657,19 +3636,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122998042</v>
+        <v>123002767</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3704,7 +3683,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3717,18 +3696,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712150</v>
+        <v>712151</v>
       </c>
       <c r="R27" t="n">
-        <v>6649898</v>
+        <v>6649915</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3769,7 +3746,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3788,10 +3764,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123000100</v>
+        <v>123008031</v>
       </c>
       <c r="B28" t="n">
-        <v>4776</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3800,31 +3776,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3833,10 +3813,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712304</v>
+        <v>712167</v>
       </c>
       <c r="R28" t="n">
-        <v>6649724</v>
+        <v>6649816</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3866,9 +3846,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3883,22 +3873,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122999168</v>
+        <v>122996823</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3907,43 +3897,54 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712092</v>
+        <v>712187</v>
       </c>
       <c r="R29" t="n">
-        <v>6649793</v>
+        <v>6650002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3984,6 +3985,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4002,10 +4004,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123000056</v>
+        <v>122997556</v>
       </c>
       <c r="B30" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4014,38 +4016,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712308</v>
+        <v>712163</v>
       </c>
       <c r="R30" t="n">
-        <v>6649706</v>
+        <v>6649978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4104,7 +4111,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122999077</v>
+        <v>122997739</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4139,7 +4146,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4147,23 +4154,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712127</v>
+        <v>712167</v>
       </c>
       <c r="R31" t="n">
-        <v>6649778</v>
+        <v>6649980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4193,40 +4193,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122998873</v>
+        <v>122997583</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4235,40 +4244,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712170</v>
+        <v>712166</v>
       </c>
       <c r="R32" t="n">
-        <v>6649811</v>
+        <v>6649973</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123054344</v>
+        <v>123012181</v>
       </c>
       <c r="B33" t="n">
-        <v>110503</v>
+        <v>97319</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4355,16 +4355,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4373,21 +4373,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712108</v>
+        <v>712565</v>
       </c>
       <c r="R33" t="n">
-        <v>6649847</v>
+        <v>6649707</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4431,30 +4426,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054353</v>
+        <v>123054352</v>
       </c>
       <c r="B34" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4463,28 +4453,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4496,10 +4495,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712005</v>
+        <v>712040</v>
       </c>
       <c r="R34" t="n">
-        <v>6649760</v>
+        <v>6649749</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123011797</v>
+        <v>123007899</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4575,47 +4574,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712581</v>
+        <v>712152</v>
       </c>
       <c r="R35" t="n">
-        <v>6649757</v>
+        <v>6649789</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4674,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123002458</v>
+        <v>123054344</v>
       </c>
       <c r="B36" t="n">
-        <v>78833</v>
+        <v>110503</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4686,52 +4676,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>637</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711934</v>
+        <v>712108</v>
       </c>
       <c r="R36" t="n">
-        <v>6649764</v>
+        <v>6649847</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4763,40 +4747,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123005529</v>
+        <v>123054371</v>
       </c>
       <c r="B37" t="n">
-        <v>97319</v>
+        <v>100631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4809,37 +4792,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712073</v>
+        <v>711866</v>
       </c>
       <c r="R37" t="n">
-        <v>6649811</v>
+        <v>6649752</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4879,26 +4867,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054342</v>
+        <v>122999379</v>
       </c>
       <c r="B38" t="n">
-        <v>100631</v>
+        <v>110503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4911,39 +4904,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712108</v>
+        <v>711874</v>
       </c>
       <c r="R38" t="n">
-        <v>6649846</v>
+        <v>6649764</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4987,30 +4975,25 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054346</v>
+        <v>123054334</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5019,43 +5002,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712166</v>
+        <v>712597</v>
       </c>
       <c r="R39" t="n">
-        <v>6649838</v>
+        <v>6649817</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5090,6 +5068,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5112,14 +5095,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054347</v>
+        <v>123054337</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5152,16 +5135,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5173,10 +5147,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712173</v>
+        <v>712185</v>
       </c>
       <c r="R40" t="n">
-        <v>6649820</v>
+        <v>6649993</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5240,10 +5214,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123054320</v>
+        <v>123001473</v>
       </c>
       <c r="B41" t="n">
-        <v>97319</v>
+        <v>78833</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5252,38 +5226,49 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712566</v>
+        <v>711936</v>
       </c>
       <c r="R41" t="n">
-        <v>6649705</v>
+        <v>6649774</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5318,39 +5303,70 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123007899</v>
+        <v>123054353</v>
       </c>
       <c r="B42" t="n">
-        <v>97319</v>
+        <v>105471</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5363,37 +5379,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712152</v>
+        <v>712005</v>
       </c>
       <c r="R42" t="n">
-        <v>6649789</v>
+        <v>6649760</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5433,23 +5454,28 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054338</v>
+        <v>123003505</v>
       </c>
       <c r="B43" t="n">
         <v>98365</v>
@@ -5482,25 +5508,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712174</v>
+        <v>712047</v>
       </c>
       <c r="R43" t="n">
-        <v>6649978</v>
+        <v>6649756</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5540,31 +5570,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123008808</v>
+        <v>123011961</v>
       </c>
       <c r="B44" t="n">
-        <v>92266</v>
+        <v>105471</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5577,37 +5602,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712097</v>
+        <v>712591</v>
       </c>
       <c r="R44" t="n">
-        <v>6649846</v>
+        <v>6649698</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5663,10 +5697,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123002544</v>
+        <v>123005529</v>
       </c>
       <c r="B45" t="n">
-        <v>78833</v>
+        <v>97319</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5675,47 +5709,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>637</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>711951</v>
+        <v>712073</v>
       </c>
       <c r="R45" t="n">
-        <v>6649783</v>
+        <v>6649811</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5767,17 +5792,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123008545</v>
+        <v>123054332</v>
       </c>
       <c r="B46" t="n">
-        <v>110503</v>
+        <v>105471</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5790,37 +5815,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712097</v>
+        <v>712595</v>
       </c>
       <c r="R46" t="n">
-        <v>6649846</v>
+        <v>6649701</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5860,26 +5890,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123012181</v>
+        <v>123054346</v>
       </c>
       <c r="B47" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5888,38 +5923,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712565</v>
+        <v>712166</v>
       </c>
       <c r="R47" t="n">
-        <v>6649707</v>
+        <v>6649838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5963,25 +6003,30 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054352</v>
+        <v>123054320</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5990,52 +6035,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712040</v>
+        <v>712566</v>
       </c>
       <c r="R48" t="n">
-        <v>6649749</v>
+        <v>6649705</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6092,17 +6123,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054371</v>
+        <v>123011797</v>
       </c>
       <c r="B49" t="n">
-        <v>100631</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,46 +6142,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>711866</v>
+        <v>712581</v>
       </c>
       <c r="R49" t="n">
-        <v>6649752</v>
+        <v>6649757</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6190,31 +6225,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123002982</v>
+        <v>123054336</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6223,50 +6253,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712017</v>
+        <v>712184</v>
       </c>
       <c r="R50" t="n">
-        <v>6649759</v>
+        <v>6649994</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6306,26 +6341,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123001473</v>
+        <v>123054339</v>
       </c>
       <c r="B51" t="n">
-        <v>78833</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6338,45 +6378,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>711936</v>
+        <v>712159</v>
       </c>
       <c r="R51" t="n">
-        <v>6649774</v>
+        <v>6649889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6413,7 +6447,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6422,59 +6456,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123054334</v>
+        <v>123054338</v>
       </c>
       <c r="B52" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6483,38 +6491,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712597</v>
+        <v>712174</v>
       </c>
       <c r="R52" t="n">
-        <v>6649817</v>
+        <v>6649978</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6549,11 +6562,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6576,17 +6584,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122999379</v>
+        <v>123054358</v>
       </c>
       <c r="B53" t="n">
-        <v>110503</v>
+        <v>78833</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6595,38 +6603,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711874</v>
+        <v>711929</v>
       </c>
       <c r="R53" t="n">
-        <v>6649764</v>
+        <v>6649767</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6661,6 +6678,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6669,26 +6691,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123003233</v>
+        <v>123002458</v>
       </c>
       <c r="B54" t="n">
-        <v>105471</v>
+        <v>78833</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6697,50 +6724,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>637</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712047</v>
+        <v>711934</v>
       </c>
       <c r="R54" t="n">
-        <v>6649756</v>
+        <v>6649764</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6772,12 +6801,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6789,17 +6824,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054337</v>
+        <v>123054342</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>100631</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6808,25 +6843,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6841,10 +6876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712185</v>
+        <v>712108</v>
       </c>
       <c r="R55" t="n">
-        <v>6649993</v>
+        <v>6649846</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6908,10 +6943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123003467</v>
+        <v>123002544</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>78833</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6924,34 +6959,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712047</v>
+        <v>711951</v>
       </c>
       <c r="R56" t="n">
-        <v>6649756</v>
+        <v>6649783</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7003,14 +7047,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054345</v>
+        <v>123054347</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -7045,7 +7089,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7064,10 +7108,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712165</v>
+        <v>712173</v>
       </c>
       <c r="R57" t="n">
-        <v>6649838</v>
+        <v>6649820</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7131,7 +7175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054339</v>
+        <v>123054345</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7164,7 +7208,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7176,10 +7229,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712159</v>
+        <v>712165</v>
       </c>
       <c r="R58" t="n">
-        <v>6649889</v>
+        <v>6649838</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7212,11 +7265,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7248,7 +7296,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054351</v>
+        <v>123054333</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7283,7 +7331,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7298,14 +7346,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712043</v>
+        <v>712580</v>
       </c>
       <c r="R59" t="n">
-        <v>6649750</v>
+        <v>6649752</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7362,17 +7410,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123008739</v>
+        <v>123008808</v>
       </c>
       <c r="B60" t="n">
-        <v>100631</v>
+        <v>92266</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7385,21 +7433,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7471,7 +7519,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054332</v>
+        <v>123003233</v>
       </c>
       <c r="B61" t="n">
         <v>105471</v>
@@ -7504,25 +7552,29 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712595</v>
+        <v>712047</v>
       </c>
       <c r="R61" t="n">
-        <v>6649701</v>
+        <v>6649756</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7562,31 +7614,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054358</v>
+        <v>123002982</v>
       </c>
       <c r="B62" t="n">
-        <v>78833</v>
+        <v>105471</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7595,50 +7642,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>637</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>711929</v>
+        <v>712017</v>
       </c>
       <c r="R62" t="n">
-        <v>6649767</v>
+        <v>6649759</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7670,11 +7717,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7683,28 +7725,23 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054336</v>
+        <v>123054351</v>
       </c>
       <c r="B63" t="n">
         <v>98365</v>
@@ -7739,7 +7776,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7758,10 +7795,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712184</v>
+        <v>712043</v>
       </c>
       <c r="R63" t="n">
-        <v>6649994</v>
+        <v>6649750</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7825,10 +7862,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054333</v>
+        <v>123008545</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>110503</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7837,55 +7874,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712580</v>
+        <v>712097</v>
       </c>
       <c r="R64" t="n">
-        <v>6649752</v>
+        <v>6649846</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7925,31 +7948,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123011961</v>
+        <v>123008739</v>
       </c>
       <c r="B65" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7962,46 +7980,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712591</v>
+        <v>712097</v>
       </c>
       <c r="R65" t="n">
-        <v>6649698</v>
+        <v>6649846</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122999323</v>
+        <v>123009298</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712171</v>
+        <v>712186</v>
       </c>
       <c r="R25" t="n">
-        <v>6649822</v>
+        <v>6649996</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123009298</v>
+        <v>122999323</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712186</v>
+        <v>712171</v>
       </c>
       <c r="R26" t="n">
-        <v>6649996</v>
+        <v>6649822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123009298</v>
+        <v>122999323</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712186</v>
+        <v>712171</v>
       </c>
       <c r="R25" t="n">
-        <v>6649996</v>
+        <v>6649822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122999323</v>
+        <v>123009298</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712171</v>
+        <v>712186</v>
       </c>
       <c r="R26" t="n">
-        <v>6649822</v>
+        <v>6649996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123003505</v>
+        <v>123005529</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>97319</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5487,47 +5487,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712047</v>
+        <v>712073</v>
       </c>
       <c r="R43" t="n">
-        <v>6649756</v>
+        <v>6649811</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5586,7 +5577,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123011961</v>
+        <v>123054332</v>
       </c>
       <c r="B44" t="n">
         <v>105471</v>
@@ -5619,26 +5610,22 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712591</v>
+        <v>712595</v>
       </c>
       <c r="R44" t="n">
-        <v>6649698</v>
+        <v>6649701</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5682,25 +5669,30 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123005529</v>
+        <v>123003505</v>
       </c>
       <c r="B45" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5709,38 +5701,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712073</v>
+        <v>712047</v>
       </c>
       <c r="R45" t="n">
-        <v>6649811</v>
+        <v>6649756</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5799,7 +5800,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123054332</v>
+        <v>123011961</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5832,22 +5833,26 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712595</v>
+        <v>712591</v>
       </c>
       <c r="R46" t="n">
-        <v>6649701</v>
+        <v>6649698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5891,20 +5896,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123000056</v>
+        <v>123000064</v>
       </c>
       <c r="B16" t="n">
-        <v>97319</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,34 +2392,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712308</v>
+        <v>712318</v>
       </c>
       <c r="R16" t="n">
-        <v>6649706</v>
+        <v>6649737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,9 +2454,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,22 +2481,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122998889</v>
+        <v>123007916</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,35 +2505,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2532,10 +2547,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712161</v>
+        <v>712142</v>
       </c>
       <c r="R17" t="n">
-        <v>6649804</v>
+        <v>6649796</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2594,10 +2609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123000064</v>
+        <v>123000056</v>
       </c>
       <c r="B18" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,39 +2625,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712318</v>
+        <v>712308</v>
       </c>
       <c r="R18" t="n">
-        <v>6649737</v>
+        <v>6649706</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2672,19 +2682,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,22 +2699,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123007916</v>
+        <v>122998889</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2723,35 +2723,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712142</v>
+        <v>712161</v>
       </c>
       <c r="R19" t="n">
-        <v>6649796</v>
+        <v>6649804</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122999323</v>
+        <v>123009298</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712171</v>
+        <v>712186</v>
       </c>
       <c r="R25" t="n">
-        <v>6649822</v>
+        <v>6649996</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123009298</v>
+        <v>122999323</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712186</v>
+        <v>712171</v>
       </c>
       <c r="R26" t="n">
-        <v>6649996</v>
+        <v>6649822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -6591,7 +6591,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123054358</v>
+        <v>123002458</v>
       </c>
       <c r="B53" t="n">
         <v>78833</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6634,19 +6634,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711929</v>
+        <v>711934</v>
       </c>
       <c r="R53" t="n">
-        <v>6649767</v>
+        <v>6649764</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6680,7 +6682,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
+          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6689,33 +6691,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123002458</v>
+        <v>123054342</v>
       </c>
       <c r="B54" t="n">
-        <v>78833</v>
+        <v>100631</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6724,52 +6722,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>637</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>711934</v>
+        <v>712108</v>
       </c>
       <c r="R54" t="n">
-        <v>6649764</v>
+        <v>6649846</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6801,40 +6793,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054342</v>
+        <v>123002544</v>
       </c>
       <c r="B55" t="n">
-        <v>100631</v>
+        <v>78833</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6843,46 +6834,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>637</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712108</v>
+        <v>711951</v>
       </c>
       <c r="R55" t="n">
-        <v>6649846</v>
+        <v>6649783</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6922,31 +6917,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123002544</v>
+        <v>123054347</v>
       </c>
       <c r="B56" t="n">
-        <v>78833</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6959,46 +6949,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>711951</v>
+        <v>712173</v>
       </c>
       <c r="R56" t="n">
-        <v>6649783</v>
+        <v>6649820</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7038,23 +7033,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054347</v>
+        <v>123054345</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712173</v>
+        <v>712165</v>
       </c>
       <c r="R57" t="n">
-        <v>6649820</v>
+        <v>6649838</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054345</v>
+        <v>123054333</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712165</v>
+        <v>712580</v>
       </c>
       <c r="R58" t="n">
-        <v>6649838</v>
+        <v>6649752</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7289,17 +7289,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054333</v>
+        <v>123008808</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>92266</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7308,55 +7308,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712580</v>
+        <v>712097</v>
       </c>
       <c r="R59" t="n">
-        <v>6649752</v>
+        <v>6649846</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7396,31 +7382,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123008808</v>
+        <v>123003233</v>
       </c>
       <c r="B60" t="n">
-        <v>92266</v>
+        <v>105471</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7433,34 +7414,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712097</v>
+        <v>712047</v>
       </c>
       <c r="R60" t="n">
-        <v>6649846</v>
+        <v>6649756</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7519,7 +7509,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123003233</v>
+        <v>123002982</v>
       </c>
       <c r="B61" t="n">
         <v>105471</v>
@@ -7554,7 +7544,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7568,10 +7558,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712047</v>
+        <v>712017</v>
       </c>
       <c r="R61" t="n">
-        <v>6649756</v>
+        <v>6649759</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7630,10 +7620,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123002982</v>
+        <v>123054351</v>
       </c>
       <c r="B62" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7642,50 +7632,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712017</v>
+        <v>712043</v>
       </c>
       <c r="R62" t="n">
-        <v>6649759</v>
+        <v>6649750</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7725,26 +7720,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054351</v>
+        <v>123008545</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>110503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7753,55 +7753,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712043</v>
+        <v>712097</v>
       </c>
       <c r="R63" t="n">
-        <v>6649750</v>
+        <v>6649846</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7841,31 +7827,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123008545</v>
+        <v>123008739</v>
       </c>
       <c r="B64" t="n">
-        <v>110503</v>
+        <v>100631</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7878,21 +7859,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7964,10 +7945,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123008739</v>
+        <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>100631</v>
+        <v>78833</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7976,41 +7957,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>637</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712097</v>
+        <v>711929</v>
       </c>
       <c r="R65" t="n">
-        <v>6649846</v>
+        <v>6649767</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8042,6 +8032,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8050,16 +8045,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -3406,7 +3406,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123009298</v>
+        <v>122999323</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712186</v>
+        <v>712171</v>
       </c>
       <c r="R25" t="n">
-        <v>6649996</v>
+        <v>6649822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122999323</v>
+        <v>123009298</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712171</v>
+        <v>712186</v>
       </c>
       <c r="R26" t="n">
-        <v>6649822</v>
+        <v>6649996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -7175,10 +7175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054333</v>
+        <v>123008808</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>92266</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7187,55 +7187,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712580</v>
+        <v>712097</v>
       </c>
       <c r="R58" t="n">
-        <v>6649752</v>
+        <v>6649846</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7275,31 +7261,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123008808</v>
+        <v>123054333</v>
       </c>
       <c r="B59" t="n">
-        <v>92266</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7308,41 +7289,55 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712097</v>
+        <v>712580</v>
       </c>
       <c r="R59" t="n">
-        <v>6649846</v>
+        <v>6649752</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7382,16 +7377,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122999077</v>
+        <v>123008031</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,23 +1605,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712127</v>
+        <v>712167</v>
       </c>
       <c r="R9" t="n">
-        <v>6649778</v>
+        <v>6649816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,40 +1644,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122998128</v>
+        <v>123009298</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,7 +1718,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1724,21 +1726,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712162</v>
+        <v>712186</v>
       </c>
       <c r="R10" t="n">
-        <v>6649897</v>
+        <v>6649996</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,9 +1765,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,22 +1792,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123000100</v>
+        <v>122998729</v>
       </c>
       <c r="B11" t="n">
-        <v>4776</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,43 +1816,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712304</v>
+        <v>712176</v>
       </c>
       <c r="R11" t="n">
-        <v>6649724</v>
+        <v>6649818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,6 +1904,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1907,7 +1926,7 @@
         <v>122997028</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2025,10 +2044,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008249</v>
+        <v>122998889</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2060,7 +2079,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2079,10 +2098,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712159</v>
+        <v>712161</v>
       </c>
       <c r="R13" t="n">
-        <v>6649832</v>
+        <v>6649804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2141,10 +2160,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122998873</v>
+        <v>123007916</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,35 +2172,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2195,10 +2214,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712170</v>
+        <v>712142</v>
       </c>
       <c r="R14" t="n">
-        <v>6649811</v>
+        <v>6649796</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122998042</v>
+        <v>123008249</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2292,7 +2311,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2305,18 +2324,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712150</v>
+        <v>712159</v>
       </c>
       <c r="R15" t="n">
-        <v>6649898</v>
+        <v>6649832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2357,7 +2374,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2376,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123000064</v>
+        <v>122997739</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,31 +2404,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2421,10 +2441,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712318</v>
+        <v>712167</v>
       </c>
       <c r="R16" t="n">
-        <v>6649737</v>
+        <v>6649980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,7 +2476,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2466,7 +2486,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2493,10 +2513,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123007916</v>
+        <v>122998042</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,35 +2525,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2541,16 +2561,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712142</v>
+        <v>712150</v>
       </c>
       <c r="R17" t="n">
-        <v>6649796</v>
+        <v>6649898</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2591,6 +2613,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2609,10 +2632,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123000056</v>
+        <v>123009388</v>
       </c>
       <c r="B18" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,38 +2644,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712308</v>
+        <v>712196</v>
       </c>
       <c r="R18" t="n">
-        <v>6649706</v>
+        <v>6650006</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2711,10 +2748,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998889</v>
+        <v>122999323</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2746,7 +2783,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2754,21 +2791,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712161</v>
+        <v>712171</v>
       </c>
       <c r="R19" t="n">
-        <v>6649804</v>
+        <v>6649822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,9 +2830,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,22 +2857,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122999168</v>
+        <v>123001398</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>105474</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2843,39 +2885,48 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712092</v>
+        <v>712451</v>
       </c>
       <c r="R20" t="n">
-        <v>6649793</v>
+        <v>6649760</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2934,10 +2985,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122998729</v>
+        <v>122997583</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,57 +2997,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712176</v>
+        <v>712166</v>
       </c>
       <c r="R21" t="n">
-        <v>6649818</v>
+        <v>6649973</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3034,7 +3074,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3053,10 +3092,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123009388</v>
+        <v>122997556</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3065,40 +3104,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3107,10 +3137,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712196</v>
+        <v>712163</v>
       </c>
       <c r="R22" t="n">
-        <v>6650006</v>
+        <v>6649978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3169,10 +3199,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123001398</v>
+        <v>122999077</v>
       </c>
       <c r="B23" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3181,35 +3211,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3217,16 +3247,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712451</v>
+        <v>712127</v>
       </c>
       <c r="R23" t="n">
-        <v>6649760</v>
+        <v>6649778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,6 +3299,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3285,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123008181</v>
+        <v>122998873</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3320,7 +3353,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3328,16 +3361,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712179</v>
+        <v>712170</v>
       </c>
       <c r="R24" t="n">
-        <v>6649820</v>
+        <v>6649811</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,19 +3405,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3394,22 +3422,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122999323</v>
+        <v>123000056</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3418,47 +3446,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712171</v>
+        <v>712308</v>
       </c>
       <c r="R25" t="n">
-        <v>6649822</v>
+        <v>6649706</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3488,19 +3507,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,22 +3524,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123009298</v>
+        <v>123000064</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3539,35 +3548,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3576,10 +3581,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712186</v>
+        <v>712318</v>
       </c>
       <c r="R26" t="n">
-        <v>6649996</v>
+        <v>6649737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,7 +3616,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3626,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,17 +3646,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123002767</v>
+        <v>123008181</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3691,21 +3696,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712151</v>
+        <v>712179</v>
       </c>
       <c r="R27" t="n">
-        <v>6649915</v>
+        <v>6649820</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,9 +3735,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3752,22 +3762,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123008031</v>
+        <v>123002767</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3799,7 +3809,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3807,16 +3817,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712167</v>
+        <v>712151</v>
       </c>
       <c r="R28" t="n">
-        <v>6649816</v>
+        <v>6649915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3846,19 +3861,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,22 +3878,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122996823</v>
+        <v>122999168</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3897,54 +3902,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712187</v>
+        <v>712092</v>
       </c>
       <c r="R29" t="n">
-        <v>6650002</v>
+        <v>6649793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3985,7 +3979,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +3997,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122997556</v>
+        <v>122996823</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4016,43 +4009,54 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712163</v>
+        <v>712187</v>
       </c>
       <c r="R30" t="n">
-        <v>6649978</v>
+        <v>6650002</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4093,6 +4097,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4111,10 +4116,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122997739</v>
+        <v>123000100</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>4776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4123,35 +4128,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4160,10 +4161,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712167</v>
+        <v>712304</v>
       </c>
       <c r="R31" t="n">
-        <v>6649980</v>
+        <v>6649724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4193,19 +4194,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4220,22 +4211,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122997583</v>
+        <v>122998128</v>
       </c>
       <c r="B32" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4244,31 +4235,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712166</v>
+        <v>712162</v>
       </c>
       <c r="R32" t="n">
-        <v>6649973</v>
+        <v>6649897</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123012181</v>
+        <v>123011797</v>
       </c>
       <c r="B33" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,41 +4351,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712565</v>
+        <v>712581</v>
       </c>
       <c r="R33" t="n">
-        <v>6649707</v>
+        <v>6649757</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4441,10 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054352</v>
+        <v>123005529</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4453,55 +4462,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712040</v>
+        <v>712073</v>
       </c>
       <c r="R34" t="n">
-        <v>6649749</v>
+        <v>6649811</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4541,31 +4536,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123007899</v>
+        <v>123054353</v>
       </c>
       <c r="B35" t="n">
-        <v>97319</v>
+        <v>105474</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,37 +4568,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712152</v>
+        <v>712005</v>
       </c>
       <c r="R35" t="n">
-        <v>6649789</v>
+        <v>6649760</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4648,26 +4643,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054344</v>
+        <v>123054334</v>
       </c>
       <c r="B36" t="n">
-        <v>110503</v>
+        <v>57851</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4680,39 +4680,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712108</v>
+        <v>712597</v>
       </c>
       <c r="R36" t="n">
-        <v>6649847</v>
+        <v>6649817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4747,6 +4742,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4769,17 +4769,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054371</v>
+        <v>123002982</v>
       </c>
       <c r="B37" t="n">
-        <v>100631</v>
+        <v>105474</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4792,42 +4792,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711866</v>
+        <v>712017</v>
       </c>
       <c r="R37" t="n">
-        <v>6649752</v>
+        <v>6649759</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4867,31 +4871,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122999379</v>
+        <v>123008545</v>
       </c>
       <c r="B38" t="n">
-        <v>110503</v>
+        <v>110509</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4928,13 +4927,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>711874</v>
+        <v>712097</v>
       </c>
       <c r="R38" t="n">
-        <v>6649764</v>
+        <v>6649846</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4990,10 +4989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054334</v>
+        <v>123054332</v>
       </c>
       <c r="B39" t="n">
-        <v>57848</v>
+        <v>105474</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5006,34 +5005,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712597</v>
+        <v>712595</v>
       </c>
       <c r="R39" t="n">
-        <v>6649817</v>
+        <v>6649701</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5066,11 +5070,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Läte.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5102,10 +5101,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054337</v>
+        <v>123012181</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5114,43 +5113,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712185</v>
+        <v>712565</v>
       </c>
       <c r="R40" t="n">
-        <v>6649993</v>
+        <v>6649707</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5194,30 +5188,25 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123001473</v>
+        <v>123054345</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>98368</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,45 +5219,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711936</v>
+        <v>712165</v>
       </c>
       <c r="R41" t="n">
-        <v>6649774</v>
+        <v>6649838</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5303,70 +5295,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054353</v>
+        <v>123054371</v>
       </c>
       <c r="B42" t="n">
-        <v>105471</v>
+        <v>100634</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5379,21 +5340,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5408,10 +5369,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712005</v>
+        <v>711866</v>
       </c>
       <c r="R42" t="n">
-        <v>6649760</v>
+        <v>6649752</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5475,10 +5436,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123005529</v>
+        <v>123054336</v>
       </c>
       <c r="B43" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5487,41 +5448,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712073</v>
+        <v>712184</v>
       </c>
       <c r="R43" t="n">
-        <v>6649811</v>
+        <v>6649994</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5561,26 +5536,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054332</v>
+        <v>123054333</v>
       </c>
       <c r="B44" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5589,28 +5569,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5622,10 +5611,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712595</v>
+        <v>712580</v>
       </c>
       <c r="R44" t="n">
-        <v>6649701</v>
+        <v>6649752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5689,10 +5678,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123003505</v>
+        <v>123003467</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5722,16 +5711,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
@@ -5803,7 +5783,7 @@
         <v>123011961</v>
       </c>
       <c r="B46" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5911,10 +5891,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123054346</v>
+        <v>123054344</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>110509</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5923,25 +5903,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5956,10 +5936,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712166</v>
+        <v>712108</v>
       </c>
       <c r="R47" t="n">
-        <v>6649838</v>
+        <v>6649847</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6023,10 +6003,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054320</v>
+        <v>123002458</v>
       </c>
       <c r="B48" t="n">
-        <v>97319</v>
+        <v>78836</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6035,41 +6015,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712566</v>
+        <v>711934</v>
       </c>
       <c r="R48" t="n">
-        <v>6649705</v>
+        <v>6649764</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6101,39 +6092,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123011797</v>
+        <v>123054347</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6165,27 +6157,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712581</v>
+        <v>712173</v>
       </c>
       <c r="R49" t="n">
-        <v>6649757</v>
+        <v>6649820</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6225,26 +6222,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123054336</v>
+        <v>123054342</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>100634</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6253,37 +6255,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6295,10 +6288,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712184</v>
+        <v>712108</v>
       </c>
       <c r="R50" t="n">
-        <v>6649994</v>
+        <v>6649846</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6362,10 +6355,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054339</v>
+        <v>123054351</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6395,7 +6388,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6407,10 +6409,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712159</v>
+        <v>712043</v>
       </c>
       <c r="R51" t="n">
-        <v>6649889</v>
+        <v>6649750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6443,11 +6445,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6479,10 +6476,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123054338</v>
+        <v>123007899</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,46 +6488,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712174</v>
+        <v>712152</v>
       </c>
       <c r="R52" t="n">
-        <v>6649978</v>
+        <v>6649789</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6570,31 +6562,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123002458</v>
+        <v>122999379</v>
       </c>
       <c r="B53" t="n">
-        <v>78833</v>
+        <v>110509</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6603,52 +6590,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>637</v>
+        <v>219711</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711934</v>
+        <v>711874</v>
       </c>
       <c r="R53" t="n">
         <v>6649764</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6680,18 +6656,12 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6703,17 +6673,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123054342</v>
+        <v>123008739</v>
       </c>
       <c r="B54" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6744,24 +6714,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712108</v>
+        <v>712097</v>
       </c>
       <c r="R54" t="n">
         <v>6649846</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6801,31 +6766,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123002544</v>
+        <v>123054337</v>
       </c>
       <c r="B55" t="n">
-        <v>78833</v>
+        <v>98368</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6838,46 +6798,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>711951</v>
+        <v>712185</v>
       </c>
       <c r="R55" t="n">
-        <v>6649783</v>
+        <v>6649993</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6917,26 +6873,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123054347</v>
+        <v>123008808</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>92269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6945,55 +6906,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712173</v>
+        <v>712097</v>
       </c>
       <c r="R56" t="n">
-        <v>6649820</v>
+        <v>6649846</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7033,31 +6980,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054345</v>
+        <v>123002544</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>78836</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7070,21 +7012,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7094,27 +7036,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712165</v>
+        <v>711951</v>
       </c>
       <c r="R57" t="n">
-        <v>6649838</v>
+        <v>6649783</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7154,31 +7091,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123008808</v>
+        <v>123054346</v>
       </c>
       <c r="B58" t="n">
-        <v>92266</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7187,41 +7119,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712097</v>
+        <v>712166</v>
       </c>
       <c r="R58" t="n">
-        <v>6649846</v>
+        <v>6649838</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7261,26 +7198,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054333</v>
+        <v>123054339</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7310,16 +7252,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7327,14 +7260,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712580</v>
+        <v>712159</v>
       </c>
       <c r="R59" t="n">
-        <v>6649752</v>
+        <v>6649889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7369,6 +7302,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7391,17 +7329,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123003233</v>
+        <v>123054320</v>
       </c>
       <c r="B60" t="n">
-        <v>105471</v>
+        <v>97322</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7414,46 +7352,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712047</v>
+        <v>712566</v>
       </c>
       <c r="R60" t="n">
-        <v>6649756</v>
+        <v>6649705</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7493,26 +7422,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123002982</v>
+        <v>123001473</v>
       </c>
       <c r="B61" t="n">
-        <v>105471</v>
+        <v>78836</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7521,50 +7455,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>637</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712017</v>
+        <v>711936</v>
       </c>
       <c r="R61" t="n">
-        <v>6649759</v>
+        <v>6649774</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7596,14 +7532,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7613,17 +7585,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054351</v>
+        <v>123054352</v>
       </c>
       <c r="B62" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7655,7 +7627,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7674,10 +7646,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712043</v>
+        <v>712040</v>
       </c>
       <c r="R62" t="n">
-        <v>6649750</v>
+        <v>6649749</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7741,10 +7713,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123008545</v>
+        <v>123003233</v>
       </c>
       <c r="B63" t="n">
-        <v>110503</v>
+        <v>105474</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7757,34 +7729,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712097</v>
+        <v>712047</v>
       </c>
       <c r="R63" t="n">
-        <v>6649846</v>
+        <v>6649756</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7843,10 +7824,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123008739</v>
+        <v>123054338</v>
       </c>
       <c r="B64" t="n">
-        <v>100631</v>
+        <v>98368</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7855,41 +7836,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712097</v>
+        <v>712174</v>
       </c>
       <c r="R64" t="n">
-        <v>6649846</v>
+        <v>6649978</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7929,16 +7915,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7948,7 +7939,7 @@
         <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>78833</v>
+        <v>78836</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008031</v>
+        <v>122997583</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,35 +1574,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1611,13 +1607,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712167</v>
+        <v>712166</v>
       </c>
       <c r="R9" t="n">
-        <v>6649816</v>
+        <v>6649973</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,19 +1640,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,22 +1657,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123009298</v>
+        <v>123000100</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>4776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,35 +1681,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1732,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712186</v>
+        <v>712304</v>
       </c>
       <c r="R10" t="n">
-        <v>6649996</v>
+        <v>6649724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1765,19 +1747,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,22 +1764,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122998729</v>
+        <v>123000064</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1816,54 +1788,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712176</v>
+        <v>712318</v>
       </c>
       <c r="R11" t="n">
-        <v>6649818</v>
+        <v>6649737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1893,40 +1854,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122997028</v>
+        <v>123008181</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1958,7 +1928,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1972,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712198</v>
+        <v>712179</v>
       </c>
       <c r="R12" t="n">
-        <v>6650001</v>
+        <v>6649820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2007,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2017,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,17 +2007,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122998889</v>
+        <v>122997739</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2079,7 +2049,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2087,21 +2057,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712161</v>
+        <v>712167</v>
       </c>
       <c r="R13" t="n">
-        <v>6649804</v>
+        <v>6649980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2131,9 +2096,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,22 +2123,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123007916</v>
+        <v>122997028</v>
       </c>
       <c r="B14" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2172,40 +2147,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2214,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712142</v>
+        <v>712198</v>
       </c>
       <c r="R14" t="n">
-        <v>6649796</v>
+        <v>6650001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2247,9 +2217,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,22 +2244,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123008249</v>
+        <v>123009298</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2311,7 +2291,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2319,21 +2299,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712159</v>
+        <v>712186</v>
       </c>
       <c r="R15" t="n">
-        <v>6649832</v>
+        <v>6649996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2363,9 +2338,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,22 +2365,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122997739</v>
+        <v>123002767</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2435,16 +2420,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712167</v>
+        <v>712151</v>
       </c>
       <c r="R16" t="n">
-        <v>6649980</v>
+        <v>6649915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,19 +2464,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,22 +2481,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122998042</v>
+        <v>123008249</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,7 +2528,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2561,18 +2541,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712150</v>
+        <v>712159</v>
       </c>
       <c r="R17" t="n">
-        <v>6649898</v>
+        <v>6649832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2613,7 +2591,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123009388</v>
+        <v>123007916</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2644,35 +2621,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2686,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712196</v>
+        <v>712142</v>
       </c>
       <c r="R18" t="n">
-        <v>6650006</v>
+        <v>6649796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2748,10 +2725,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122999323</v>
+        <v>122999168</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2760,35 +2737,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2797,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712171</v>
+        <v>712092</v>
       </c>
       <c r="R19" t="n">
-        <v>6649822</v>
+        <v>6649793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2830,19 +2803,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2857,22 +2820,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123001398</v>
+        <v>122999077</v>
       </c>
       <c r="B20" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,35 +2844,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2917,16 +2880,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712451</v>
+        <v>712127</v>
       </c>
       <c r="R20" t="n">
-        <v>6649760</v>
+        <v>6649778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2967,6 +2932,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2985,10 +2951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122997583</v>
+        <v>123008031</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2997,31 +2963,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3030,13 +3000,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712166</v>
+        <v>712167</v>
       </c>
       <c r="R21" t="n">
-        <v>6649973</v>
+        <v>6649816</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3063,9 +3033,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3080,22 +3060,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122997556</v>
+        <v>122998729</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3104,43 +3084,54 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712163</v>
+        <v>712176</v>
       </c>
       <c r="R22" t="n">
-        <v>6649978</v>
+        <v>6649818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3181,6 +3172,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3199,10 +3191,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999077</v>
+        <v>122997556</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,54 +3203,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712127</v>
+        <v>712163</v>
       </c>
       <c r="R23" t="n">
-        <v>6649778</v>
+        <v>6649978</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3299,7 +3280,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3298,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122998873</v>
+        <v>122999323</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3353,7 +3333,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3361,21 +3341,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712170</v>
+        <v>712171</v>
       </c>
       <c r="R24" t="n">
-        <v>6649811</v>
+        <v>6649822</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,9 +3380,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3422,22 +3407,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123000056</v>
+        <v>123001398</v>
       </c>
       <c r="B25" t="n">
-        <v>97322</v>
+        <v>105476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,34 +3435,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712308</v>
+        <v>712451</v>
       </c>
       <c r="R25" t="n">
-        <v>6649706</v>
+        <v>6649760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,10 +3535,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123000064</v>
+        <v>122998889</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3548,31 +3547,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3581,10 +3589,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712318</v>
+        <v>712161</v>
       </c>
       <c r="R26" t="n">
-        <v>6649737</v>
+        <v>6649804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3614,19 +3622,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,22 +3639,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123008181</v>
+        <v>122998042</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3688,7 +3686,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3696,16 +3694,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712179</v>
+        <v>712150</v>
       </c>
       <c r="R27" t="n">
-        <v>6649820</v>
+        <v>6649898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,49 +3740,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123002767</v>
+        <v>123000056</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>97324</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3786,52 +3782,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712151</v>
+        <v>712308</v>
       </c>
       <c r="R28" t="n">
-        <v>6649915</v>
+        <v>6649706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3890,10 +3872,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122999168</v>
+        <v>122996823</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3902,43 +3884,54 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712092</v>
+        <v>712187</v>
       </c>
       <c r="R29" t="n">
-        <v>6649793</v>
+        <v>6650002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3979,6 +3972,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3997,10 +3991,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122996823</v>
+        <v>123009388</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4032,7 +4026,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4045,18 +4039,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712187</v>
+        <v>712196</v>
       </c>
       <c r="R30" t="n">
-        <v>6650002</v>
+        <v>6650006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4097,7 +4089,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4116,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123000100</v>
+        <v>122998873</v>
       </c>
       <c r="B31" t="n">
-        <v>4776</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4128,31 +4119,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712304</v>
+        <v>712170</v>
       </c>
       <c r="R31" t="n">
-        <v>6649724</v>
+        <v>6649811</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
         <v>122998128</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123011797</v>
+        <v>123054345</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4374,27 +4374,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712581</v>
+        <v>712165</v>
       </c>
       <c r="R33" t="n">
-        <v>6649757</v>
+        <v>6649838</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4434,26 +4439,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123005529</v>
+        <v>123011961</v>
       </c>
       <c r="B34" t="n">
-        <v>97322</v>
+        <v>105476</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4466,37 +4476,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712073</v>
+        <v>712591</v>
       </c>
       <c r="R34" t="n">
-        <v>6649811</v>
+        <v>6649698</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4552,10 +4571,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054353</v>
+        <v>123054338</v>
       </c>
       <c r="B35" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4564,25 +4583,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4597,10 +4616,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712005</v>
+        <v>712174</v>
       </c>
       <c r="R35" t="n">
-        <v>6649760</v>
+        <v>6649978</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4683,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054334</v>
+        <v>123054371</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>100636</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4680,34 +4699,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712597</v>
+        <v>711866</v>
       </c>
       <c r="R36" t="n">
-        <v>6649817</v>
+        <v>6649752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4742,11 +4766,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4769,17 +4788,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123002982</v>
+        <v>123008739</v>
       </c>
       <c r="B37" t="n">
-        <v>105474</v>
+        <v>100636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4792,43 +4811,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712017</v>
+        <v>712097</v>
       </c>
       <c r="R37" t="n">
-        <v>6649759</v>
+        <v>6649846</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4887,10 +4897,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123008545</v>
+        <v>123002982</v>
       </c>
       <c r="B38" t="n">
-        <v>110509</v>
+        <v>105476</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4903,34 +4913,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712097</v>
+        <v>712017</v>
       </c>
       <c r="R38" t="n">
-        <v>6649846</v>
+        <v>6649759</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4989,10 +5008,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054332</v>
+        <v>122999379</v>
       </c>
       <c r="B39" t="n">
-        <v>105474</v>
+        <v>110511</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5005,39 +5024,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712595</v>
+        <v>711874</v>
       </c>
       <c r="R39" t="n">
-        <v>6649701</v>
+        <v>6649764</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5081,30 +5095,25 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123012181</v>
+        <v>123054347</v>
       </c>
       <c r="B40" t="n">
-        <v>97322</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5113,38 +5122,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712565</v>
+        <v>712173</v>
       </c>
       <c r="R40" t="n">
-        <v>6649707</v>
+        <v>6649820</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5188,25 +5211,30 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123054345</v>
+        <v>123054342</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>100636</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,37 +5243,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5257,10 +5276,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712165</v>
+        <v>712108</v>
       </c>
       <c r="R41" t="n">
-        <v>6649838</v>
+        <v>6649846</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5324,10 +5343,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054371</v>
+        <v>123054346</v>
       </c>
       <c r="B42" t="n">
-        <v>100634</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5336,25 +5355,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5369,10 +5388,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711866</v>
+        <v>712166</v>
       </c>
       <c r="R42" t="n">
-        <v>6649752</v>
+        <v>6649838</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5436,10 +5455,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054336</v>
+        <v>123054334</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5448,52 +5467,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712184</v>
+        <v>712597</v>
       </c>
       <c r="R43" t="n">
-        <v>6649994</v>
+        <v>6649817</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5528,6 +5533,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5550,17 +5560,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054333</v>
+        <v>123054344</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>110511</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5569,37 +5579,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5607,14 +5608,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712580</v>
+        <v>712108</v>
       </c>
       <c r="R44" t="n">
-        <v>6649752</v>
+        <v>6649847</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5671,17 +5672,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123003467</v>
+        <v>123054352</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5711,20 +5712,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712047</v>
+        <v>712040</v>
       </c>
       <c r="R45" t="n">
-        <v>6649756</v>
+        <v>6649749</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5764,26 +5779,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123011961</v>
+        <v>123003233</v>
       </c>
       <c r="B46" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5815,7 +5835,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5825,17 +5845,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712591</v>
+        <v>712047</v>
       </c>
       <c r="R46" t="n">
-        <v>6649698</v>
+        <v>6649756</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5891,10 +5911,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123054344</v>
+        <v>123012181</v>
       </c>
       <c r="B47" t="n">
-        <v>110509</v>
+        <v>97324</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5907,16 +5927,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5925,21 +5945,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712108</v>
+        <v>712565</v>
       </c>
       <c r="R47" t="n">
-        <v>6649847</v>
+        <v>6649707</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5983,30 +5998,25 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123002458</v>
+        <v>123054320</v>
       </c>
       <c r="B48" t="n">
-        <v>78836</v>
+        <v>97324</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6015,52 +6025,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>637</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>711934</v>
+        <v>712566</v>
       </c>
       <c r="R48" t="n">
-        <v>6649764</v>
+        <v>6649705</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6092,40 +6091,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054347</v>
+        <v>123054337</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6155,16 +6153,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6176,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712173</v>
+        <v>712185</v>
       </c>
       <c r="R49" t="n">
-        <v>6649820</v>
+        <v>6649993</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6243,10 +6232,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123054342</v>
+        <v>123011797</v>
       </c>
       <c r="B50" t="n">
-        <v>100634</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6255,46 +6244,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712108</v>
+        <v>712581</v>
       </c>
       <c r="R50" t="n">
-        <v>6649846</v>
+        <v>6649757</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6334,31 +6327,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054351</v>
+        <v>123054339</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6388,16 +6376,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6409,10 +6388,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712043</v>
+        <v>712159</v>
       </c>
       <c r="R51" t="n">
-        <v>6649750</v>
+        <v>6649889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6445,6 +6424,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6476,10 +6460,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123007899</v>
+        <v>123054336</v>
       </c>
       <c r="B52" t="n">
-        <v>97322</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6488,41 +6472,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712152</v>
+        <v>712184</v>
       </c>
       <c r="R52" t="n">
-        <v>6649789</v>
+        <v>6649994</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6562,26 +6560,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122999379</v>
+        <v>123003505</v>
       </c>
       <c r="B53" t="n">
-        <v>110509</v>
+        <v>98370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6590,41 +6593,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711874</v>
+        <v>712047</v>
       </c>
       <c r="R53" t="n">
-        <v>6649764</v>
+        <v>6649756</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6680,10 +6692,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123008739</v>
+        <v>123008545</v>
       </c>
       <c r="B54" t="n">
-        <v>100634</v>
+        <v>110511</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6696,21 +6708,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6782,10 +6794,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054337</v>
+        <v>123001473</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>78838</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6798,39 +6810,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712185</v>
+        <v>711936</v>
       </c>
       <c r="R55" t="n">
-        <v>6649993</v>
+        <v>6649774</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6865,29 +6883,60 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6897,7 +6946,7 @@
         <v>123008808</v>
       </c>
       <c r="B56" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6996,10 +7045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123002544</v>
+        <v>123054333</v>
       </c>
       <c r="B57" t="n">
-        <v>78836</v>
+        <v>98370</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7012,46 +7061,51 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>711951</v>
+        <v>712580</v>
       </c>
       <c r="R57" t="n">
-        <v>6649783</v>
+        <v>6649752</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7091,26 +7145,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054346</v>
+        <v>123054332</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7119,25 +7178,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7148,14 +7207,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712166</v>
+        <v>712595</v>
       </c>
       <c r="R58" t="n">
-        <v>6649838</v>
+        <v>6649701</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7212,17 +7271,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054339</v>
+        <v>123002458</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>78838</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7235,42 +7294,48 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712159</v>
+        <v>711934</v>
       </c>
       <c r="R59" t="n">
-        <v>6649889</v>
+        <v>6649764</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7304,7 +7369,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ymnig.</t>
+          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7313,33 +7378,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054320</v>
+        <v>123002544</v>
       </c>
       <c r="B60" t="n">
-        <v>97322</v>
+        <v>78838</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7348,41 +7409,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712566</v>
+        <v>711951</v>
       </c>
       <c r="R60" t="n">
-        <v>6649705</v>
+        <v>6649783</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7422,31 +7492,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123001473</v>
+        <v>123054351</v>
       </c>
       <c r="B61" t="n">
-        <v>78836</v>
+        <v>98370</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7459,45 +7524,48 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>711936</v>
+        <v>712043</v>
       </c>
       <c r="R61" t="n">
-        <v>6649774</v>
+        <v>6649750</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7532,70 +7600,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054352</v>
+        <v>123005529</v>
       </c>
       <c r="B62" t="n">
-        <v>98368</v>
+        <v>97324</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7604,55 +7641,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712040</v>
+        <v>712073</v>
       </c>
       <c r="R62" t="n">
-        <v>6649749</v>
+        <v>6649811</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7692,31 +7715,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123003233</v>
+        <v>123054353</v>
       </c>
       <c r="B63" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7746,29 +7764,25 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712047</v>
+        <v>712005</v>
       </c>
       <c r="R63" t="n">
-        <v>6649756</v>
+        <v>6649760</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7808,26 +7822,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054338</v>
+        <v>123007899</v>
       </c>
       <c r="B64" t="n">
-        <v>98368</v>
+        <v>97324</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7836,46 +7855,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712174</v>
+        <v>712152</v>
       </c>
       <c r="R64" t="n">
-        <v>6649978</v>
+        <v>6649789</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7915,21 +7929,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7939,7 +7948,7 @@
         <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>78836</v>
+        <v>78838</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008249</v>
+        <v>123007916</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>105476</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,35 +2505,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712159</v>
+        <v>712142</v>
       </c>
       <c r="R17" t="n">
-        <v>6649832</v>
+        <v>6649796</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123007916</v>
+        <v>123008249</v>
       </c>
       <c r="B18" t="n">
-        <v>105476</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,35 +2621,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712142</v>
+        <v>712159</v>
       </c>
       <c r="R18" t="n">
-        <v>6649796</v>
+        <v>6649832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123054345</v>
+        <v>123011961</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>105476</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,25 +4351,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4379,24 +4379,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712165</v>
+        <v>712591</v>
       </c>
       <c r="R33" t="n">
-        <v>6649838</v>
+        <v>6649698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4440,30 +4435,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123011961</v>
+        <v>123054345</v>
       </c>
       <c r="B34" t="n">
-        <v>105476</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,25 +4462,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4500,19 +4490,24 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712591</v>
+        <v>712165</v>
       </c>
       <c r="R34" t="n">
-        <v>6649698</v>
+        <v>6649838</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4556,15 +4551,20 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122997583</v>
+        <v>123007916</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>105482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,27 +1578,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1607,13 +1616,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712166</v>
+        <v>712142</v>
       </c>
       <c r="R9" t="n">
-        <v>6649973</v>
+        <v>6649796</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1669,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123000100</v>
+        <v>123008181</v>
       </c>
       <c r="B10" t="n">
-        <v>4776</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,31 +1690,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1714,10 +1727,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712304</v>
+        <v>712179</v>
       </c>
       <c r="R10" t="n">
-        <v>6649724</v>
+        <v>6649820</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,9 +1760,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,22 +1787,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123000064</v>
+        <v>123008249</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,31 +1811,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1821,10 +1853,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712318</v>
+        <v>712159</v>
       </c>
       <c r="R11" t="n">
-        <v>6649737</v>
+        <v>6649832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1854,19 +1886,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,22 +1903,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008181</v>
+        <v>122998042</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,7 +1950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1936,16 +1958,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712179</v>
+        <v>712150</v>
       </c>
       <c r="R12" t="n">
-        <v>6649820</v>
+        <v>6649898</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,49 +2004,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122997739</v>
+        <v>123009298</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2049,7 +2069,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2063,10 +2083,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712167</v>
+        <v>712186</v>
       </c>
       <c r="R13" t="n">
-        <v>6649980</v>
+        <v>6649996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2098,7 +2118,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2108,7 +2128,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,17 +2148,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122997028</v>
+        <v>122999168</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2147,35 +2167,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2184,10 +2200,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712198</v>
+        <v>712092</v>
       </c>
       <c r="R14" t="n">
-        <v>6650001</v>
+        <v>6649793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,19 +2233,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,22 +2250,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123009298</v>
+        <v>123002767</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,7 +2297,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2299,16 +2305,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712186</v>
+        <v>712151</v>
       </c>
       <c r="R15" t="n">
-        <v>6649996</v>
+        <v>6649915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,19 +2349,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,22 +2366,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123002767</v>
+        <v>122998128</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2412,7 +2413,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2431,10 +2432,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712151</v>
+        <v>712162</v>
       </c>
       <c r="R16" t="n">
-        <v>6649915</v>
+        <v>6649897</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123007916</v>
+        <v>123000064</v>
       </c>
       <c r="B17" t="n">
-        <v>105476</v>
+        <v>57851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,36 +2510,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2547,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712142</v>
+        <v>712318</v>
       </c>
       <c r="R17" t="n">
-        <v>6649796</v>
+        <v>6649737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2580,9 +2572,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,22 +2599,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123008249</v>
+        <v>123001398</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,35 +2623,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2659,14 +2661,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712159</v>
+        <v>712451</v>
       </c>
       <c r="R18" t="n">
-        <v>6649832</v>
+        <v>6649760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122999168</v>
+        <v>122999323</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,31 +2739,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2770,10 +2776,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712092</v>
+        <v>712171</v>
       </c>
       <c r="R19" t="n">
-        <v>6649793</v>
+        <v>6649822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2803,9 +2809,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2836,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122999077</v>
+        <v>122997028</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,7 +2883,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,23 +2891,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712127</v>
+        <v>712198</v>
       </c>
       <c r="R20" t="n">
-        <v>6649778</v>
+        <v>6650001</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,40 +2930,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123008031</v>
+        <v>122999077</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2986,7 +3004,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2994,16 +3012,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712167</v>
+        <v>712127</v>
       </c>
       <c r="R21" t="n">
-        <v>6649816</v>
+        <v>6649778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3033,49 +3058,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122998729</v>
+        <v>123000056</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3084,54 +3100,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712176</v>
+        <v>712308</v>
       </c>
       <c r="R22" t="n">
-        <v>6649818</v>
+        <v>6649706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3172,7 +3172,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3191,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122997556</v>
+        <v>122998729</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,43 +3202,54 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712163</v>
+        <v>712176</v>
       </c>
       <c r="R23" t="n">
-        <v>6649978</v>
+        <v>6649818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,6 +3290,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3298,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122999323</v>
+        <v>123000100</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>4776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3310,35 +3321,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3347,10 +3354,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712171</v>
+        <v>712304</v>
       </c>
       <c r="R24" t="n">
-        <v>6649822</v>
+        <v>6649724</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3380,19 +3387,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,22 +3404,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123001398</v>
+        <v>122998889</v>
       </c>
       <c r="B25" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3431,35 +3428,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3469,14 +3466,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712451</v>
+        <v>712161</v>
       </c>
       <c r="R25" t="n">
-        <v>6649760</v>
+        <v>6649804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3535,10 +3532,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998889</v>
+        <v>122997556</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3547,40 +3544,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3589,10 +3577,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712161</v>
+        <v>712163</v>
       </c>
       <c r="R26" t="n">
-        <v>6649804</v>
+        <v>6649978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3651,10 +3639,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122998042</v>
+        <v>123008031</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3686,7 +3674,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3694,23 +3682,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712150</v>
+        <v>712167</v>
       </c>
       <c r="R27" t="n">
-        <v>6649898</v>
+        <v>6649816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3740,40 +3721,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123000056</v>
+        <v>123009388</v>
       </c>
       <c r="B28" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3782,38 +3772,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712308</v>
+        <v>712196</v>
       </c>
       <c r="R28" t="n">
-        <v>6649706</v>
+        <v>6650006</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3872,10 +3876,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122996823</v>
+        <v>122997739</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3907,7 +3911,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3915,23 +3919,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712187</v>
+        <v>712167</v>
       </c>
       <c r="R29" t="n">
-        <v>6650002</v>
+        <v>6649980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3961,40 +3958,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123009388</v>
+        <v>122996823</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4026,7 +4032,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4039,16 +4045,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712196</v>
+        <v>712187</v>
       </c>
       <c r="R30" t="n">
-        <v>6650006</v>
+        <v>6650002</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4089,6 +4097,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4107,10 +4116,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122998873</v>
+        <v>122997583</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4119,40 +4128,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712170</v>
+        <v>712166</v>
       </c>
       <c r="R31" t="n">
-        <v>6649811</v>
+        <v>6649973</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122998128</v>
+        <v>122998873</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712162</v>
+        <v>712170</v>
       </c>
       <c r="R32" t="n">
-        <v>6649897</v>
+        <v>6649811</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123011961</v>
+        <v>123002544</v>
       </c>
       <c r="B33" t="n">
-        <v>105476</v>
+        <v>78839</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,25 +4351,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>637</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4379,22 +4379,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712591</v>
+        <v>711951</v>
       </c>
       <c r="R33" t="n">
-        <v>6649698</v>
+        <v>6649783</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4443,17 +4443,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054345</v>
+        <v>123011961</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,25 +4462,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4490,24 +4490,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712165</v>
+        <v>712591</v>
       </c>
       <c r="R34" t="n">
-        <v>6649838</v>
+        <v>6649698</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4551,30 +4546,25 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054338</v>
+        <v>123054334</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4583,43 +4573,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712174</v>
+        <v>712597</v>
       </c>
       <c r="R35" t="n">
-        <v>6649978</v>
+        <v>6649817</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,6 +4639,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4676,17 +4666,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054371</v>
+        <v>123054336</v>
       </c>
       <c r="B36" t="n">
-        <v>100636</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4695,28 +4685,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4728,10 +4727,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711866</v>
+        <v>712184</v>
       </c>
       <c r="R36" t="n">
-        <v>6649752</v>
+        <v>6649994</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4795,10 +4794,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123008739</v>
+        <v>123054351</v>
       </c>
       <c r="B37" t="n">
-        <v>100636</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4807,41 +4806,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712097</v>
+        <v>712043</v>
       </c>
       <c r="R37" t="n">
-        <v>6649846</v>
+        <v>6649750</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4881,26 +4894,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123002982</v>
+        <v>123054337</v>
       </c>
       <c r="B38" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4909,50 +4927,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712017</v>
+        <v>712185</v>
       </c>
       <c r="R38" t="n">
-        <v>6649759</v>
+        <v>6649993</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4992,26 +5006,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122999379</v>
+        <v>123001473</v>
       </c>
       <c r="B39" t="n">
-        <v>110511</v>
+        <v>78839</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5020,38 +5039,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>711874</v>
+        <v>711936</v>
       </c>
       <c r="R39" t="n">
-        <v>6649764</v>
+        <v>6649774</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5086,14 +5116,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5103,17 +5169,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054347</v>
+        <v>123054344</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>110518</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5122,37 +5188,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5164,10 +5221,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712173</v>
+        <v>712108</v>
       </c>
       <c r="R40" t="n">
-        <v>6649820</v>
+        <v>6649847</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5231,10 +5288,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123054342</v>
+        <v>123054371</v>
       </c>
       <c r="B41" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5276,10 +5333,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712108</v>
+        <v>711866</v>
       </c>
       <c r="R41" t="n">
-        <v>6649846</v>
+        <v>6649752</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5343,10 +5400,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054346</v>
+        <v>123003233</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5355,46 +5412,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712166</v>
+        <v>712047</v>
       </c>
       <c r="R42" t="n">
-        <v>6649838</v>
+        <v>6649756</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5434,31 +5495,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054334</v>
+        <v>123054338</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5467,38 +5523,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712597</v>
+        <v>712174</v>
       </c>
       <c r="R43" t="n">
-        <v>6649817</v>
+        <v>6649978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5533,11 +5594,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5560,17 +5616,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054344</v>
+        <v>123002458</v>
       </c>
       <c r="B44" t="n">
-        <v>110511</v>
+        <v>78839</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5579,46 +5635,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712108</v>
+        <v>711934</v>
       </c>
       <c r="R44" t="n">
-        <v>6649847</v>
+        <v>6649764</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5650,39 +5712,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123054352</v>
+        <v>123012181</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5691,52 +5754,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712040</v>
+        <v>712565</v>
       </c>
       <c r="R45" t="n">
-        <v>6649749</v>
+        <v>6649707</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5780,30 +5829,25 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123003233</v>
+        <v>123054345</v>
       </c>
       <c r="B46" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5812,50 +5856,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712047</v>
+        <v>712165</v>
       </c>
       <c r="R46" t="n">
-        <v>6649756</v>
+        <v>6649838</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5895,26 +5944,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123012181</v>
+        <v>123054346</v>
       </c>
       <c r="B47" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5923,38 +5977,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712565</v>
+        <v>712166</v>
       </c>
       <c r="R47" t="n">
-        <v>6649707</v>
+        <v>6649838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5998,25 +6057,30 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054320</v>
+        <v>123054333</v>
       </c>
       <c r="B48" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6025,38 +6089,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712566</v>
+        <v>712580</v>
       </c>
       <c r="R48" t="n">
-        <v>6649705</v>
+        <v>6649752</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6120,10 +6198,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054337</v>
+        <v>123008808</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>92277</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6132,46 +6210,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712185</v>
+        <v>712097</v>
       </c>
       <c r="R49" t="n">
-        <v>6649993</v>
+        <v>6649846</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6211,31 +6284,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123011797</v>
+        <v>123054339</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6265,29 +6333,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712581</v>
+        <v>712159</v>
       </c>
       <c r="R50" t="n">
-        <v>6649757</v>
+        <v>6649889</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6319,6 +6383,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6327,26 +6396,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054339</v>
+        <v>123054353</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6355,25 +6429,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6388,10 +6462,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712159</v>
+        <v>712005</v>
       </c>
       <c r="R51" t="n">
-        <v>6649889</v>
+        <v>6649760</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6424,11 +6498,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6460,10 +6529,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123054336</v>
+        <v>123011797</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6495,32 +6564,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712184</v>
+        <v>712581</v>
       </c>
       <c r="R52" t="n">
-        <v>6649994</v>
+        <v>6649757</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6560,31 +6624,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123003505</v>
+        <v>123054352</v>
       </c>
       <c r="B53" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6616,7 +6675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6624,19 +6683,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712047</v>
+        <v>712040</v>
       </c>
       <c r="R53" t="n">
-        <v>6649756</v>
+        <v>6649749</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6676,26 +6740,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123008545</v>
+        <v>123054332</v>
       </c>
       <c r="B54" t="n">
-        <v>110511</v>
+        <v>105482</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6708,37 +6777,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712097</v>
+        <v>712595</v>
       </c>
       <c r="R54" t="n">
-        <v>6649846</v>
+        <v>6649701</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6778,26 +6852,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123001473</v>
+        <v>123007899</v>
       </c>
       <c r="B55" t="n">
-        <v>78838</v>
+        <v>97330</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6806,52 +6885,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>637</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>711936</v>
+        <v>712152</v>
       </c>
       <c r="R55" t="n">
-        <v>6649774</v>
+        <v>6649789</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6883,50 +6951,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6936,17 +6968,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123008808</v>
+        <v>123003505</v>
       </c>
       <c r="B56" t="n">
-        <v>92271</v>
+        <v>98376</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6955,38 +6987,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712097</v>
+        <v>712047</v>
       </c>
       <c r="R56" t="n">
-        <v>6649846</v>
+        <v>6649756</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7045,10 +7086,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054333</v>
+        <v>123005529</v>
       </c>
       <c r="B57" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7057,55 +7098,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712580</v>
+        <v>712073</v>
       </c>
       <c r="R57" t="n">
-        <v>6649752</v>
+        <v>6649811</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7145,31 +7172,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054332</v>
+        <v>123008545</v>
       </c>
       <c r="B58" t="n">
-        <v>105476</v>
+        <v>110518</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7182,42 +7204,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712595</v>
+        <v>712097</v>
       </c>
       <c r="R58" t="n">
-        <v>6649701</v>
+        <v>6649846</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7257,31 +7274,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123002458</v>
+        <v>123054347</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>98376</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7294,48 +7306,51 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>711934</v>
+        <v>712173</v>
       </c>
       <c r="R59" t="n">
-        <v>6649764</v>
+        <v>6649820</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7367,40 +7382,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123002544</v>
+        <v>123054342</v>
       </c>
       <c r="B60" t="n">
-        <v>78838</v>
+        <v>100642</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7409,50 +7423,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>637</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>711951</v>
+        <v>712108</v>
       </c>
       <c r="R60" t="n">
-        <v>6649783</v>
+        <v>6649846</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7492,26 +7502,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054351</v>
+        <v>122999379</v>
       </c>
       <c r="B61" t="n">
-        <v>98370</v>
+        <v>110518</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7520,52 +7535,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712043</v>
+        <v>711874</v>
       </c>
       <c r="R61" t="n">
-        <v>6649750</v>
+        <v>6649764</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7609,30 +7610,25 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123005529</v>
+        <v>123054320</v>
       </c>
       <c r="B62" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7665,17 +7661,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712073</v>
+        <v>712566</v>
       </c>
       <c r="R62" t="n">
-        <v>6649811</v>
+        <v>6649705</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7715,26 +7711,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054353</v>
+        <v>123002982</v>
       </c>
       <c r="B63" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7764,25 +7765,29 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712005</v>
+        <v>712017</v>
       </c>
       <c r="R63" t="n">
-        <v>6649760</v>
+        <v>6649759</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7822,31 +7827,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123007899</v>
+        <v>123008739</v>
       </c>
       <c r="B64" t="n">
-        <v>97324</v>
+        <v>100642</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7859,21 +7859,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712152</v>
+        <v>712097</v>
       </c>
       <c r="R64" t="n">
-        <v>6649789</v>
+        <v>6649846</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7948,7 +7948,7 @@
         <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2600,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122998873</v>
+        <v>122997556</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,40 +2612,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2654,10 +2645,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712170</v>
+        <v>712163</v>
       </c>
       <c r="R18" t="n">
-        <v>6649811</v>
+        <v>6649978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2716,10 +2707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122997556</v>
+        <v>122998873</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,31 +2719,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712163</v>
+        <v>712170</v>
       </c>
       <c r="R19" t="n">
-        <v>6649978</v>
+        <v>6649811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122997739</v>
+        <v>123000100</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>4776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,35 +2835,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2872,10 +2868,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712167</v>
+        <v>712304</v>
       </c>
       <c r="R20" t="n">
-        <v>6649980</v>
+        <v>6649724</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,19 +2901,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,22 +2918,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123000100</v>
+        <v>122997739</v>
       </c>
       <c r="B21" t="n">
-        <v>4776</v>
+        <v>98379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2956,31 +2942,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2989,10 +2979,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712304</v>
+        <v>712167</v>
       </c>
       <c r="R21" t="n">
-        <v>6649724</v>
+        <v>6649980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,9 +3012,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,12 +3039,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123001473</v>
+        <v>123011797</v>
       </c>
       <c r="B51" t="n">
-        <v>78842</v>
+        <v>98379</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6381,48 +6381,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>711936</v>
+        <v>712581</v>
       </c>
       <c r="R51" t="n">
-        <v>6649774</v>
+        <v>6649757</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6454,50 +6452,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6507,7 +6469,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6616,10 +6578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123011797</v>
+        <v>123001473</v>
       </c>
       <c r="B53" t="n">
-        <v>98379</v>
+        <v>78842</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6632,46 +6594,48 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712581</v>
+        <v>711936</v>
       </c>
       <c r="R53" t="n">
-        <v>6649757</v>
+        <v>6649774</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6703,14 +6667,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6720,17 +6720,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123054334</v>
+        <v>123002458</v>
       </c>
       <c r="B54" t="n">
-        <v>57851</v>
+        <v>78842</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6739,41 +6739,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>637</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712597</v>
+        <v>711934</v>
       </c>
       <c r="R54" t="n">
-        <v>6649817</v>
+        <v>6649764</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6807,7 +6818,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Läte.</t>
+          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6816,33 +6827,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123002458</v>
+        <v>123054334</v>
       </c>
       <c r="B55" t="n">
-        <v>78842</v>
+        <v>57851</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6851,52 +6858,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>637</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>711934</v>
+        <v>712597</v>
       </c>
       <c r="R55" t="n">
-        <v>6649764</v>
+        <v>6649817</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6930,7 +6926,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
+          <t>Läte.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6939,19 +6935,23 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7405,10 +7405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123008739</v>
+        <v>123054346</v>
       </c>
       <c r="B60" t="n">
-        <v>100645</v>
+        <v>98379</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7417,41 +7417,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712097</v>
+        <v>712166</v>
       </c>
       <c r="R60" t="n">
-        <v>6649846</v>
+        <v>6649838</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7491,26 +7496,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054332</v>
+        <v>123012181</v>
       </c>
       <c r="B61" t="n">
-        <v>105485</v>
+        <v>97333</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7523,39 +7533,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712595</v>
+        <v>712565</v>
       </c>
       <c r="R61" t="n">
-        <v>6649701</v>
+        <v>6649707</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7599,30 +7604,25 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054353</v>
+        <v>123008739</v>
       </c>
       <c r="B62" t="n">
-        <v>105485</v>
+        <v>100645</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712005</v>
+        <v>712097</v>
       </c>
       <c r="R62" t="n">
-        <v>6649760</v>
+        <v>6649846</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7710,31 +7705,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054346</v>
+        <v>123054332</v>
       </c>
       <c r="B63" t="n">
-        <v>98379</v>
+        <v>105485</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7743,25 +7733,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7772,14 +7762,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712166</v>
+        <v>712595</v>
       </c>
       <c r="R63" t="n">
-        <v>6649838</v>
+        <v>6649701</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7836,17 +7826,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123012181</v>
+        <v>123054353</v>
       </c>
       <c r="B64" t="n">
-        <v>97333</v>
+        <v>105485</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7859,34 +7849,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712565</v>
+        <v>712005</v>
       </c>
       <c r="R64" t="n">
-        <v>6649707</v>
+        <v>6649760</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7930,15 +7925,20 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123000064</v>
+        <v>123008031</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,31 +1574,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1607,10 +1611,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712318</v>
+        <v>712167</v>
       </c>
       <c r="R9" t="n">
-        <v>6649737</v>
+        <v>6649816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1672,17 +1676,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122998042</v>
+        <v>123000064</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,54 +1695,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712150</v>
+        <v>712318</v>
       </c>
       <c r="R10" t="n">
-        <v>6649898</v>
+        <v>6649737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,40 +1761,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008181</v>
+        <v>122999077</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,7 +1835,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1841,16 +1843,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712179</v>
+        <v>712127</v>
       </c>
       <c r="R11" t="n">
-        <v>6649820</v>
+        <v>6649778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1880,49 +1889,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122999168</v>
+        <v>122999323</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,31 +1931,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1964,10 +1968,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712092</v>
+        <v>712171</v>
       </c>
       <c r="R12" t="n">
-        <v>6649793</v>
+        <v>6649822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,9 +2001,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,22 +2028,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123000056</v>
+        <v>122997739</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,38 +2052,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712308</v>
+        <v>712167</v>
       </c>
       <c r="R13" t="n">
-        <v>6649706</v>
+        <v>6649980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,9 +2122,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,22 +2149,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123002767</v>
+        <v>123008181</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,7 +2196,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2171,21 +2204,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712151</v>
+        <v>712179</v>
       </c>
       <c r="R14" t="n">
-        <v>6649915</v>
+        <v>6649820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,9 +2243,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,22 +2270,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122999077</v>
+        <v>122997028</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2279,7 +2317,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2287,23 +2325,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712127</v>
+        <v>712198</v>
       </c>
       <c r="R15" t="n">
-        <v>6649778</v>
+        <v>6650001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2333,40 +2364,49 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123009298</v>
+        <v>123002767</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2398,7 +2438,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2406,16 +2446,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712186</v>
+        <v>712151</v>
       </c>
       <c r="R16" t="n">
-        <v>6649996</v>
+        <v>6649915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,19 +2490,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,22 +2507,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008249</v>
+        <v>123000100</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>4776</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,40 +2531,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2538,10 +2564,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712159</v>
+        <v>712304</v>
       </c>
       <c r="R17" t="n">
-        <v>6649832</v>
+        <v>6649724</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,10 +2626,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122997556</v>
+        <v>123008249</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,31 +2638,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2645,10 +2680,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712163</v>
+        <v>712159</v>
       </c>
       <c r="R18" t="n">
-        <v>6649978</v>
+        <v>6649832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2710,7 +2745,7 @@
         <v>122998873</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2823,10 +2858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123000100</v>
+        <v>122996823</v>
       </c>
       <c r="B20" t="n">
-        <v>4776</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,43 +2870,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712304</v>
+        <v>712187</v>
       </c>
       <c r="R20" t="n">
-        <v>6649724</v>
+        <v>6650002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2912,6 +2958,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2930,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122997739</v>
+        <v>123001398</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,47 +2989,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712167</v>
+        <v>712451</v>
       </c>
       <c r="R21" t="n">
-        <v>6649980</v>
+        <v>6649760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,19 +3064,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,22 +3081,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123008031</v>
+        <v>123009298</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,7 +3128,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3100,10 +3142,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712167</v>
+        <v>712186</v>
       </c>
       <c r="R22" t="n">
-        <v>6649816</v>
+        <v>6649996</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3145,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123001398</v>
+        <v>122998042</v>
       </c>
       <c r="B23" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3184,35 +3226,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3220,16 +3262,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712451</v>
+        <v>712150</v>
       </c>
       <c r="R23" t="n">
-        <v>6649760</v>
+        <v>6649898</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3270,6 +3314,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3288,10 +3333,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122997583</v>
+        <v>122998128</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3300,31 +3345,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3333,13 +3387,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712166</v>
+        <v>712162</v>
       </c>
       <c r="R24" t="n">
-        <v>6649973</v>
+        <v>6649897</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3395,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122999323</v>
+        <v>122997583</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3407,35 +3461,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3444,13 +3494,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712171</v>
+        <v>712166</v>
       </c>
       <c r="R25" t="n">
-        <v>6649822</v>
+        <v>6649973</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3477,19 +3527,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,22 +3544,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998128</v>
+        <v>122998729</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3551,7 +3591,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3564,16 +3604,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712162</v>
+        <v>712176</v>
       </c>
       <c r="R26" t="n">
-        <v>6649897</v>
+        <v>6649818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3614,6 +3656,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3632,10 +3675,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123009388</v>
+        <v>123007916</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3644,35 +3687,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3686,10 +3729,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712196</v>
+        <v>712142</v>
       </c>
       <c r="R27" t="n">
-        <v>6650006</v>
+        <v>6649796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3748,10 +3791,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123007916</v>
+        <v>123000056</v>
       </c>
       <c r="B28" t="n">
-        <v>105485</v>
+        <v>97350</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3764,48 +3807,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712142</v>
+        <v>712308</v>
       </c>
       <c r="R28" t="n">
-        <v>6649796</v>
+        <v>6649706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3864,10 +3893,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122998729</v>
+        <v>122997556</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3876,54 +3905,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712176</v>
+        <v>712163</v>
       </c>
       <c r="R29" t="n">
-        <v>6649818</v>
+        <v>6649978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3964,7 +3982,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3983,10 +4000,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122997028</v>
+        <v>122998889</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4018,7 +4035,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4026,16 +4043,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712198</v>
+        <v>712161</v>
       </c>
       <c r="R30" t="n">
-        <v>6650001</v>
+        <v>6649804</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,19 +4087,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4092,22 +4104,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122996823</v>
+        <v>123009388</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4139,7 +4151,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4152,18 +4164,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712187</v>
+        <v>712196</v>
       </c>
       <c r="R31" t="n">
-        <v>6650002</v>
+        <v>6650006</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4204,7 +4214,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4223,10 +4232,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122998889</v>
+        <v>122999168</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>5174</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4235,40 +4244,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712161</v>
+        <v>712092</v>
       </c>
       <c r="R32" t="n">
-        <v>6649804</v>
+        <v>6649793</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123005529</v>
+        <v>123054333</v>
       </c>
       <c r="B33" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,41 +4351,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712073</v>
+        <v>712580</v>
       </c>
       <c r="R33" t="n">
-        <v>6649811</v>
+        <v>6649752</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4425,26 +4439,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054338</v>
+        <v>123054336</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4474,7 +4493,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4486,10 +4514,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712174</v>
+        <v>712184</v>
       </c>
       <c r="R34" t="n">
-        <v>6649978</v>
+        <v>6649994</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4553,10 +4581,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123003233</v>
+        <v>123008808</v>
       </c>
       <c r="B35" t="n">
-        <v>105485</v>
+        <v>92297</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,43 +4597,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712047</v>
+        <v>712097</v>
       </c>
       <c r="R35" t="n">
-        <v>6649756</v>
+        <v>6649846</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4664,10 +4683,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054337</v>
+        <v>123054345</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4697,7 +4716,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4709,10 +4737,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712185</v>
+        <v>712165</v>
       </c>
       <c r="R36" t="n">
-        <v>6649993</v>
+        <v>6649838</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4776,10 +4804,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054351</v>
+        <v>123008739</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>100662</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4788,55 +4816,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712043</v>
+        <v>712097</v>
       </c>
       <c r="R37" t="n">
-        <v>6649750</v>
+        <v>6649846</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4876,31 +4890,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054345</v>
+        <v>123054339</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4930,16 +4939,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712165</v>
+        <v>712159</v>
       </c>
       <c r="R38" t="n">
-        <v>6649838</v>
+        <v>6649889</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4987,6 +4987,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5018,10 +5023,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054342</v>
+        <v>123011961</v>
       </c>
       <c r="B39" t="n">
-        <v>100645</v>
+        <v>105502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5034,39 +5039,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712108</v>
+        <v>712591</v>
       </c>
       <c r="R39" t="n">
-        <v>6649846</v>
+        <v>6649698</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5110,30 +5119,25 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123008808</v>
+        <v>123054371</v>
       </c>
       <c r="B40" t="n">
-        <v>92280</v>
+        <v>100662</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5146,37 +5150,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712097</v>
+        <v>711866</v>
       </c>
       <c r="R40" t="n">
-        <v>6649846</v>
+        <v>6649752</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5216,26 +5225,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123003505</v>
+        <v>123001473</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>78848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5248,46 +5262,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712047</v>
+        <v>711936</v>
       </c>
       <c r="R41" t="n">
-        <v>6649756</v>
+        <v>6649774</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5319,14 +5335,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5336,17 +5388,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054336</v>
+        <v>123054334</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5355,52 +5407,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712184</v>
+        <v>712597</v>
       </c>
       <c r="R42" t="n">
-        <v>6649994</v>
+        <v>6649817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5435,6 +5473,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5457,17 +5500,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054320</v>
+        <v>123003505</v>
       </c>
       <c r="B43" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5476,41 +5519,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712566</v>
+        <v>712047</v>
       </c>
       <c r="R43" t="n">
-        <v>6649705</v>
+        <v>6649756</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5550,31 +5602,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123011961</v>
+        <v>123054351</v>
       </c>
       <c r="B44" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5583,47 +5630,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712591</v>
+        <v>712043</v>
       </c>
       <c r="R44" t="n">
-        <v>6649698</v>
+        <v>6649750</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5667,25 +5719,30 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123054339</v>
+        <v>123054332</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5694,25 +5751,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5723,14 +5780,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712159</v>
+        <v>712595</v>
       </c>
       <c r="R45" t="n">
-        <v>6649889</v>
+        <v>6649701</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5765,11 +5822,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5792,17 +5844,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123054333</v>
+        <v>123002458</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>78848</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5815,51 +5867,48 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712580</v>
+        <v>711934</v>
       </c>
       <c r="R46" t="n">
-        <v>6649752</v>
+        <v>6649764</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5891,39 +5940,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123002982</v>
+        <v>123007899</v>
       </c>
       <c r="B47" t="n">
-        <v>105485</v>
+        <v>97350</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5936,43 +5986,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712017</v>
+        <v>712152</v>
       </c>
       <c r="R47" t="n">
-        <v>6649759</v>
+        <v>6649789</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6031,10 +6072,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122999379</v>
+        <v>123054347</v>
       </c>
       <c r="B48" t="n">
-        <v>110521</v>
+        <v>98396</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6043,38 +6084,52 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>711874</v>
+        <v>712173</v>
       </c>
       <c r="R48" t="n">
-        <v>6649764</v>
+        <v>6649820</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6118,25 +6173,30 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054352</v>
+        <v>123054342</v>
       </c>
       <c r="B49" t="n">
-        <v>98379</v>
+        <v>100662</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6145,37 +6205,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6187,10 +6238,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712040</v>
+        <v>712108</v>
       </c>
       <c r="R49" t="n">
-        <v>6649749</v>
+        <v>6649846</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6254,10 +6305,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123002544</v>
+        <v>122999379</v>
       </c>
       <c r="B50" t="n">
-        <v>78842</v>
+        <v>110538</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6266,50 +6317,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>637</v>
+        <v>219711</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>711951</v>
+        <v>711874</v>
       </c>
       <c r="R50" t="n">
-        <v>6649783</v>
+        <v>6649764</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6358,17 +6400,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123011797</v>
+        <v>123054344</v>
       </c>
       <c r="B51" t="n">
-        <v>98379</v>
+        <v>110538</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6377,50 +6419,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712581</v>
+        <v>712108</v>
       </c>
       <c r="R51" t="n">
-        <v>6649757</v>
+        <v>6649847</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6460,26 +6498,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123008545</v>
+        <v>123003233</v>
       </c>
       <c r="B52" t="n">
-        <v>110521</v>
+        <v>105502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6492,34 +6535,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712097</v>
+        <v>712047</v>
       </c>
       <c r="R52" t="n">
-        <v>6649846</v>
+        <v>6649756</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6578,10 +6630,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123001473</v>
+        <v>123002982</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>105502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6590,52 +6642,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>637</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>711936</v>
+        <v>712017</v>
       </c>
       <c r="R53" t="n">
-        <v>6649774</v>
+        <v>6649759</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6667,50 +6717,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6720,17 +6734,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123002458</v>
+        <v>123054338</v>
       </c>
       <c r="B54" t="n">
-        <v>78842</v>
+        <v>98396</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6743,48 +6757,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>711934</v>
+        <v>712174</v>
       </c>
       <c r="R54" t="n">
-        <v>6649764</v>
+        <v>6649978</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6816,40 +6824,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054334</v>
+        <v>123054352</v>
       </c>
       <c r="B55" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6858,38 +6865,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712597</v>
+        <v>712040</v>
       </c>
       <c r="R55" t="n">
-        <v>6649817</v>
+        <v>6649749</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6924,11 +6945,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6951,17 +6967,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123007899</v>
+        <v>123002544</v>
       </c>
       <c r="B56" t="n">
-        <v>97333</v>
+        <v>78848</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6970,38 +6986,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712152</v>
+        <v>711951</v>
       </c>
       <c r="R56" t="n">
-        <v>6649789</v>
+        <v>6649783</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7053,17 +7078,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054344</v>
+        <v>123011797</v>
       </c>
       <c r="B57" t="n">
-        <v>110521</v>
+        <v>98396</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7072,46 +7097,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712108</v>
+        <v>712581</v>
       </c>
       <c r="R57" t="n">
-        <v>6649847</v>
+        <v>6649757</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7151,31 +7180,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054371</v>
+        <v>123012181</v>
       </c>
       <c r="B58" t="n">
-        <v>100645</v>
+        <v>97350</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7188,39 +7212,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>711866</v>
+        <v>712565</v>
       </c>
       <c r="R58" t="n">
-        <v>6649752</v>
+        <v>6649707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7264,30 +7283,25 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054347</v>
+        <v>123054337</v>
       </c>
       <c r="B59" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7317,16 +7331,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7338,10 +7343,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712173</v>
+        <v>712185</v>
       </c>
       <c r="R59" t="n">
-        <v>6649820</v>
+        <v>6649993</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7405,10 +7410,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054346</v>
+        <v>123008545</v>
       </c>
       <c r="B60" t="n">
-        <v>98379</v>
+        <v>110538</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7417,46 +7422,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712166</v>
+        <v>712097</v>
       </c>
       <c r="R60" t="n">
-        <v>6649838</v>
+        <v>6649846</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7496,31 +7496,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123012181</v>
+        <v>123054353</v>
       </c>
       <c r="B61" t="n">
-        <v>97333</v>
+        <v>105502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7533,34 +7528,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712565</v>
+        <v>712005</v>
       </c>
       <c r="R61" t="n">
-        <v>6649707</v>
+        <v>6649760</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7604,25 +7604,30 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123008739</v>
+        <v>123005529</v>
       </c>
       <c r="B62" t="n">
-        <v>100645</v>
+        <v>97350</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7635,21 +7640,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7659,10 +7664,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712097</v>
+        <v>712073</v>
       </c>
       <c r="R62" t="n">
-        <v>6649846</v>
+        <v>6649811</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7721,10 +7726,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054332</v>
+        <v>123054346</v>
       </c>
       <c r="B63" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7733,25 +7738,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7762,14 +7767,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712595</v>
+        <v>712166</v>
       </c>
       <c r="R63" t="n">
-        <v>6649701</v>
+        <v>6649838</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7826,17 +7831,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054353</v>
+        <v>123054320</v>
       </c>
       <c r="B64" t="n">
-        <v>105485</v>
+        <v>97350</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7849,39 +7854,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712005</v>
+        <v>712566</v>
       </c>
       <c r="R64" t="n">
-        <v>6649760</v>
+        <v>6649705</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7948,7 +7948,7 @@
         <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>78842</v>
+        <v>78848</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998873</v>
+        <v>123001398</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,35 +2754,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712170</v>
+        <v>712451</v>
       </c>
       <c r="R19" t="n">
-        <v>6649811</v>
+        <v>6649760</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122996823</v>
+        <v>122998873</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2906,18 +2906,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712187</v>
+        <v>712170</v>
       </c>
       <c r="R20" t="n">
-        <v>6650002</v>
+        <v>6649811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,7 +2956,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2977,10 +2974,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123001398</v>
+        <v>122996823</v>
       </c>
       <c r="B21" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,35 +2986,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3025,16 +3022,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712451</v>
+        <v>712187</v>
       </c>
       <c r="R21" t="n">
-        <v>6649760</v>
+        <v>6650002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,6 +3074,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054339</v>
+        <v>123011961</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,43 +4918,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712159</v>
+        <v>712591</v>
       </c>
       <c r="R38" t="n">
-        <v>6649889</v>
+        <v>6649698</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4989,11 +4993,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5002,31 +5001,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123011961</v>
+        <v>123054339</v>
       </c>
       <c r="B39" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5035,47 +5029,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712591</v>
+        <v>712159</v>
       </c>
       <c r="R39" t="n">
-        <v>6649698</v>
+        <v>6649889</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5110,6 +5100,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5118,16 +5113,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123002544</v>
+        <v>123011797</v>
       </c>
       <c r="B56" t="n">
-        <v>78848</v>
+        <v>98396</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6990,43 +6990,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>711951</v>
+        <v>712581</v>
       </c>
       <c r="R56" t="n">
-        <v>6649783</v>
+        <v>6649757</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7078,17 +7078,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123011797</v>
+        <v>123012181</v>
       </c>
       <c r="B57" t="n">
-        <v>98396</v>
+        <v>97350</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7097,50 +7097,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712581</v>
+        <v>712565</v>
       </c>
       <c r="R57" t="n">
-        <v>6649757</v>
+        <v>6649707</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7196,10 +7187,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123012181</v>
+        <v>123002544</v>
       </c>
       <c r="B58" t="n">
-        <v>97350</v>
+        <v>78848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7208,41 +7199,50 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>637</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712565</v>
+        <v>711951</v>
       </c>
       <c r="R58" t="n">
-        <v>6649707</v>
+        <v>6649783</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123001398</v>
+        <v>122998873</v>
       </c>
       <c r="B19" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,35 +2754,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712451</v>
+        <v>712170</v>
       </c>
       <c r="R19" t="n">
-        <v>6649760</v>
+        <v>6649811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122998873</v>
+        <v>122996823</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2906,16 +2906,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712170</v>
+        <v>712187</v>
       </c>
       <c r="R20" t="n">
-        <v>6649811</v>
+        <v>6650002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2956,6 +2958,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2974,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122996823</v>
+        <v>123001398</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2986,35 +2989,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3022,18 +3025,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712187</v>
+        <v>712451</v>
       </c>
       <c r="R21" t="n">
-        <v>6650002</v>
+        <v>6649760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3074,7 +3075,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998729</v>
+        <v>123007916</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3568,35 +3568,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3604,18 +3604,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712176</v>
+        <v>712142</v>
       </c>
       <c r="R26" t="n">
-        <v>6649818</v>
+        <v>6649796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3656,7 +3654,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3675,10 +3672,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123007916</v>
+        <v>122998729</v>
       </c>
       <c r="B27" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3687,35 +3684,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3723,16 +3720,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712142</v>
+        <v>712176</v>
       </c>
       <c r="R27" t="n">
-        <v>6649796</v>
+        <v>6649818</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3773,6 +3772,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998873</v>
+        <v>123001398</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,35 +2754,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712170</v>
+        <v>712451</v>
       </c>
       <c r="R19" t="n">
-        <v>6649811</v>
+        <v>6649760</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122996823</v>
+        <v>122998873</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2906,18 +2906,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712187</v>
+        <v>712170</v>
       </c>
       <c r="R20" t="n">
-        <v>6650002</v>
+        <v>6649811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,7 +2956,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2977,10 +2974,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123001398</v>
+        <v>122996823</v>
       </c>
       <c r="B21" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,35 +2986,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3025,16 +3022,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712451</v>
+        <v>712187</v>
       </c>
       <c r="R21" t="n">
-        <v>6649760</v>
+        <v>6650002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,6 +3074,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123007916</v>
+        <v>122998729</v>
       </c>
       <c r="B26" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3568,35 +3568,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3604,16 +3604,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712142</v>
+        <v>712176</v>
       </c>
       <c r="R26" t="n">
-        <v>6649796</v>
+        <v>6649818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3654,6 +3656,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3672,10 +3675,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122998729</v>
+        <v>123007916</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3684,35 +3687,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3720,18 +3723,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712176</v>
+        <v>712142</v>
       </c>
       <c r="R27" t="n">
-        <v>6649818</v>
+        <v>6649796</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3772,7 +3773,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123011961</v>
+        <v>123054339</v>
       </c>
       <c r="B38" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,47 +4918,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712591</v>
+        <v>712159</v>
       </c>
       <c r="R38" t="n">
-        <v>6649698</v>
+        <v>6649889</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4993,6 +4989,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5001,26 +5002,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054339</v>
+        <v>123011961</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5029,43 +5035,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712159</v>
+        <v>712591</v>
       </c>
       <c r="R39" t="n">
-        <v>6649889</v>
+        <v>6649698</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5100,11 +5110,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5113,21 +5118,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -4339,10 +4339,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123054333</v>
+        <v>123011797</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4379,27 +4379,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712580</v>
+        <v>712581</v>
       </c>
       <c r="R33" t="n">
-        <v>6649752</v>
+        <v>6649757</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4439,31 +4434,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054336</v>
+        <v>122999379</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>110560</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,52 +4462,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712184</v>
+        <v>711874</v>
       </c>
       <c r="R34" t="n">
-        <v>6649994</v>
+        <v>6649764</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4561,30 +4537,25 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123008808</v>
+        <v>123054338</v>
       </c>
       <c r="B35" t="n">
-        <v>92297</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4593,41 +4564,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712097</v>
+        <v>712174</v>
       </c>
       <c r="R35" t="n">
-        <v>6649846</v>
+        <v>6649978</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4667,26 +4643,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054345</v>
+        <v>123054352</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4718,7 +4699,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4737,10 +4718,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712165</v>
+        <v>712040</v>
       </c>
       <c r="R36" t="n">
-        <v>6649838</v>
+        <v>6649749</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4804,10 +4785,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123008739</v>
+        <v>123054346</v>
       </c>
       <c r="B37" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4816,41 +4797,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712097</v>
+        <v>712166</v>
       </c>
       <c r="R37" t="n">
-        <v>6649846</v>
+        <v>6649838</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4890,26 +4876,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054339</v>
+        <v>123054332</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4918,25 +4909,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4947,14 +4938,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712159</v>
+        <v>712595</v>
       </c>
       <c r="R38" t="n">
-        <v>6649889</v>
+        <v>6649701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4989,11 +4980,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5016,17 +5002,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123011961</v>
+        <v>123054353</v>
       </c>
       <c r="B39" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5056,26 +5042,22 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712591</v>
+        <v>712005</v>
       </c>
       <c r="R39" t="n">
-        <v>6649698</v>
+        <v>6649760</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5119,25 +5101,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054371</v>
+        <v>123054344</v>
       </c>
       <c r="B40" t="n">
-        <v>100662</v>
+        <v>110560</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5150,21 +5137,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5179,10 +5166,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711866</v>
+        <v>712108</v>
       </c>
       <c r="R40" t="n">
-        <v>6649752</v>
+        <v>6649847</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,10 +5233,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123001473</v>
+        <v>123054371</v>
       </c>
       <c r="B41" t="n">
-        <v>78848</v>
+        <v>100680</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5258,49 +5245,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>637</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711936</v>
+        <v>711866</v>
       </c>
       <c r="R41" t="n">
-        <v>6649774</v>
+        <v>6649752</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5335,70 +5316,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054334</v>
+        <v>123008545</v>
       </c>
       <c r="B42" t="n">
-        <v>57857</v>
+        <v>110560</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5411,37 +5361,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712597</v>
+        <v>712097</v>
       </c>
       <c r="R42" t="n">
-        <v>6649817</v>
+        <v>6649846</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5473,11 +5423,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5486,31 +5431,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123003505</v>
+        <v>123054345</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5542,7 +5482,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5550,19 +5490,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712047</v>
+        <v>712165</v>
       </c>
       <c r="R43" t="n">
-        <v>6649756</v>
+        <v>6649838</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5602,26 +5547,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123054351</v>
+        <v>123005529</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5630,55 +5580,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712043</v>
+        <v>712073</v>
       </c>
       <c r="R44" t="n">
-        <v>6649750</v>
+        <v>6649811</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5718,31 +5654,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123054332</v>
+        <v>123008808</v>
       </c>
       <c r="B45" t="n">
-        <v>105502</v>
+        <v>92302</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5755,42 +5686,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712595</v>
+        <v>712097</v>
       </c>
       <c r="R45" t="n">
-        <v>6649701</v>
+        <v>6649846</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5830,31 +5756,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123002458</v>
+        <v>123003467</v>
       </c>
       <c r="B46" t="n">
-        <v>78848</v>
+        <v>98502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5867,48 +5788,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>711934</v>
+        <v>712047</v>
       </c>
       <c r="R46" t="n">
-        <v>6649764</v>
+        <v>6649756</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5940,18 +5850,12 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5963,17 +5867,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123007899</v>
+        <v>123011961</v>
       </c>
       <c r="B47" t="n">
-        <v>97350</v>
+        <v>105518</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5986,37 +5890,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712152</v>
+        <v>712591</v>
       </c>
       <c r="R47" t="n">
-        <v>6649789</v>
+        <v>6649698</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6072,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054347</v>
+        <v>123054339</v>
       </c>
       <c r="B48" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,16 +6018,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6126,10 +6030,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712173</v>
+        <v>712159</v>
       </c>
       <c r="R48" t="n">
-        <v>6649820</v>
+        <v>6649889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6162,6 +6066,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6193,10 +6102,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123054342</v>
+        <v>123002458</v>
       </c>
       <c r="B49" t="n">
-        <v>100662</v>
+        <v>78853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6205,46 +6114,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>637</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712108</v>
+        <v>711934</v>
       </c>
       <c r="R49" t="n">
-        <v>6649846</v>
+        <v>6649764</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6276,39 +6191,40 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122999379</v>
+        <v>123002544</v>
       </c>
       <c r="B50" t="n">
-        <v>110538</v>
+        <v>78853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6317,41 +6233,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>637</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>711874</v>
+        <v>711951</v>
       </c>
       <c r="R50" t="n">
-        <v>6649764</v>
+        <v>6649783</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6400,17 +6325,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123054344</v>
+        <v>123008739</v>
       </c>
       <c r="B51" t="n">
-        <v>110538</v>
+        <v>100680</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6423,42 +6348,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712108</v>
+        <v>712097</v>
       </c>
       <c r="R51" t="n">
-        <v>6649847</v>
+        <v>6649846</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6498,31 +6418,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123003233</v>
+        <v>123012181</v>
       </c>
       <c r="B52" t="n">
-        <v>105502</v>
+        <v>97367</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6535,46 +6450,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712047</v>
+        <v>712565</v>
       </c>
       <c r="R52" t="n">
-        <v>6649756</v>
+        <v>6649707</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6630,10 +6536,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123002982</v>
+        <v>123054336</v>
       </c>
       <c r="B53" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6642,50 +6548,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712017</v>
+        <v>712184</v>
       </c>
       <c r="R53" t="n">
-        <v>6649759</v>
+        <v>6649994</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6725,26 +6636,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123054338</v>
+        <v>123054320</v>
       </c>
       <c r="B54" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6753,43 +6669,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712174</v>
+        <v>712566</v>
       </c>
       <c r="R54" t="n">
-        <v>6649978</v>
+        <v>6649705</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6846,17 +6757,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054352</v>
+        <v>123003233</v>
       </c>
       <c r="B55" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6865,55 +6776,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712040</v>
+        <v>712047</v>
       </c>
       <c r="R55" t="n">
-        <v>6649749</v>
+        <v>6649756</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6953,31 +6859,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123011797</v>
+        <v>123054337</v>
       </c>
       <c r="B56" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7007,29 +6908,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712581</v>
+        <v>712185</v>
       </c>
       <c r="R56" t="n">
-        <v>6649757</v>
+        <v>6649993</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7069,26 +6966,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123012181</v>
+        <v>123054334</v>
       </c>
       <c r="B57" t="n">
-        <v>97350</v>
+        <v>57860</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7101,34 +7003,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712565</v>
+        <v>712597</v>
       </c>
       <c r="R57" t="n">
-        <v>6649707</v>
+        <v>6649817</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7163,6 +7065,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7171,26 +7078,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123002544</v>
+        <v>123001473</v>
       </c>
       <c r="B58" t="n">
-        <v>78848</v>
+        <v>78853</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7222,7 +7134,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7230,19 +7142,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>711951</v>
+        <v>711936</v>
       </c>
       <c r="R58" t="n">
-        <v>6649783</v>
+        <v>6649774</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7274,14 +7188,50 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7298,10 +7248,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054337</v>
+        <v>123054347</v>
       </c>
       <c r="B59" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7331,7 +7281,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7343,10 +7302,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712185</v>
+        <v>712173</v>
       </c>
       <c r="R59" t="n">
-        <v>6649993</v>
+        <v>6649820</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7410,10 +7369,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123008545</v>
+        <v>123054342</v>
       </c>
       <c r="B60" t="n">
-        <v>110538</v>
+        <v>100680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7426,37 +7385,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712097</v>
+        <v>712108</v>
       </c>
       <c r="R60" t="n">
         <v>6649846</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7496,26 +7460,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054353</v>
+        <v>123054351</v>
       </c>
       <c r="B61" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7524,28 +7493,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7557,10 +7535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712005</v>
+        <v>712043</v>
       </c>
       <c r="R61" t="n">
-        <v>6649760</v>
+        <v>6649750</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7624,10 +7602,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123005529</v>
+        <v>123054333</v>
       </c>
       <c r="B62" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7636,41 +7614,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712073</v>
+        <v>712580</v>
       </c>
       <c r="R62" t="n">
-        <v>6649811</v>
+        <v>6649752</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7710,26 +7702,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123054346</v>
+        <v>123007899</v>
       </c>
       <c r="B63" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7738,46 +7735,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712166</v>
+        <v>712152</v>
       </c>
       <c r="R63" t="n">
-        <v>6649838</v>
+        <v>6649789</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7817,31 +7809,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054320</v>
+        <v>123002982</v>
       </c>
       <c r="B64" t="n">
-        <v>97350</v>
+        <v>105518</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7854,37 +7841,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712566</v>
+        <v>712017</v>
       </c>
       <c r="R64" t="n">
-        <v>6649705</v>
+        <v>6649759</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7924,21 +7920,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7948,7 +7939,7 @@
         <v>123054358</v>
       </c>
       <c r="B65" t="n">
-        <v>78848</v>
+        <v>78853</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89254677</v>
+        <v>88192713</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>85000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,47 +1065,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kassjön SO om (*knärot* /stjälk/), Upl</t>
+          <t>Kassjön SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712121.4015056478</v>
+        <v>711995.8186275256</v>
       </c>
       <c r="R5" t="n">
-        <v>6649910.67590899</v>
+        <v>6649792.948826373</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,14 +1122,9 @@
           <t>Väddö</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>AB-Nor-1758</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1147,7 +1134,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1155,11 +1142,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barrskog SO om kassjön, Obskoord: 6649630/1667228/25 m (). /Mängden ej rapporterad.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1169,34 +1151,35 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Betesmark nära bryn i nordsluttning</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Jan Edelsjö, Birgitta Wasstorp, Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Niklas Lönnell, Jan Edelsjö</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88192713</v>
+        <v>88192654</v>
       </c>
       <c r="B6" t="n">
-        <v>85000</v>
+        <v>85004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,21 +1192,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3294</v>
+        <v>3297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Clavulinopsis luteoalba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>(Rea) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1316,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88192654</v>
+        <v>88192841</v>
       </c>
       <c r="B7" t="n">
-        <v>85004</v>
+        <v>86161</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,21 +1315,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3297</v>
+        <v>4394</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aprikosfingersvamp</t>
+          <t>Honungsvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavulinopsis luteoalba</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rea) Corner</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1439,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88192841</v>
+        <v>123008031</v>
       </c>
       <c r="B8" t="n">
-        <v>86161</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,42 +1434,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4394</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kassjön SO-ut, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711995.8186275256</v>
+        <v>712167</v>
       </c>
       <c r="R8" t="n">
-        <v>6649792.948826373</v>
+        <v>6649816</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,22 +1501,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,36 +1527,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Betesmark nära bryn i nordsluttning</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Jan Edelsjö</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008031</v>
+        <v>123000064</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,35 +1555,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1611,10 +1588,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712167</v>
+        <v>712318</v>
       </c>
       <c r="R9" t="n">
-        <v>6649816</v>
+        <v>6649737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,7 +1623,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1656,7 +1633,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,17 +1653,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123000064</v>
+        <v>122999077</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,43 +1672,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712318</v>
+        <v>712127</v>
       </c>
       <c r="R10" t="n">
-        <v>6649737</v>
+        <v>6649778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,46 +1749,37 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122999077</v>
+        <v>122999323</v>
       </c>
       <c r="B11" t="n">
         <v>98396</v>
@@ -1835,7 +1814,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1843,23 +1822,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712127</v>
+        <v>712171</v>
       </c>
       <c r="R11" t="n">
-        <v>6649778</v>
+        <v>6649822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1889,37 +1861,46 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122999323</v>
+        <v>122997739</v>
       </c>
       <c r="B12" t="n">
         <v>98396</v>
@@ -1968,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712171</v>
+        <v>712167</v>
       </c>
       <c r="R12" t="n">
-        <v>6649822</v>
+        <v>6649980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +1994,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,7 +2021,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122997739</v>
+        <v>123008181</v>
       </c>
       <c r="B13" t="n">
         <v>98396</v>
@@ -2075,7 +2056,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2089,10 +2070,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712167</v>
+        <v>712179</v>
       </c>
       <c r="R13" t="n">
-        <v>6649980</v>
+        <v>6649820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2105,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2134,7 +2115,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2154,14 +2135,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008181</v>
+        <v>122997028</v>
       </c>
       <c r="B14" t="n">
         <v>98396</v>
@@ -2196,7 +2177,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2210,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712179</v>
+        <v>712198</v>
       </c>
       <c r="R14" t="n">
-        <v>6649820</v>
+        <v>6650001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2245,7 +2226,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2255,7 +2236,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2275,14 +2256,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122997028</v>
+        <v>123002767</v>
       </c>
       <c r="B15" t="n">
         <v>98396</v>
@@ -2317,7 +2298,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2325,16 +2306,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712198</v>
+        <v>712151</v>
       </c>
       <c r="R15" t="n">
-        <v>6650001</v>
+        <v>6649915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2364,19 +2350,9 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2391,22 +2367,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123002767</v>
+        <v>123000100</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>4776</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,40 +2391,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2457,10 +2424,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712151</v>
+        <v>712304</v>
       </c>
       <c r="R16" t="n">
-        <v>6649915</v>
+        <v>6649724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2519,10 +2486,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123000100</v>
+        <v>123008249</v>
       </c>
       <c r="B17" t="n">
-        <v>4776</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,31 +2498,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2564,10 +2540,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712304</v>
+        <v>712159</v>
       </c>
       <c r="R17" t="n">
-        <v>6649724</v>
+        <v>6649832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2626,10 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123008249</v>
+        <v>123001398</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2638,35 +2614,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2676,14 +2652,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712159</v>
+        <v>712451</v>
       </c>
       <c r="R18" t="n">
-        <v>6649832</v>
+        <v>6649760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2742,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123001398</v>
+        <v>122998873</v>
       </c>
       <c r="B19" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,35 +2730,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2792,14 +2768,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712451</v>
+        <v>712170</v>
       </c>
       <c r="R19" t="n">
-        <v>6649760</v>
+        <v>6649811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2858,7 +2834,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122998873</v>
+        <v>122996823</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2893,7 +2869,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2906,16 +2882,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712170</v>
+        <v>712187</v>
       </c>
       <c r="R20" t="n">
-        <v>6649811</v>
+        <v>6650002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2956,6 +2934,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2974,7 +2953,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122996823</v>
+        <v>123009298</v>
       </c>
       <c r="B21" t="n">
         <v>98396</v>
@@ -3009,7 +2988,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3017,23 +2996,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712187</v>
+        <v>712186</v>
       </c>
       <c r="R21" t="n">
-        <v>6650002</v>
+        <v>6649996</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3063,37 +3035,46 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123009298</v>
+        <v>122998042</v>
       </c>
       <c r="B22" t="n">
         <v>98396</v>
@@ -3128,7 +3109,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3136,16 +3117,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712186</v>
+        <v>712150</v>
       </c>
       <c r="R22" t="n">
-        <v>6649996</v>
+        <v>6649898</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3175,46 +3163,37 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122998042</v>
+        <v>122998128</v>
       </c>
       <c r="B23" t="n">
         <v>98396</v>
@@ -3249,7 +3228,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3262,18 +3241,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712150</v>
+        <v>712162</v>
       </c>
       <c r="R23" t="n">
-        <v>6649898</v>
+        <v>6649897</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3314,7 +3291,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3333,10 +3309,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122998128</v>
+        <v>122997583</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3345,40 +3321,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3387,13 +3354,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712162</v>
+        <v>712166</v>
       </c>
       <c r="R24" t="n">
-        <v>6649897</v>
+        <v>6649973</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3449,10 +3416,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122997583</v>
+        <v>122998729</v>
       </c>
       <c r="B25" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3461,46 +3428,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712166</v>
+        <v>712176</v>
       </c>
       <c r="R25" t="n">
-        <v>6649973</v>
+        <v>6649818</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3538,6 +3516,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3556,10 +3535,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122998729</v>
+        <v>123007916</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3568,35 +3547,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3604,18 +3583,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712176</v>
+        <v>712142</v>
       </c>
       <c r="R26" t="n">
-        <v>6649818</v>
+        <v>6649796</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3656,7 +3633,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3675,10 +3651,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123007916</v>
+        <v>123000056</v>
       </c>
       <c r="B27" t="n">
-        <v>105502</v>
+        <v>97350</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3691,48 +3667,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712142</v>
+        <v>712308</v>
       </c>
       <c r="R27" t="n">
-        <v>6649796</v>
+        <v>6649706</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3791,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123000056</v>
+        <v>122997556</v>
       </c>
       <c r="B28" t="n">
-        <v>97350</v>
+        <v>57503</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3803,38 +3765,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712308</v>
+        <v>712163</v>
       </c>
       <c r="R28" t="n">
-        <v>6649706</v>
+        <v>6649978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3893,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122997556</v>
+        <v>122998889</v>
       </c>
       <c r="B29" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3905,31 +3872,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3938,10 +3914,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712163</v>
+        <v>712161</v>
       </c>
       <c r="R29" t="n">
-        <v>6649978</v>
+        <v>6649804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4000,7 +3976,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122998889</v>
+        <v>123009388</v>
       </c>
       <c r="B30" t="n">
         <v>98396</v>
@@ -4035,7 +4011,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4054,10 +4030,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712161</v>
+        <v>712196</v>
       </c>
       <c r="R30" t="n">
-        <v>6649804</v>
+        <v>6650006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4116,10 +4092,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123009388</v>
+        <v>122999168</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>5174</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4128,40 +4104,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4170,10 +4137,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712196</v>
+        <v>712092</v>
       </c>
       <c r="R31" t="n">
-        <v>6650006</v>
+        <v>6649793</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4232,10 +4199,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122999168</v>
+        <v>123011797</v>
       </c>
       <c r="B32" t="n">
-        <v>5174</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4244,46 +4211,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712092</v>
+        <v>712581</v>
       </c>
       <c r="R32" t="n">
-        <v>6649793</v>
+        <v>6649757</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4327,22 +4298,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123011797</v>
+        <v>122999379</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>110560</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4351,50 +4322,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712581</v>
+        <v>711874</v>
       </c>
       <c r="R33" t="n">
-        <v>6649757</v>
+        <v>6649764</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4450,10 +4412,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122999379</v>
+        <v>123054338</v>
       </c>
       <c r="B34" t="n">
-        <v>110560</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,38 +4424,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711874</v>
+        <v>712174</v>
       </c>
       <c r="R34" t="n">
-        <v>6649764</v>
+        <v>6649978</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,22 +4504,27 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054338</v>
+        <v>123054352</v>
       </c>
       <c r="B35" t="n">
         <v>98502</v>
@@ -4585,7 +4557,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4597,10 +4578,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712174</v>
+        <v>712040</v>
       </c>
       <c r="R35" t="n">
-        <v>6649978</v>
+        <v>6649749</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,7 +4645,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054352</v>
+        <v>123054346</v>
       </c>
       <c r="B36" t="n">
         <v>98502</v>
@@ -4697,16 +4678,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4718,10 +4690,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712040</v>
+        <v>712166</v>
       </c>
       <c r="R36" t="n">
-        <v>6649749</v>
+        <v>6649838</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4785,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054346</v>
+        <v>123054332</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>105518</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4797,25 +4769,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4826,14 +4798,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712166</v>
+        <v>712595</v>
       </c>
       <c r="R37" t="n">
-        <v>6649838</v>
+        <v>6649701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4890,14 +4862,14 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054332</v>
+        <v>123054353</v>
       </c>
       <c r="B38" t="n">
         <v>105518</v>
@@ -4938,14 +4910,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712595</v>
+        <v>712005</v>
       </c>
       <c r="R38" t="n">
-        <v>6649701</v>
+        <v>6649760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5002,17 +4974,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054353</v>
+        <v>123054344</v>
       </c>
       <c r="B39" t="n">
-        <v>105518</v>
+        <v>110560</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5025,21 +4997,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5054,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712005</v>
+        <v>712108</v>
       </c>
       <c r="R39" t="n">
-        <v>6649760</v>
+        <v>6649847</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5121,10 +5093,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054344</v>
+        <v>123054371</v>
       </c>
       <c r="B40" t="n">
-        <v>110560</v>
+        <v>100680</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5137,21 +5109,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5166,10 +5138,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712108</v>
+        <v>711866</v>
       </c>
       <c r="R40" t="n">
-        <v>6649847</v>
+        <v>6649752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5233,10 +5205,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123054371</v>
+        <v>123008545</v>
       </c>
       <c r="B41" t="n">
-        <v>100680</v>
+        <v>110560</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5249,42 +5221,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711866</v>
+        <v>712097</v>
       </c>
       <c r="R41" t="n">
-        <v>6649752</v>
+        <v>6649846</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5324,31 +5291,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123008545</v>
+        <v>123054345</v>
       </c>
       <c r="B42" t="n">
-        <v>110560</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5357,41 +5319,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712097</v>
+        <v>712165</v>
       </c>
       <c r="R42" t="n">
-        <v>6649846</v>
+        <v>6649838</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5431,26 +5407,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123054345</v>
+        <v>123005529</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>97367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5459,55 +5440,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712165</v>
+        <v>712073</v>
       </c>
       <c r="R43" t="n">
-        <v>6649838</v>
+        <v>6649811</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5547,31 +5514,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123005529</v>
+        <v>123008808</v>
       </c>
       <c r="B44" t="n">
-        <v>97367</v>
+        <v>92302</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5584,21 +5546,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5608,10 +5570,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712073</v>
+        <v>712097</v>
       </c>
       <c r="R44" t="n">
-        <v>6649811</v>
+        <v>6649846</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5670,10 +5632,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123008808</v>
+        <v>123003467</v>
       </c>
       <c r="B45" t="n">
-        <v>92302</v>
+        <v>98502</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5682,25 +5644,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5710,10 +5672,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712097</v>
+        <v>712047</v>
       </c>
       <c r="R45" t="n">
-        <v>6649846</v>
+        <v>6649756</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5772,10 +5734,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123003467</v>
+        <v>123011961</v>
       </c>
       <c r="B46" t="n">
-        <v>98502</v>
+        <v>105518</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5784,41 +5746,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712047</v>
+        <v>712591</v>
       </c>
       <c r="R46" t="n">
-        <v>6649756</v>
+        <v>6649698</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5874,10 +5845,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123011961</v>
+        <v>123054339</v>
       </c>
       <c r="B47" t="n">
-        <v>105518</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5886,47 +5857,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712591</v>
+        <v>712159</v>
       </c>
       <c r="R47" t="n">
-        <v>6649698</v>
+        <v>6649889</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5961,6 +5928,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5969,26 +5941,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123054339</v>
+        <v>123002458</v>
       </c>
       <c r="B48" t="n">
-        <v>98502</v>
+        <v>78853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6001,42 +5978,48 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712159</v>
+        <v>711934</v>
       </c>
       <c r="R48" t="n">
-        <v>6649889</v>
+        <v>6649764</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6070,7 +6053,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ymnig.</t>
+          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,30 +6062,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123002458</v>
+        <v>123002544</v>
       </c>
       <c r="B49" t="n">
         <v>78853</v>
@@ -6137,7 +6116,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6145,21 +6124,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>711934</v>
+        <v>711951</v>
       </c>
       <c r="R49" t="n">
-        <v>6649764</v>
+        <v>6649783</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6191,18 +6168,12 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6221,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123002544</v>
+        <v>123008739</v>
       </c>
       <c r="B50" t="n">
-        <v>78853</v>
+        <v>100680</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6233,47 +6204,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>637</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>711951</v>
+        <v>712097</v>
       </c>
       <c r="R50" t="n">
-        <v>6649783</v>
+        <v>6649846</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6325,17 +6287,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123008739</v>
+        <v>123012181</v>
       </c>
       <c r="B51" t="n">
-        <v>100680</v>
+        <v>97367</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6348,37 +6310,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712097</v>
+        <v>712565</v>
       </c>
       <c r="R51" t="n">
-        <v>6649846</v>
+        <v>6649707</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6434,10 +6396,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123012181</v>
+        <v>123054336</v>
       </c>
       <c r="B52" t="n">
-        <v>97367</v>
+        <v>98502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6446,38 +6408,52 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712565</v>
+        <v>712184</v>
       </c>
       <c r="R52" t="n">
-        <v>6649707</v>
+        <v>6649994</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6521,25 +6497,30 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123054336</v>
+        <v>123054320</v>
       </c>
       <c r="B53" t="n">
-        <v>98502</v>
+        <v>97367</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6548,52 +6529,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712184</v>
+        <v>712566</v>
       </c>
       <c r="R53" t="n">
-        <v>6649994</v>
+        <v>6649705</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6650,17 +6617,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123054320</v>
+        <v>123003233</v>
       </c>
       <c r="B54" t="n">
-        <v>97367</v>
+        <v>105518</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6673,37 +6640,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712566</v>
+        <v>712047</v>
       </c>
       <c r="R54" t="n">
-        <v>6649705</v>
+        <v>6649756</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6743,31 +6719,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123003233</v>
+        <v>123054337</v>
       </c>
       <c r="B55" t="n">
-        <v>105518</v>
+        <v>98502</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6776,50 +6747,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712047</v>
+        <v>712185</v>
       </c>
       <c r="R55" t="n">
-        <v>6649756</v>
+        <v>6649993</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6859,26 +6826,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123054337</v>
+        <v>123054334</v>
       </c>
       <c r="B56" t="n">
-        <v>98502</v>
+        <v>57860</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6887,43 +6859,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712185</v>
+        <v>712597</v>
       </c>
       <c r="R56" t="n">
-        <v>6649993</v>
+        <v>6649817</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6958,6 +6925,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6980,17 +6952,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123054334</v>
+        <v>123001473</v>
       </c>
       <c r="B57" t="n">
-        <v>57860</v>
+        <v>78853</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,38 +6971,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>637</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712597</v>
+        <v>711936</v>
       </c>
       <c r="R57" t="n">
-        <v>6649817</v>
+        <v>6649774</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7067,7 +7050,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Läte.</t>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7076,33 +7059,59 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123001473</v>
+        <v>123054347</v>
       </c>
       <c r="B58" t="n">
-        <v>78853</v>
+        <v>98502</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7115,45 +7124,48 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>711936</v>
+        <v>712173</v>
       </c>
       <c r="R58" t="n">
-        <v>6649774</v>
+        <v>6649820</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7188,70 +7200,39 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054347</v>
+        <v>123054342</v>
       </c>
       <c r="B59" t="n">
-        <v>98502</v>
+        <v>100680</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7260,37 +7241,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7302,10 +7274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712173</v>
+        <v>712108</v>
       </c>
       <c r="R59" t="n">
-        <v>6649820</v>
+        <v>6649846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7369,10 +7341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054342</v>
+        <v>123054351</v>
       </c>
       <c r="B60" t="n">
-        <v>100680</v>
+        <v>98502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7381,28 +7353,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7414,10 +7395,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712108</v>
+        <v>712043</v>
       </c>
       <c r="R60" t="n">
-        <v>6649846</v>
+        <v>6649750</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7481,7 +7462,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054351</v>
+        <v>123054333</v>
       </c>
       <c r="B61" t="n">
         <v>98502</v>
@@ -7516,7 +7497,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7531,14 +7512,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712043</v>
+        <v>712580</v>
       </c>
       <c r="R61" t="n">
-        <v>6649750</v>
+        <v>6649752</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7595,17 +7576,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123054333</v>
+        <v>123007899</v>
       </c>
       <c r="B62" t="n">
-        <v>98502</v>
+        <v>97367</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7614,55 +7595,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712580</v>
+        <v>712152</v>
       </c>
       <c r="R62" t="n">
-        <v>6649752</v>
+        <v>6649789</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7702,31 +7669,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123007899</v>
+        <v>123002982</v>
       </c>
       <c r="B63" t="n">
-        <v>97367</v>
+        <v>105518</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7739,34 +7701,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712152</v>
+        <v>712017</v>
       </c>
       <c r="R63" t="n">
-        <v>6649789</v>
+        <v>6649759</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7825,10 +7796,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123002982</v>
+        <v>123054358</v>
       </c>
       <c r="B64" t="n">
-        <v>105518</v>
+        <v>78855</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7837,50 +7808,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>637</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712017</v>
+        <v>711929</v>
       </c>
       <c r="R64" t="n">
-        <v>6649759</v>
+        <v>6649767</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7912,6 +7883,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7920,140 +7896,24 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>123054358</v>
-      </c>
-      <c r="B65" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>637</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Ringlav</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Evernia divaricata</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Kassjön, O-SO om, Upl</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>711929</v>
-      </c>
-      <c r="R65" t="n">
-        <v>6649767</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Väddö</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8021,7 +8021,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mats Nordin, Karolina Wallin</t>
+          <t>Karolina Wallin, Mats Nordin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8021,7 +8021,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karolina Wallin, Mats Nordin</t>
+          <t>Mats Nordin, Karolina Wallin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8026,6 +8026,1104 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128594071</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90927</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>720</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gåsvik, barrnaturskog , Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>712053</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6649813</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128594356</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kvarån, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>712002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6649782</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128595580</v>
+      </c>
+      <c r="B68" t="n">
+        <v>86944</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gåsvik, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>711862</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6649764</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128593847</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kvarån, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>712118</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6649926</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>En meter utanför stängslet.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128593978</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92744</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>788</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kvarån, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>712097</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6649840</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128594811</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90988</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fläckfingersvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramaria sanguinea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gåsvik, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>711903</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6649776</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128595026</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86716</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gåsvik, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>711988</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6649770</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128594434</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kvarån, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>711898</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6649780</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128594725</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86878</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kvarån, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>711867</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6649773</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128595009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92750</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gåsvik, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>711986</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6649779</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128596191</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86807</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Porslinsblå spindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius cumatilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gåsvik, Kvarån, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>712010</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6649788</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Åtta fruktkroppar. Runt liten gran i beteshagen. Grön i UV-ljus.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90927</v>
+        <v>90933</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>90987</v>
+        <v>90993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92744</v>
+        <v>92750</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>90988</v>
+        <v>90994</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86716</v>
+        <v>86721</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86878</v>
+        <v>86882</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86807</v>
+        <v>86811</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90933</v>
+        <v>90939</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>90993</v>
+        <v>90999</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>90994</v>
+        <v>91000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86721</v>
+        <v>86727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86882</v>
+        <v>86888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92756</v>
+        <v>92762</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86811</v>
+        <v>86817</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86954</v>
+        <v>86956</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91000</v>
+        <v>91002</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92762</v>
+        <v>92764</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91002</v>
+        <v>91003</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91003</v>
+        <v>91030</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86819</v>
+        <v>86846</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92786</v>
+        <v>92791</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91030</v>
+        <v>91035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86846</v>
+        <v>86850</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90974</v>
+        <v>90979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91035</v>
+        <v>91040</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92796</v>
+        <v>92800</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91040</v>
+        <v>91044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86850</v>
+        <v>86854</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91044</v>
+        <v>91049</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128595009</v>
       </c>
       <c r="B75" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>128596191</v>
       </c>
       <c r="B76" t="n">
-        <v>86854</v>
+        <v>86859</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90990</v>
+        <v>90995</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91050</v>
+        <v>91055</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92808</v>
+        <v>92813</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91051</v>
+        <v>91056</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86771</v>
+        <v>86776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86933</v>
+        <v>86938</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128596191</v>
       </c>
       <c r="B75" t="n">
-        <v>86861</v>
+        <v>86866</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8031,7 +8031,7 @@
         <v>128594071</v>
       </c>
       <c r="B66" t="n">
-        <v>90995</v>
+        <v>91001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>128594356</v>
       </c>
       <c r="B67" t="n">
-        <v>91055</v>
+        <v>91061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>128595580</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>128593847</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>128593978</v>
       </c>
       <c r="B70" t="n">
-        <v>92813</v>
+        <v>92821</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91056</v>
+        <v>91062</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
         <v>128595026</v>
       </c>
       <c r="B72" t="n">
-        <v>86776</v>
+        <v>86782</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8732,7 +8732,7 @@
         <v>128594434</v>
       </c>
       <c r="B73" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>128594725</v>
       </c>
       <c r="B74" t="n">
-        <v>86938</v>
+        <v>86944</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         <v>128596191</v>
       </c>
       <c r="B75" t="n">
-        <v>86866</v>
+        <v>86872</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92834</v>
+        <v>92841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92841</v>
+        <v>92843</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92843</v>
+        <v>92829</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92829</v>
+        <v>92830</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92835</v>
+        <v>92839</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92839</v>
+        <v>92840</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -9032,7 +9032,7 @@
         <v>128595009</v>
       </c>
       <c r="B76" t="n">
-        <v>92843</v>
+        <v>92871</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91062</v>
+        <v>91355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91355</v>
+        <v>91356</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Karin Wiklund, Fatimah Fazal, Joakim Ekman</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91359</v>
+        <v>91365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91365</v>
+        <v>91368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91368</v>
+        <v>91373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91373</v>
+        <v>91375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
+          <t>Joakim Ekman, Fae Fazal, Karin Wiklund, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8625,7 +8625,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Fae Fazal, Karin Wiklund, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -8538,7 +8538,7 @@
         <v>128594811</v>
       </c>
       <c r="B71" t="n">
-        <v>91416</v>
+        <v>91419</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61839173</v>
+        <v>123001473</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>637</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kassjön SO-ut, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711963.0032964781</v>
+        <v>711936</v>
       </c>
       <c r="R2" t="n">
-        <v>6649786.042014163</v>
+        <v>6649774</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Naturbetesmark.</t>
+          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,76 +770,108 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Naturbetesmark, öppen</t>
+          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>även några bålar på björk.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # även några bålar på björk.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78836213</v>
+        <v>123002458</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kassjön, O om, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711962.9170978669</v>
+        <v>711934</v>
       </c>
       <c r="R3" t="n">
-        <v>6649787.544141024</v>
+        <v>6649764</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,66 +895,48 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsbryn. Naturbetesmark.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>BSIS - Floraväkteri-exkursion</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88726494</v>
+        <v>123002544</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,41 +944,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrskog SO om kassjön, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712121.3727509676</v>
+        <v>711951</v>
       </c>
       <c r="R4" t="n">
-        <v>6649911.176601575</v>
+        <v>6649783</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +1007,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,77 +1021,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Jan Edelsjö, Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88192713</v>
+        <v>123054358</v>
       </c>
       <c r="B5" t="n">
-        <v>85000</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3294</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kassjön SO-ut, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711995.8186275256</v>
+        <v>711929</v>
       </c>
       <c r="R5" t="n">
-        <v>6649792.948826373</v>
+        <v>6649767</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1113,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,76 +1135,68 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Betesmark nära bryn i nordsluttning</t>
+          <t>Kalkbarrskog - mest gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Jan Edelsjö</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88192654</v>
+        <v>124420481</v>
       </c>
       <c r="B6" t="n">
-        <v>85004</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3297</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aprikosfingersvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Clavulinopsis luteoalba</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Rea) Corner</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kassjön SO-ut, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711995.8186275256</v>
+        <v>711926</v>
       </c>
       <c r="R6" t="n">
-        <v>6649792.948826373</v>
+        <v>6649771</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1247,106 +1223,86 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Som närmst skogsbrynet 6-7 meter. I kikare sågs sannolik ringlav på åtminstone 5 meters höjd i gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Betesmark nära bryn i nordsluttning</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Mats Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Jan Edelsjö</t>
+          <t>Mats Nordin, Karolina Wallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88192841</v>
+        <v>128594071</v>
       </c>
       <c r="B7" t="n">
-        <v>86161</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4394</v>
+        <v>720</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kassjön SO-ut, Upl</t>
+          <t>Gåsvik, barrnaturskog , Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711995.8186275256</v>
+        <v>712053</v>
       </c>
       <c r="R7" t="n">
-        <v>6649792.948826373</v>
+        <v>6649813</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,22 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,85 +1342,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Betesmark nära bryn i nordsluttning</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Jan Edelsjö</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123008031</v>
+        <v>128595186</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>720</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712167</v>
+        <v>711905</v>
       </c>
       <c r="R8" t="n">
-        <v>6649816</v>
+        <v>6649784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,22 +1423,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,67 +1443,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123000064</v>
+        <v>128593978</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712318</v>
+        <v>712097</v>
       </c>
       <c r="R9" t="n">
-        <v>6649737</v>
+        <v>6649840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,22 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,27 +1540,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122999077</v>
+        <v>128594811</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,50 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712127</v>
+        <v>711903</v>
       </c>
       <c r="R10" t="n">
-        <v>6649778</v>
+        <v>6649776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,12 +1617,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,7 +1631,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1772,22 +1642,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122999323</v>
+        <v>128596191</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,43 +1660,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1980</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712171</v>
+        <v>712010</v>
       </c>
       <c r="R11" t="n">
-        <v>6649822</v>
+        <v>6649788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,22 +1717,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Åtta fruktkroppar. Runt liten gran i beteshagen. Grön i UV-ljus.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,77 +1736,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122997739</v>
+        <v>128595009</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2058</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712167</v>
+        <v>711986</v>
       </c>
       <c r="R12" t="n">
-        <v>6649980</v>
+        <v>6649779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,22 +1820,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2009,74 +1840,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008181</v>
+        <v>88192713</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>3294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712179</v>
+        <v>711996</v>
       </c>
       <c r="R13" t="n">
-        <v>6649820</v>
+        <v>6649793</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2100,22 +1918,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,78 +1934,75 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Betesmark nära bryn i nordsluttning</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Niklas Lönnell, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122997028</v>
+        <v>88192654</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavulinopsis luteoalba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Rea) Corner</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712198</v>
+        <v>711996</v>
       </c>
       <c r="R14" t="n">
-        <v>6650001</v>
+        <v>6649793</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2221,106 +2026,87 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Betesmark nära bryn i nordsluttning</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Niklas Lönnell, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123002767</v>
+        <v>128594725</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712151</v>
+        <v>711867</v>
       </c>
       <c r="R15" t="n">
-        <v>6649915</v>
+        <v>6649773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,12 +2133,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,62 +2158,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123000100</v>
+        <v>128595580</v>
       </c>
       <c r="B16" t="n">
-        <v>4776</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>3739</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712304</v>
+        <v>711862</v>
       </c>
       <c r="R16" t="n">
-        <v>6649724</v>
+        <v>6649764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,12 +2230,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,71 +2255,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008249</v>
+        <v>128595026</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Gåsvik, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712159</v>
+        <v>711988</v>
       </c>
       <c r="R17" t="n">
-        <v>6649832</v>
+        <v>6649770</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,12 +2327,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2595,71 +2352,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123001398</v>
+        <v>128594434</v>
       </c>
       <c r="B18" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Smedjebacken, Smedjebacken, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712451</v>
+        <v>711898</v>
       </c>
       <c r="R18" t="n">
-        <v>6649760</v>
+        <v>6649780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2686,12 +2424,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,74 +2449,55 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122998873</v>
+        <v>128620434</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712170</v>
+        <v>712008</v>
       </c>
       <c r="R19" t="n">
-        <v>6649811</v>
+        <v>6649818</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2802,12 +2521,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,69 +2563,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122996823</v>
+        <v>88192841</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4394</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712187</v>
+        <v>711996</v>
       </c>
       <c r="R20" t="n">
-        <v>6650002</v>
+        <v>6649793</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2920,12 +2629,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2934,78 +2643,73 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Betesmark nära bryn i nordsluttning</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Niklas Lönnell, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123009298</v>
+        <v>128594652</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5741</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712186</v>
+        <v>711865</v>
       </c>
       <c r="R21" t="n">
-        <v>6649996</v>
+        <v>6649729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3032,22 +2736,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3062,27 +2756,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122998042</v>
+        <v>128594356</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3090,50 +2779,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712150</v>
+        <v>712002</v>
       </c>
       <c r="R22" t="n">
-        <v>6649898</v>
+        <v>6649782</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,12 +2833,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,7 +2847,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3186,74 +2858,55 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122998128</v>
+        <v>123008808</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712162</v>
+        <v>712097</v>
       </c>
       <c r="R23" t="n">
-        <v>6649897</v>
+        <v>6649846</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3297,27 +2950,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122997583</v>
+        <v>88779583</v>
       </c>
       <c r="B24" t="n">
-        <v>57857</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,42 +2973,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6254</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hårjordtunga</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Trichoglossum hirsutum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Boud.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Kassjön O, naturbetesmark, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712166</v>
+        <v>712032</v>
       </c>
       <c r="R24" t="n">
-        <v>6649973</v>
+        <v>6649980</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3384,12 +3027,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>rikligt, sporer 15-septerade</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,82 +3048,76 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>Jan Edelsjö</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>JE-2840</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Edelsjö</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Edelsjö, Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122998729</v>
+        <v>123054315</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712176</v>
+        <v>712393</v>
       </c>
       <c r="R25" t="n">
-        <v>6649818</v>
+        <v>6649681</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,40 +3152,44 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På basen av gran i fuktig granskog.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123007916</v>
+        <v>122997556</v>
       </c>
       <c r="B26" t="n">
-        <v>105502</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3551,36 +3197,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3589,10 +3226,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712142</v>
+        <v>712163</v>
       </c>
       <c r="R26" t="n">
-        <v>6649796</v>
+        <v>6649978</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3651,15 +3288,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123000056</v>
+        <v>122999168</v>
       </c>
       <c r="B27" t="n">
-        <v>97350</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3667,34 +3299,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712308</v>
+        <v>712092</v>
       </c>
       <c r="R27" t="n">
-        <v>6649706</v>
+        <v>6649793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3753,43 +3390,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122997556</v>
+        <v>123000100</v>
       </c>
       <c r="B28" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3798,10 +3430,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>712163</v>
+        <v>712304</v>
       </c>
       <c r="R28" t="n">
-        <v>6649978</v>
+        <v>6649724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3860,52 +3492,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122998889</v>
+        <v>122997583</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3914,13 +3532,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712161</v>
+        <v>712166</v>
       </c>
       <c r="R29" t="n">
-        <v>6649804</v>
+        <v>6649973</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3976,52 +3594,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123009388</v>
+        <v>123000064</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4030,10 +3634,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712196</v>
+        <v>712318</v>
       </c>
       <c r="R30" t="n">
-        <v>6650006</v>
+        <v>6649737</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,9 +3667,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4080,27 +3694,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122999168</v>
+        <v>123054334</v>
       </c>
       <c r="B31" t="n">
-        <v>5174</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,39 +3717,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnån, Kvarnån, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712092</v>
+        <v>712597</v>
       </c>
       <c r="R31" t="n">
-        <v>6649793</v>
+        <v>6649817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4175,6 +3779,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4183,78 +3792,69 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123011797</v>
+        <v>122999379</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712581</v>
+        <v>711874</v>
       </c>
       <c r="R32" t="n">
-        <v>6649757</v>
+        <v>6649764</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4310,19 +3910,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122999379</v>
+        <v>123008545</v>
       </c>
       <c r="B33" t="n">
-        <v>110560</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4350,13 +3945,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711874</v>
+        <v>712097</v>
       </c>
       <c r="R33" t="n">
-        <v>6649764</v>
+        <v>6649846</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4412,37 +4007,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123054338</v>
+        <v>123054344</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4457,10 +4047,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>712174</v>
+        <v>712108</v>
       </c>
       <c r="R34" t="n">
-        <v>6649978</v>
+        <v>6649847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4524,64 +4114,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123054352</v>
+        <v>60861108</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön O om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712040</v>
+        <v>711966</v>
       </c>
       <c r="R35" t="n">
-        <v>6649749</v>
+        <v>6649794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4608,12 +4184,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-07-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-07-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 stor planta</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,7 +4208,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Ängsmark</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4638,47 +4219,51 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123054346</v>
+        <v>61612201</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4686,17 +4271,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, naturbetesmark SO om O-änden, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712166</v>
+        <v>711963</v>
       </c>
       <c r="R36" t="n">
-        <v>6649838</v>
+        <v>6649797</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4720,12 +4305,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-05-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-05-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,76 +4334,80 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Frisk öppen naturbetesmark</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123054332</v>
+        <v>61839173</v>
       </c>
       <c r="B37" t="n">
-        <v>105518</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>220204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712595</v>
+        <v>711963</v>
       </c>
       <c r="R37" t="n">
-        <v>6649701</v>
+        <v>6649786</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4832,12 +4431,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-07-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2016-07-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4851,73 +4465,77 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Naturbetesmark, öppen</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123054353</v>
+        <v>78836215</v>
       </c>
       <c r="B38" t="n">
-        <v>105518</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kassjön, O om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712005</v>
+        <v>711962</v>
       </c>
       <c r="R38" t="n">
-        <v>6649760</v>
+        <v>6649800</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4944,12 +4562,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2019-07-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2019-07-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4963,7 +4581,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog - mest gran</t>
+          <t>Skogsbryn. Naturbetesmark.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4974,65 +4592,63 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Jan Yngve Andersson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123054344</v>
+        <v>88726494</v>
       </c>
       <c r="B39" t="n">
-        <v>110560</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Barrskog SO om kassjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712108</v>
+        <v>712121</v>
       </c>
       <c r="R39" t="n">
-        <v>6649847</v>
+        <v>6649911</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5056,12 +4672,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5070,78 +4686,84 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Jan Edelsjö, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123054371</v>
+        <v>122996823</v>
       </c>
       <c r="B40" t="n">
-        <v>100680</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711866</v>
+        <v>712187</v>
       </c>
       <c r="R40" t="n">
-        <v>6649752</v>
+        <v>6650002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5182,76 +4804,76 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123008545</v>
+        <v>122997028</v>
       </c>
       <c r="B41" t="n">
-        <v>110560</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>712097</v>
+        <v>712198</v>
       </c>
       <c r="R41" t="n">
-        <v>6649846</v>
+        <v>6650001</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5278,9 +4900,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,27 +4927,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123054345</v>
+        <v>122997739</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,21 +4977,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712165</v>
+        <v>712167</v>
       </c>
       <c r="R42" t="n">
-        <v>6649838</v>
+        <v>6649980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,11 +5016,21 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5407,74 +5039,80 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123005529</v>
+        <v>122998042</v>
       </c>
       <c r="B43" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712073</v>
+        <v>712150</v>
       </c>
       <c r="R43" t="n">
-        <v>6649811</v>
+        <v>6649898</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5512,71 +5150,81 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123008808</v>
+        <v>122998128</v>
       </c>
       <c r="B44" t="n">
-        <v>92302</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712097</v>
+        <v>712162</v>
       </c>
       <c r="R44" t="n">
-        <v>6649846</v>
+        <v>6649897</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5620,27 +5268,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123003467</v>
+        <v>122998729</v>
       </c>
       <c r="B45" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5665,20 +5308,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712047</v>
+        <v>712176</v>
       </c>
       <c r="R45" t="n">
-        <v>6649756</v>
+        <v>6649818</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5716,77 +5375,78 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123011961</v>
+        <v>122998873</v>
       </c>
       <c r="B46" t="n">
-        <v>105518</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712591</v>
+        <v>712170</v>
       </c>
       <c r="R46" t="n">
-        <v>6649698</v>
+        <v>6649811</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5833,27 +5493,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123054339</v>
+        <v>122998889</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5878,7 +5533,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -5886,14 +5550,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712159</v>
+        <v>712161</v>
       </c>
       <c r="R47" t="n">
-        <v>6649889</v>
+        <v>6649804</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5928,11 +5592,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ymnig.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5941,36 +5600,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123002458</v>
+        <v>122999077</v>
       </c>
       <c r="B48" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,48 +5627,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>711934</v>
+        <v>712127</v>
       </c>
       <c r="R48" t="n">
-        <v>6649764</v>
+        <v>6649778</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6049,11 +5703,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>7 bålar på 3 granar (1 på marken).</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6069,27 +5718,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123002544</v>
+        <v>122999323</v>
       </c>
       <c r="B49" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6097,21 +5741,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6121,22 +5765,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>711951</v>
+        <v>712171</v>
       </c>
       <c r="R49" t="n">
-        <v>6649783</v>
+        <v>6649822</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6163,9 +5807,19 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6180,65 +5834,74 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123008739</v>
+        <v>123002767</v>
       </c>
       <c r="B50" t="n">
-        <v>100680</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712097</v>
+        <v>712151</v>
       </c>
       <c r="R50" t="n">
-        <v>6649846</v>
+        <v>6649915</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6282,65 +5945,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123012181</v>
+        <v>123003467</v>
       </c>
       <c r="B51" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Smedjebacken, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712565</v>
+        <v>712047</v>
       </c>
       <c r="R51" t="n">
-        <v>6649707</v>
+        <v>6649756</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6396,15 +6054,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123054336</v>
+        <v>123008031</v>
       </c>
       <c r="B52" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6431,7 +6084,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6439,21 +6092,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712184</v>
+        <v>712167</v>
       </c>
       <c r="R52" t="n">
-        <v>6649994</v>
+        <v>6649816</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6483,11 +6131,21 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6496,71 +6154,70 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123054320</v>
+        <v>123008181</v>
       </c>
       <c r="B53" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712566</v>
+        <v>712179</v>
       </c>
       <c r="R53" t="n">
-        <v>6649705</v>
+        <v>6649820</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6590,11 +6247,21 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6603,83 +6270,78 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123003233</v>
+        <v>123008249</v>
       </c>
       <c r="B54" t="n">
-        <v>105518</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712047</v>
+        <v>712159</v>
       </c>
       <c r="R54" t="n">
-        <v>6649756</v>
+        <v>6649832</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6723,27 +6385,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123054337</v>
+        <v>123009298</v>
       </c>
       <c r="B55" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6768,22 +6425,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712185</v>
+        <v>712186</v>
       </c>
       <c r="R55" t="n">
-        <v>6649993</v>
+        <v>6649996</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,11 +6474,21 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6826,71 +6497,75 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123054334</v>
+        <v>123009388</v>
       </c>
       <c r="B56" t="n">
-        <v>57860</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712597</v>
+        <v>712196</v>
       </c>
       <c r="R56" t="n">
-        <v>6649817</v>
+        <v>6650006</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6925,11 +6600,6 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Läte.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6938,36 +6608,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog - mest gran</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123001473</v>
+        <v>123011797</v>
       </c>
       <c r="B57" t="n">
-        <v>78853</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6975,48 +6635,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>711936</v>
+        <v>712581</v>
       </c>
       <c r="R57" t="n">
-        <v>6649774</v>
+        <v>6649757</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7048,50 +6706,14 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>39 bålar på 17 träd inom 25 × 25 meter kring lodyta. Både söder och norr om lodytans västra del. Några bålar på marken. 2 björkar resten av träden gran. 3 granar döda resten levande (en del senvuxna smågranar).</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kring lodyta i nordsluttande bitvis kalkpåverkad granskog med lång kontinuitet.</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>även några bålar på björk.</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # även några bålar på björk.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7101,22 +6723,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123054347</v>
+        <v>123054333</v>
       </c>
       <c r="B58" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7143,7 +6760,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7158,14 +6775,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kassjön, O-SO om, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712173</v>
+        <v>712580</v>
       </c>
       <c r="R58" t="n">
-        <v>6649820</v>
+        <v>6649752</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7222,47 +6839,51 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123054342</v>
+        <v>123054336</v>
       </c>
       <c r="B59" t="n">
-        <v>100680</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7274,10 +6895,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712108</v>
+        <v>712184</v>
       </c>
       <c r="R59" t="n">
-        <v>6649846</v>
+        <v>6649994</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,15 +6962,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123054351</v>
+        <v>123054337</v>
       </c>
       <c r="B60" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,16 +6990,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7395,10 +7002,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712043</v>
+        <v>712185</v>
       </c>
       <c r="R60" t="n">
-        <v>6649750</v>
+        <v>6649993</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7462,15 +7069,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123054333</v>
+        <v>123054338</v>
       </c>
       <c r="B61" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7495,16 +7097,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7512,14 +7105,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Charlottenberg, V om, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712580</v>
+        <v>712174</v>
       </c>
       <c r="R61" t="n">
-        <v>6649752</v>
+        <v>6649978</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7576,60 +7169,60 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123007899</v>
+        <v>123054339</v>
       </c>
       <c r="B62" t="n">
-        <v>97367</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712152</v>
+        <v>712159</v>
       </c>
       <c r="R62" t="n">
-        <v>6649789</v>
+        <v>6649889</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7661,6 +7254,11 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ymnig.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7669,78 +7267,83 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123002982</v>
+        <v>123054345</v>
       </c>
       <c r="B63" t="n">
-        <v>105518</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712017</v>
+        <v>712165</v>
       </c>
       <c r="R63" t="n">
-        <v>6649759</v>
+        <v>6649838</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7780,31 +7383,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123054358</v>
+        <v>123054346</v>
       </c>
       <c r="B64" t="n">
-        <v>78877</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7812,31 +7415,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7845,10 +7444,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>711929</v>
+        <v>712166</v>
       </c>
       <c r="R64" t="n">
-        <v>6649767</v>
+        <v>6649838</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7881,11 +7480,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På björk och gran. Totalt på 10 träd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7917,15 +7511,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124420481</v>
+        <v>123054347</v>
       </c>
       <c r="B65" t="n">
-        <v>78877</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7933,40 +7522,51 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kassjön, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>711926</v>
+        <v>712173</v>
       </c>
       <c r="R65" t="n">
-        <v>6649771</v>
+        <v>6649820</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7990,17 +7590,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Som närmst skogsbrynet 6-7 meter. I kikare sågs sannolik ringlav på åtminstone 5 meters höjd i gran.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8009,29 +7604,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mats Nordin</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mats Nordin, Karolina Wallin</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128594071</v>
+        <v>123054351</v>
       </c>
       <c r="B66" t="n">
-        <v>91001</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8039,34 +7638,48 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>720</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gåsvik, barrnaturskog , Kvarån, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>712053</v>
+        <v>712043</v>
       </c>
       <c r="R66" t="n">
-        <v>6649813</v>
+        <v>6649750</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8093,12 +7706,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8109,26 +7722,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128594356</v>
+        <v>123054352</v>
       </c>
       <c r="B67" t="n">
-        <v>91061</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8136,34 +7754,48 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kvarån, Kvarån, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712002</v>
+        <v>712040</v>
       </c>
       <c r="R67" t="n">
-        <v>6649782</v>
+        <v>6649749</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8190,12 +7822,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8206,61 +7838,82 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128595580</v>
+        <v>128593847</v>
       </c>
       <c r="B68" t="n">
-        <v>87010</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3739</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gåsvik, Kvarån, Upl</t>
+          <t>Kvarån, Kvarån, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>711862</v>
+        <v>712118</v>
       </c>
       <c r="R68" t="n">
-        <v>6649764</v>
+        <v>6649926</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8295,12 +7948,18 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>En meter utanför stängslet.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8312,49 +7971,49 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128593847</v>
+        <v>123001398</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>106244</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8362,18 +8021,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarån, Kvarån, Upl</t>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712118</v>
+        <v>712451</v>
       </c>
       <c r="R69" t="n">
-        <v>6649926</v>
+        <v>6649760</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8400,17 +8057,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>En meter utanför stängslet.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8419,7 +8071,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8431,55 +8082,64 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128593978</v>
+        <v>123002982</v>
       </c>
       <c r="B70" t="n">
-        <v>92821</v>
+        <v>106244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>788</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarån, Kvarån, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712097</v>
+        <v>712017</v>
       </c>
       <c r="R70" t="n">
-        <v>6649840</v>
+        <v>6649759</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8503,12 +8163,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8523,60 +8183,69 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128594811</v>
+        <v>123003233</v>
       </c>
       <c r="B71" t="n">
-        <v>91419</v>
+        <v>106244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1357</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gåsvik, Kvarån, Upl</t>
+          <t>Kassjön, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>711903</v>
+        <v>712047</v>
       </c>
       <c r="R71" t="n">
-        <v>6649776</v>
+        <v>6649756</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8600,12 +8269,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8620,22 +8289,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fae Fazal, Karin Wiklund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128595026</v>
+        <v>123007916</v>
       </c>
       <c r="B72" t="n">
-        <v>86782</v>
+        <v>106244</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8643,34 +8312,48 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3762</v>
+        <v>221144</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gåsvik, Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>711988</v>
+        <v>712142</v>
       </c>
       <c r="R72" t="n">
-        <v>6649770</v>
+        <v>6649796</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8697,12 +8380,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8722,17 +8405,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128594434</v>
+        <v>123011961</v>
       </c>
       <c r="B73" t="n">
-        <v>92831</v>
+        <v>106244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,34 +8423,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kvarån, Kvarån, Upl</t>
+          <t>Smedjebacken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>711898</v>
+        <v>712591</v>
       </c>
       <c r="R73" t="n">
-        <v>6649780</v>
+        <v>6649698</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8794,12 +8486,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8814,22 +8506,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128594725</v>
+        <v>123054332</v>
       </c>
       <c r="B74" t="n">
-        <v>86944</v>
+        <v>106244</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8837,34 +8529,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3674</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarån, Kvarån, Upl</t>
+          <t>Charlottenberg, V om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>711867</v>
+        <v>712595</v>
       </c>
       <c r="R74" t="n">
-        <v>6649773</v>
+        <v>6649701</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8891,12 +8588,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8907,64 +8604,71 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128596191</v>
+        <v>123054353</v>
       </c>
       <c r="B75" t="n">
-        <v>86872</v>
+        <v>106244</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1980</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gåsvik, Kvarån, Upl</t>
+          <t>Kassjön, O-SO om, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712010</v>
+        <v>712005</v>
       </c>
       <c r="R75" t="n">
-        <v>6649788</v>
+        <v>6649760</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8991,17 +8695,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Åtta fruktkroppar. Runt liten gran i beteshagen. Grön i UV-ljus.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9010,64 +8709,68 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Fatimah Fazal, Karin Wiklund, Liam Sebestyén</t>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128595009</v>
+        <v>123000056</v>
       </c>
       <c r="B76" t="n">
-        <v>92871</v>
+        <v>97983</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2058</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gåsvik, Kvarån, Upl</t>
+          <t>Kvarnån, Kvarnån, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>711986</v>
+        <v>712308</v>
       </c>
       <c r="R76" t="n">
-        <v>6649779</v>
+        <v>6649706</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9094,12 +8797,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9119,10 +8822,1806 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Joakim Ekman, Fatimah Fazal, Karin Wiklund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123000217</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>712358</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6649684</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123005529</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>712073</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6649811</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123007899</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>712152</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6649789</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123012181</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Smedjebacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>712565</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6649707</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123054320</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Charlottenberg, V om, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>712566</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6649705</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126474935</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98127</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kassjön 200-450 m OSO centrala delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>712020</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6649811</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>68271506</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kassjön 300-450 m OSO centrala delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>711859</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6649779</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ett tiotal ex på trampad, frisk betesmark. I SV-hörnet av den öppna naturbetesmarken.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Naturbetesmark (nöt)</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>78836217</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kassjön, O om, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>711862</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6649788</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2019-07-04</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>I kanten av traktorväg - ganska fuktigt och skuggigt.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Lerig och fuktig mark</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>86610500</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kassjön, 250 m SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>711859</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6649785</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Lerig körväg</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>102571819</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kassjön, strax SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>711865</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6649786</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturbetesmark, fuktig</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>110437439</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kassjön SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>711862</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6649784</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Fruktgömmena ännu ej nedfällda.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Blandskogsbryn (kanten av hage)</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126474937</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kassjön 200-450 m OSO centrala delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>711867</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6649782</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>122999304</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>711856</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6649789</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>123008739</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kassjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>712097</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>123054342</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>712108</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6649846</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>123054371</v>
+      </c>
+      <c r="B92" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kassjön, O-SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>711866</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6649752</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog - mest gran</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Joakim Ekman, Gabriel Ekman, Viktor Lund, Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126474936</v>
+      </c>
+      <c r="B93" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kassjön 200-450 m OSO centrala delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>712020</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6649811</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ny dellokal</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9472-2025 artfynd.xlsx
+++ b/artfynd/A 9472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -816,6 +821,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123001473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123002458</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123002544</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124420481</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594071</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128595186</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128593978</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594811</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128596191</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128595009</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88192713</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88192654</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2162,6 +2232,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128595580</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128595026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,6 +2538,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594434</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128620434</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88192841</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2765,6 +2865,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594652</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2862,6 +2967,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128594356</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2959,6 +3069,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008808</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3076,6 +3191,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88779583</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3183,6 +3303,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054315</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3285,6 +3410,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997556</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3387,6 +3517,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122999168</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3489,6 +3624,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123000100</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3591,6 +3731,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997583</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3703,6 +3848,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123000064</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3810,6 +3960,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054334</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3907,6 +4062,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122999379</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4004,6 +4164,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008545</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4111,6 +4276,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054344</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4223,6 +4393,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60861108</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4349,6 +4524,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61612201</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4480,6 +4660,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61839173</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4598,6 +4783,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>BSIS - Floraväkteri-exkursion</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78836215</t>
         </is>
       </c>
     </row>
@@ -4706,6 +4896,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88726494</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4820,6 +5015,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122996823</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4936,6 +5136,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997028</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5052,6 +5257,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122997739</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122998042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5277,6 +5492,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122998128</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5391,6 +5611,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122998729</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5502,6 +5727,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122998873</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5613,6 +5843,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122998889</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5727,6 +5962,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122999077</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5843,6 +6083,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122999323</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5954,6 +6199,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123002767</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6051,6 +6301,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123003467</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6167,6 +6422,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008031</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6283,6 +6543,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008181</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6394,6 +6659,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008249</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6510,6 +6780,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123009298</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6621,6 +6896,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123009388</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6727,6 +7007,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123011797</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6843,6 +7128,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054333</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6959,6 +7249,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054336</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7066,6 +7361,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054337</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7173,6 +7473,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054338</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7285,6 +7590,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054339</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7401,6 +7711,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054345</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7508,6 +7823,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054346</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7624,6 +7944,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054347</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7740,6 +8065,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054351</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7856,6 +8186,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054352</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7975,6 +8310,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128593847</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8086,6 +8426,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123001398</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8192,6 +8537,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123002982</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8298,6 +8648,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123003233</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8409,6 +8764,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123007916</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8515,6 +8875,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123011961</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8622,6 +8987,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054332</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8729,6 +9099,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054353</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8826,6 +9201,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123000056</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8923,6 +9303,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123000217</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9020,6 +9405,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123005529</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9117,6 +9507,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123007899</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9214,6 +9609,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123012181</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9316,6 +9716,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054320</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9418,6 +9823,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126474935</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9540,6 +9950,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68271506</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9665,6 +10080,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78836217</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9772,6 +10192,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86610500</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9879,6 +10304,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102571819</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9991,6 +10421,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110437439</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10093,6 +10528,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126474937</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10190,6 +10630,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122999304</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10287,6 +10732,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008739</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10394,6 +10844,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054342</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10501,6 +10956,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054371</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10622,8 +11082,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126474936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>